--- a/退職金_DC・DB_重複調整シミュレーション.xlsx
+++ b/退職金_DC・DB_重複調整シミュレーション.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\40_個人年金\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F45348-D183-4BCA-93A1-1A5B88A76258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A34EDFB-0FE1-45C4-88B8-050BC7F0FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -384,9 +384,6 @@
     <t>控除を2回受けられる可能性</t>
   </si>
   <si>
-    <t>会社退職金と企業型DC一時金は、それぞれ退職所得控除の対象となり得ますが、重複期間がある場合は控除額の調整が必要です。</t>
-  </si>
-  <si>
     <t>受取時期の調整効果</t>
   </si>
   <si>
@@ -819,10 +816,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>DC→会社=9年、会社→DC=19年</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>前の退職手当等が控除額未満</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -927,6 +920,15 @@
     <t>会社退職金とDC/DB一時金の受取順序・受取時期を比較し、重複調整の影響を検討するための材料を整理します。現状の重複期間欄は確認用の簡易値であり、申告税額を確定するものではありません。</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>DC→会社退職金は9年、会社退職金→DCは19年。
+DB→会社退職金は4年、会社退職金→DBは4年。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会社退職金とDC・DB一時金は、それぞれ退職所得控除の対象となり得ますが、重複期間がある場合は控除額の調整が必要です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -941,7 +943,7 @@
     <numFmt numFmtId="180" formatCode="0&quot;年&quot;"/>
     <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1455,7 +1457,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4384"/>
+                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4387"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1520,7 +1522,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4385"/>
+                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4388"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1585,7 +1587,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4386"/>
+                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4389"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1943,7 +1945,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" style="10" customWidth="1"/>
     <col min="2" max="2" width="22.25" style="10" customWidth="1"/>
@@ -1954,24 +1956,24 @@
     <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="62" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
@@ -1982,18 +1984,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>217</v>
-      </c>
       <c r="C6" s="11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
@@ -2004,13 +2006,13 @@
         <v>4</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F7" s="6">
         <v>25689</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>5</v>
       </c>
@@ -2021,14 +2023,14 @@
         <v>6</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F8" s="15" t="str">
         <f>DATEDIF($F$7, B8, "Y") &amp; "歳" &amp; DATEDIF($F$7, B8, "YM") &amp; "ヶ月"</f>
         <v>65歳0ヶ月</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>7</v>
       </c>
@@ -2039,7 +2041,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>9</v>
       </c>
@@ -2050,7 +2052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="str">
         <f>$B$6&amp;"の控除計算用加入開始日"</f>
         <v>DCの控除計算用加入開始日</v>
@@ -2062,7 +2064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1">
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="str">
         <f>$B$6&amp;"の控除計算用加入終了日"</f>
         <v>DCの控除計算用加入終了日</v>
@@ -2074,14 +2076,14 @@
         <v>11</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F12" s="11" t="str">
         <f>DATEDIF($F$7, B12, "Y") &amp; "歳" &amp; DATEDIF($F$7, B12, "YM") &amp; "ヶ月"</f>
         <v>66歳0ヶ月</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="str">
         <f>$B$6&amp;"一時金の受取日"</f>
         <v>DC一時金の受取日</v>
@@ -2093,7 +2095,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="str">
         <f>$B$6&amp;"一時金額"</f>
         <v>DC一時金額</v>
@@ -2105,7 +2107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="str">
         <f>"会社退職金→"&amp;B6&amp;"の調整対象期間"</f>
         <v>会社退職金→DCの調整対象期間</v>
@@ -2115,10 +2117,10 @@
         <v>9</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="str">
         <f>B6&amp;"→会社退職金の調整対象期間"</f>
         <v>DC→会社退職金の調整対象期間</v>
@@ -2128,15 +2130,15 @@
         <v>19</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="18.75" customHeight="1">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18.75" customHeight="1">
+    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
@@ -2148,7 +2150,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18.75" customHeight="1">
+    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -2159,7 +2161,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18.75" customHeight="1">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>20</v>
       </c>
@@ -2171,7 +2173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18.75" customHeight="1">
+    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>22</v>
       </c>
@@ -2183,7 +2185,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18.75" customHeight="1">
+    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="str">
         <f>$B$6&amp;"の加入年数"</f>
         <v>DCの加入年数</v>
@@ -2196,7 +2198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18.75" customHeight="1">
+    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="str">
         <f>$B$6&amp;"の退職所得控除額"</f>
         <v>DCの退職所得控除額</v>
@@ -2209,60 +2211,60 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="48" customHeight="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="12" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="61" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C25" s="61"/>
     </row>
-    <row r="27" spans="1:4" ht="18.75" customHeight="1">
+    <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="12" t="s">
         <v>28</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="13"/>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B28" s="61"/>
       <c r="C28" s="61"/>
       <c r="D28" s="13"/>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="B29" s="63"/>
       <c r="C29" s="63"/>
       <c r="D29" s="13"/>
     </row>
-    <row r="30" spans="1:4" ht="18.75" customHeight="1">
+    <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="64" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="64"/>
       <c r="C30" s="64"/>
     </row>
-    <row r="31" spans="1:4" ht="54.95" customHeight="1">
+    <row r="31" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="18" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="61" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C31" s="61"/>
     </row>
-    <row r="32" spans="1:4" ht="54.95" customHeight="1">
+    <row r="32" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="18" t="s">
         <v>31</v>
       </c>
@@ -2272,37 +2274,37 @@
       <c r="C32" s="61"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="54.95" customHeight="1">
+    <row r="33" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="18" t="s">
         <v>33</v>
       </c>
       <c r="B33" s="61" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C33" s="61"/>
       <c r="D33" s="17"/>
     </row>
-    <row r="34" spans="1:4" ht="54.95" customHeight="1">
+    <row r="34" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="18" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="61" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C34" s="61"/>
       <c r="D34" s="17"/>
     </row>
-    <row r="35" spans="1:4" ht="54.95" customHeight="1">
+    <row r="35" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="18" t="s">
         <v>35</v>
       </c>
       <c r="B35" s="61" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C35" s="61"/>
       <c r="D35" s="17"/>
     </row>
-    <row r="36" spans="1:4" ht="18.75" customHeight="1">
+    <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="18" t="s">
         <v>36</v>
       </c>
@@ -2311,7 +2313,7 @@
       </c>
       <c r="C36" s="61"/>
     </row>
-    <row r="37" spans="1:4" ht="50.1" customHeight="1">
+    <row r="37" spans="1:4" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
         <v>38</v>
       </c>
@@ -2321,15 +2323,16 @@
       <c r="C37" s="61"/>
       <c r="D37" s="17"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B38" s="60" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="wk22Vh9GcSruQCaHGxM2I+NCwzsRiISxs5So5KYQI8ZFQj71a2CvnzYW/y3nxuogXgQd2zSANEEnhJ4ehZR4TQ==" saltValue="K0cUR0lxmhRr4NIfRwossA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -2365,18 +2368,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30" style="10" customWidth="1"/>
     <col min="2" max="2" width="22.625" style="10" customWidth="1"/>
-    <col min="3" max="3" width="40.125" style="10" customWidth="1"/>
-    <col min="4" max="4" width="34.875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="44.625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="46.375" style="10" customWidth="1"/>
     <col min="5" max="5" width="14.75" style="10" customWidth="1"/>
     <col min="6" max="6" width="12" style="10" customWidth="1"/>
     <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="67" t="s">
         <v>40</v>
       </c>
@@ -2386,7 +2389,7 @@
       <c r="E1" s="66"/>
       <c r="F1" s="66"/>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1">
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>41</v>
       </c>
@@ -2404,7 +2407,7 @@
       </c>
       <c r="F3" s="12"/>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1">
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>45</v>
       </c>
@@ -2421,7 +2424,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>48</v>
       </c>
@@ -2438,7 +2441,7 @@
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
     </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1">
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2455,7 +2458,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>53</v>
       </c>
@@ -2472,7 +2475,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>55</v>
       </c>
@@ -2489,7 +2492,7 @@
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>57</v>
       </c>
@@ -2506,7 +2509,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>59</v>
       </c>
@@ -2523,7 +2526,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>62</v>
       </c>
@@ -2542,16 +2545,16 @@
       </c>
       <c r="F11" s="13"/>
     </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1">
+    <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="16">
-        <f>入力!B16</f>
-        <v>19</v>
+        <f>IF(ISNUMBER(SEARCH("→ 会社退職金",入力!B18)),入力!B15,IF(ISNUMBER(SEARCH("会社退職金 →",入力!B18)),入力!B16,""))</f>
+        <v>9</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>65</v>
@@ -2559,13 +2562,13 @@
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B13" s="16" t="str">
         <f>IF(OR(B5="",B6="",B12=""),"",IF(YEARFRAC(B5,B6,1)&lt;=B12,"対象","対象外"))</f>
-        <v>対象</v>
+        <v>対象外</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>67</v>
@@ -2578,13 +2581,13 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B14" s="16" t="str">
+      <c r="B14" s="16">
         <f>IF(B13="対象","要計算（開始日・終了日で算定）",IF(B13="対象外",0,"要確認"))</f>
-        <v>要計算（開始日・終了日で算定）</v>
+        <v>0</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>70</v>
@@ -2599,13 +2602,13 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1">
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="16" t="str">
+      <c r="B15" s="16">
         <f>IF(B14=0,IF(B4="企業型DC",入力!B23,入力!B21),"要計算")</f>
-        <v>要計算</v>
+        <v>6000000</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>73</v>
@@ -2620,7 +2623,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1">
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
         <v>75</v>
       </c>
@@ -2631,7 +2634,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1">
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
         <v>26</v>
       </c>
@@ -2639,8 +2642,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1"/>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1">
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="12" t="s">
         <v>79</v>
       </c>
@@ -2652,22 +2655,22 @@
       <c r="E19" s="66"/>
       <c r="F19" s="66"/>
     </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1">
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
       <c r="D20" s="66"/>
       <c r="E20" s="66"/>
       <c r="F20" s="66"/>
     </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1">
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="66"/>
       <c r="C21" s="66"/>
       <c r="D21" s="66"/>
       <c r="E21" s="66"/>
       <c r="F21" s="66"/>
     </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1"/>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1">
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="65" t="s">
         <v>81</v>
       </c>
@@ -2675,39 +2678,39 @@
       <c r="C23" s="66"/>
       <c r="D23" s="66"/>
     </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1">
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>82</v>
       </c>
       <c r="B24" s="68" t="s">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="C24" s="66"/>
       <c r="D24" s="66"/>
     </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1">
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="68" t="s">
         <v>84</v>
-      </c>
-      <c r="B25" s="68" t="s">
-        <v>85</v>
       </c>
       <c r="C25" s="66"/>
       <c r="D25" s="66"/>
     </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1">
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B26" s="68" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C26" s="66"/>
       <c r="D26" s="66"/>
     </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1"/>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8j75dRmrA6xe8KiWnttmznHgUHDPX/TT2uZEnJHlQDzN/mjOKLdrAX+ffDSC9cVqLuiZS2qUo5X5am14EDBsnw==" saltValue="zfL+G8Q6nvc3tO7tok6ytA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ifNBCZqiO8+mmYbAfzrWPolPVTHUv+Zsm6KmmW171D9RHCqIPBdvIGE9pu+fl3sU2jGKIoXL64H/EFud49HRHg==" saltValue="Ql9f02+LZ1pla8xJcjabWA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="6">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A1:F1"/>
@@ -2725,7 +2728,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="10" customWidth="1"/>
     <col min="2" max="2" width="13" style="10" customWidth="1"/>
@@ -2759,9 +2762,9 @@
     <col min="44" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="24">
+    <row r="1" spans="1:43" ht="24" x14ac:dyDescent="0.5">
       <c r="A1" s="69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B1" s="69"/>
       <c r="C1" s="69"/>
@@ -2773,31 +2776,31 @@
       <c r="I1" s="69"/>
       <c r="J1" s="69"/>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN2" s="10"/>
+    </row>
+    <row r="3" spans="1:43" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="AN2" s="10"/>
-    </row>
-    <row r="3" spans="1:43" ht="60" customHeight="1">
-      <c r="A3" s="22" t="s">
+      <c r="B3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="C3" s="22" t="s">
+      <c r="D3" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="22" t="s">
         <v>92</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>93</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>9</v>
@@ -2806,115 +2809,115 @@
         <v>15</v>
       </c>
       <c r="H3" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="I3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="J3" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="K3" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="L3" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="M3" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="N3" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="L3" s="23" t="s">
+      <c r="O3" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="P3" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q3" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="R3" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="S3" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="T3" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="U3" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="V3" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="W3" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="X3" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y3" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="M3" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="N3" s="23" t="s">
-        <v>97</v>
-      </c>
-      <c r="O3" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="P3" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q3" s="23" t="s">
-        <v>100</v>
-      </c>
-      <c r="R3" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="S3" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="T3" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="U3" s="23" t="s">
-        <v>103</v>
-      </c>
-      <c r="V3" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="W3" s="23" t="s">
-        <v>104</v>
-      </c>
-      <c r="X3" s="23" t="s">
+      <c r="Z3" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="Y3" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z3" s="23" t="s">
+      <c r="AA3" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="AA3" s="23" t="s">
+      <c r="AB3" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="AB3" s="23" t="s">
+      <c r="AC3" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="AC3" s="23" t="s">
+      <c r="AD3" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="AD3" s="23" t="s">
+      <c r="AE3" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="AE3" s="23" t="s">
+      <c r="AF3" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="AF3" s="23" t="s">
+      <c r="AG3" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="AG3" s="23" t="s">
+      <c r="AH3" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="AI3" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ3" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK3" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="AH3" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="AI3" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ3" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK3" s="23" t="s">
+      <c r="AL3" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM3" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="AL3" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="AM3" s="23" t="s">
+      <c r="AN3" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="AN3" s="23" t="s">
+      <c r="AO3" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP3" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="AO3" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="AP3" s="23" t="s">
-        <v>117</v>
-      </c>
       <c r="AQ3" s="23" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="4" spans="1:43" ht="18.75" customHeight="1">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -3254,7 +3257,7 @@
         <v>10452828</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="18.75" customHeight="1">
+    <row r="5" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -3583,7 +3586,7 @@
         <v>10493248</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="18.75" customHeight="1">
+    <row r="6" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -3912,7 +3915,7 @@
         <v>10533668</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="18.75" customHeight="1">
+    <row r="7" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -4241,7 +4244,7 @@
         <v>10574088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="18.75" customHeight="1">
+    <row r="8" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -4570,7 +4573,7 @@
         <v>10614508</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="18.75" customHeight="1">
+    <row r="9" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -4899,7 +4902,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="18.75" customHeight="1">
+    <row r="10" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -5228,7 +5231,7 @@
         <v>10695348</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="18.75" customHeight="1">
+    <row r="11" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -5557,7 +5560,7 @@
         <v>10728110</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="18.75" customHeight="1">
+    <row r="12" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -5886,7 +5889,7 @@
         <v>10758320</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="18.75" customHeight="1">
+    <row r="13" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -6215,24 +6218,24 @@
         <v>10788530</v>
       </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.4">
       <c r="AJ14" s="11"/>
     </row>
-    <row r="15" spans="1:43" ht="19.5">
+    <row r="15" spans="1:43" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A15" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="O15" s="37"/>
+    </row>
+    <row r="16" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="38" t="s">
         <v>118</v>
-      </c>
-      <c r="O15" s="37"/>
-    </row>
-    <row r="16" spans="1:43" ht="18.75" customHeight="1">
-      <c r="A16" s="38" t="s">
-        <v>119</v>
       </c>
       <c r="B16" s="38"/>
       <c r="C16" s="38"/>
       <c r="D16" s="38"/>
       <c r="E16" s="39" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F16" s="40"/>
       <c r="G16" s="40"/>
@@ -6240,7 +6243,7 @@
       <c r="I16" s="40"/>
       <c r="J16" s="40"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B17" s="40"/>
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
@@ -6251,7 +6254,7 @@
       <c r="I17" s="40"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B18" s="40"/>
       <c r="C18" s="40"/>
       <c r="D18" s="40"/>
@@ -6262,59 +6265,60 @@
       <c r="I18" s="40"/>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="39" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="41" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C20" s="39" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="41"/>
       <c r="C21" s="39" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="41"/>
       <c r="C22" s="39" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="C23" s="39" t="s">
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A24" s="41" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="41" t="s">
+      <c r="C24" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="C24" s="39" t="s">
+    </row>
+    <row r="25" spans="1:10" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="A25" s="41" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" ht="19.5">
-      <c r="A25" s="41" t="s">
+      <c r="B25" s="42" t="s">
         <v>127</v>
       </c>
-      <c r="B25" s="42" t="s">
-        <v>128</v>
-      </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="7A9UXF2xczKPds6wI+lCm9Cm2b7h85yl09b4tt/0si3ZUpbkNUaVRC6W4j1Xh/kCCKqLvkGEwz7c852alayJOA==" saltValue="uW/rq+rt/iz/qon/+Z+MNA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -6336,7 +6340,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18" style="10" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="10" bestFit="1" customWidth="1"/>
@@ -6356,180 +6360,180 @@
     <col min="23" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="A4" s="43" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
-      <c r="A4" s="43" t="s">
-        <v>130</v>
       </c>
       <c r="B4" s="1">
         <v>25689</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A5" s="43" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B5" s="1">
         <v>32599</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A6" s="43" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B6" s="1">
         <v>49460</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E6" s="11" t="str">
         <f>DATEDIF(B4, B6, "Y") &amp; "歳" &amp; DATEDIF(B4, B6, "YM") &amp; "ヶ月"</f>
         <v>65歳0ヶ月</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A7" s="43" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B7" s="44">
         <f>IF(DATEDIF(B5,B6+1,"M")=0, 1, CEILING(DATEDIF(B5,B6+1,"M")/12, 1))</f>
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A8" s="43" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" s="45">
         <f>IF(B7&lt;=20, MAX(400000*B7, 800000), 8000000+700000*(B7-20))</f>
         <v>26900000</v>
       </c>
       <c r="C8" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="A9" s="43" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
-      <c r="A9" s="43" t="s">
-        <v>136</v>
       </c>
       <c r="B9" s="4">
         <v>10000000</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A10" s="43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B10" s="45">
         <f>MAX(0, FLOOR((B9-B8)/2, 1000))</f>
         <v>0</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="A11" s="43" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
-      <c r="A11" s="43" t="s">
-        <v>138</v>
       </c>
       <c r="B11" s="46">
         <f>VLOOKUP(B10,tabletax,3,TRUE)</f>
         <v>0.05</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="R11" s="47"/>
       <c r="S11" s="47"/>
       <c r="T11" s="47"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A12" s="43" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B12" s="45">
         <f>VLOOKUP(B10,tabletax,4,TRUE)</f>
         <v>0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O12" s="47"/>
       <c r="P12" s="47"/>
       <c r="Q12" s="47"/>
       <c r="R12" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="S12" s="47"/>
       <c r="T12" s="47"/>
       <c r="V12" s="47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="W12" s="47"/>
       <c r="X12" s="47"/>
       <c r="Y12" s="47"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A13" s="43" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B13" s="45">
         <f>FLOOR((B10*B11-B12)*1.021, 1)</f>
         <v>0</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O13" s="47"/>
       <c r="P13" s="47"/>
       <c r="Q13" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="R13" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="R13" s="48" t="s">
+      <c r="S13" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="S13" s="48" t="s">
+      <c r="T13" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="T13" s="48" t="s">
-        <v>148</v>
-      </c>
       <c r="V13" s="47" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="W13" s="47"/>
       <c r="X13" s="47"/>
       <c r="Y13" s="47"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A14" s="43" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B14" s="45">
         <f>FLOOR(B10 * 0.1, 100)</f>
         <v>0</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="N14" s="47" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O14" s="47"/>
       <c r="P14" s="47"/>
@@ -6537,7 +6541,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="48" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="S14" s="49">
         <v>0.05</v>
@@ -6546,32 +6550,32 @@
         <v>0</v>
       </c>
       <c r="V14" s="47" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="W14" s="47"/>
       <c r="X14" s="47"/>
       <c r="Y14" s="47"/>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A15" s="43" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15" s="50">
         <f>B13+B14</f>
         <v>0</v>
       </c>
       <c r="N15" s="48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O15" s="48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P15" s="47"/>
       <c r="Q15" s="51">
         <v>1950000</v>
       </c>
       <c r="R15" s="51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S15" s="49">
         <v>0.1</v>
@@ -6580,29 +6584,29 @@
         <v>97500</v>
       </c>
       <c r="V15" s="47" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A16" s="43" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B16" s="45">
         <f>B9-B15</f>
         <v>10000000</v>
       </c>
       <c r="N16" s="52" t="s">
+        <v>160</v>
+      </c>
+      <c r="O16" s="52" t="s">
         <v>161</v>
-      </c>
-      <c r="O16" s="52" t="s">
-        <v>162</v>
       </c>
       <c r="P16" s="47"/>
       <c r="Q16" s="51">
         <v>3300000</v>
       </c>
       <c r="R16" s="51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="S16" s="49">
         <v>0.2</v>
@@ -6615,18 +6619,18 @@
       <c r="X16" s="47"/>
       <c r="Y16" s="47"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B17" s="34"/>
       <c r="N17" s="53"/>
       <c r="O17" s="54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P17" s="47"/>
       <c r="Q17" s="51">
         <v>6950000</v>
       </c>
       <c r="R17" s="51" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="S17" s="49">
         <v>0.23</v>
@@ -6639,19 +6643,19 @@
       <c r="X17" s="47"/>
       <c r="Y17" s="47"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.4">
       <c r="N18" s="48" t="s">
+        <v>165</v>
+      </c>
+      <c r="O18" s="48" t="s">
         <v>166</v>
-      </c>
-      <c r="O18" s="48" t="s">
-        <v>167</v>
       </c>
       <c r="P18" s="47"/>
       <c r="Q18" s="51">
         <v>9000000</v>
       </c>
       <c r="R18" s="51" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="S18" s="49">
         <v>0.33</v>
@@ -6664,7 +6668,7 @@
       <c r="X18" s="47"/>
       <c r="Y18" s="47"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.4">
       <c r="N19" s="47"/>
       <c r="O19" s="47"/>
       <c r="P19" s="47"/>
@@ -6672,7 +6676,7 @@
         <v>18000000</v>
       </c>
       <c r="R19" s="51" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="S19" s="49">
         <v>0.4</v>
@@ -6685,7 +6689,7 @@
       <c r="X19" s="47"/>
       <c r="Y19" s="47"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.4">
       <c r="N20" s="47"/>
       <c r="O20" s="47"/>
       <c r="P20" s="47"/>
@@ -6693,7 +6697,7 @@
         <v>40000000</v>
       </c>
       <c r="R20" s="51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="S20" s="49">
         <v>0.45</v>
@@ -6706,7 +6710,7 @@
       <c r="X20" s="47"/>
       <c r="Y20" s="47"/>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.4">
       <c r="N21" s="47"/>
       <c r="O21" s="47"/>
       <c r="P21" s="47"/>
@@ -6715,59 +6719,59 @@
       <c r="X21" s="47"/>
       <c r="Y21" s="47"/>
     </row>
-    <row r="22" spans="2:25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.4">
       <c r="W22" s="47"/>
       <c r="X22" s="47"/>
       <c r="Y22" s="47"/>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.4">
       <c r="W23" s="47"/>
       <c r="X23" s="47"/>
       <c r="Y23" s="47"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" s="11" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A34" s="11" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="11" t="s">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A35" s="55" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="55" t="s">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A36" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="11" t="s">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A37" s="55" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="55" t="s">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A38" s="11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="11" t="s">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A39" s="55" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="55" t="s">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A40" s="11" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="11" t="s">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A41" s="55" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="55" t="s">
-        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -6795,96 +6799,96 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="38" style="2" customWidth="1"/>
     <col min="2" max="2" width="42" style="2" customWidth="1"/>
     <col min="3" max="6" width="20" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24">
+    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.5">
       <c r="A1" s="70" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1" s="71"/>
       <c r="C1" s="71"/>
       <c r="D1" s="71"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B3" s="72" t="s">
         <v>180</v>
-      </c>
-      <c r="B3" s="72" t="s">
-        <v>181</v>
       </c>
       <c r="C3" s="71"/>
       <c r="D3" s="71"/>
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B4" s="71"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B5" s="71"/>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
       <c r="E5" s="71"/>
       <c r="F5" s="71"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="72" t="s">
         <v>182</v>
-      </c>
-      <c r="B6" s="72" t="s">
-        <v>183</v>
       </c>
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B7" s="71"/>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B8" s="71"/>
       <c r="C8" s="71"/>
       <c r="D8" s="71"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="72" t="s">
         <v>184</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>185</v>
       </c>
       <c r="C9" s="71"/>
       <c r="D9" s="71"/>
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B10" s="71"/>
       <c r="C10" s="71"/>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B11" s="71"/>
       <c r="C11" s="71"/>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B12" s="71"/>
       <c r="C12" s="71"/>
@@ -6892,64 +6896,64 @@
       <c r="E12" s="71"/>
       <c r="F12" s="71"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B13" s="71"/>
       <c r="C13" s="71"/>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B14" s="71"/>
       <c r="C14" s="71"/>
       <c r="D14" s="71"/>
       <c r="E14" s="71"/>
       <c r="F14" s="71"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B16" s="71"/>
       <c r="C16" s="71"/>
       <c r="D16" s="71"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B17" s="73" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C17" s="73"/>
       <c r="D17" s="73"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B18" s="73" t="s">
         <v>189</v>
-      </c>
-      <c r="B18" s="73" t="s">
-        <v>190</v>
       </c>
       <c r="C18" s="73"/>
       <c r="D18" s="73"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20"/>
       <c r="B20" s="9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21"/>
       <c r="B21"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22"/>
       <c r="B22"/>
     </row>
@@ -6980,24 +6984,24 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
     <col min="2" max="3" width="12" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="56" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B1" s="57" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="56" t="s">
         <v>147</v>
       </c>
-      <c r="C1" s="56" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="58">
         <v>0</v>
       </c>
@@ -7008,7 +7012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="58">
         <v>1950000</v>
       </c>
@@ -7019,7 +7023,7 @@
         <v>97500</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="58">
         <v>3300000</v>
       </c>
@@ -7030,7 +7034,7 @@
         <v>427500</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="58">
         <v>6950000</v>
       </c>
@@ -7041,7 +7045,7 @@
         <v>636000</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="58">
         <v>9000000</v>
       </c>
@@ -7052,7 +7056,7 @@
         <v>1536000</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="58">
         <v>18000000</v>
       </c>
@@ -7063,7 +7067,7 @@
         <v>2796000</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="58">
         <v>40000000</v>
       </c>
@@ -7075,7 +7079,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="wud38P6r/UuFmLta6rl7BPfCOniGIqycUdRkh3LQBbHVNIshO1jC1MkQzYoyoCWiuw456qey+cMMvyL9EXFqbg==" saltValue="q8wghWMXnBxLKYguyEqABg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="R7HdsFuN7G+M9d7WfXO4Fl+u2EykUniR6JrXMEKI+Nt7y1LecwUpOIkNXPgJxsxAt1hMYvUlokrUyrVbaonC2Q==" saltValue="/4G4w0SIARQnBxiO4mBxkA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/退職金_DC・DB_重複調整シミュレーション.xlsx
+++ b/退職金_DC・DB_重複調整シミュレーション.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\40_個人年金\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A34EDFB-0FE1-45C4-88B8-050BC7F0FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F94255-75D1-4208-B1CB-A680CB3BF7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="入力" sheetId="1" r:id="rId1"/>
-    <sheet name="重複調整計算" sheetId="2" r:id="rId2"/>
-    <sheet name="受取時期比較" sheetId="3" r:id="rId3"/>
-    <sheet name="会社退職金" sheetId="5" r:id="rId4"/>
-    <sheet name="説明・参照情報" sheetId="9" r:id="rId5"/>
-    <sheet name="税率表" sheetId="10" r:id="rId6"/>
+    <sheet name="期間図" sheetId="11" r:id="rId2"/>
+    <sheet name="重複調整計算" sheetId="2" r:id="rId3"/>
+    <sheet name="受取時期比較" sheetId="3" r:id="rId4"/>
+    <sheet name="会社退職金" sheetId="5" r:id="rId5"/>
+    <sheet name="説明・参照情報" sheetId="9" r:id="rId6"/>
+    <sheet name="税率表" sheetId="10" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">受取時期比較!$A$3:$AC$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">会社退職金!$A$1:$L$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">受取時期比較!$A$3:$AC$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">会社退職金!$A$1:$L$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">期間図!$A$1:$BF$70</definedName>
     <definedName name="tabletax">会社退職金!$Q$14:$T$19</definedName>
   </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
@@ -133,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="281">
   <si>
     <t>入力項目</t>
   </si>
@@ -929,6 +931,333 @@
     <t>会社退職金とDC・DB一時金は、それぞれ退職所得控除の対象となり得ますが、重複期間がある場合は控除額の調整が必要です。</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>退職所得控除の調整規定</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>■DC（企業型DC・iDeCo）の老齢一時金は税法上「退職手当等」に該当し、退職所得控除が適用される</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>■退職手当等の支払を複数受ける場合は、後に支払を受ける退職手当等の退職所得控除を算出するに当たって、過去に支払を受けた</t>
+  </si>
+  <si>
+    <t>　退職手当等と重複する期間の年数に基づく退職所得控除額を控除する仕組みとなっている。</t>
+  </si>
+  <si>
+    <t>退職一時金（DCの老齢一時金を除く）</t>
+  </si>
+  <si>
+    <r>
+      <t>前年以前</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>９年内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>に他の支払者から支払われた退職手当等との重複期間に基づく</t>
+    </r>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>の退職所得控除額</t>
+  </si>
+  <si>
+    <t>額を控除した残額</t>
+  </si>
+  <si>
+    <t>DCの老齢一時金の退職所得控除額</t>
+  </si>
+  <si>
+    <r>
+      <t>前年以前</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>19年内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>に他の支払者から支払われた退職手当等との重複期間</t>
+    </r>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>に基づく額を控除した残額</t>
+  </si>
+  <si>
+    <t>　https://www.nta.go.jp/taxes/shiraberu/taxanswer/gensen/2732.htm</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>退職金・DC/iDeCo「重複期間」図解</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>年齢の列を横軸として、会社の勤続期間・DC/iDeCo加入期間・その共通部分を色分けしています。</t>
+  </si>
+  <si>
+    <t>会社：青</t>
+  </si>
+  <si>
+    <t>DC/iDeCo：橙</t>
+  </si>
+  <si>
+    <t>重複：黄</t>
+  </si>
+  <si>
+    <t>年齢</t>
+  </si>
+  <si>
+    <t>ケースA：DC/iDeCo → 退職金</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>退職金 65歳</t>
+  </si>
+  <si>
+    <t>会社の勤続期間</t>
+  </si>
+  <si>
+    <t>DC/iDeCo加入期間</t>
+  </si>
+  <si>
+    <t>重複期間</t>
+  </si>
+  <si>
+    <t>受給時点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC/iDeCo 60歳 </t>
+  </si>
+  <si>
+    <t>前年以前9年内</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>重複期間：30歳～60歳 ＝ 30年間</t>
+  </si>
+  <si>
+    <t>黄色の部分が、会社の勤続期間とDC/iDeCo加入期間の両方に含まれる範囲です。</t>
+  </si>
+  <si>
+    <t>ケースB：退職金 → DC/iDeCo</t>
+  </si>
+  <si>
+    <t>退職金 60歳</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DC/iDeCo 65歳 </t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>前年以前19年内</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>■DB(確定給付企業年金 / Defined Benefit Plan)の場合</t>
+    <rPh sb="0" eb="39">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>退職一時金（DCの老齢一時金を除く）</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <r>
+      <t>前年以前</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>４年内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>に他の支払者から支払われた退職手当等との重複期間に基づく</t>
+    </r>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>DBの一時金の退職所得控除額</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <r>
+      <t>前年以前</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>４年内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>に他の支払者から支払われた退職手当等（DCの老齢一時金を除く）</t>
+    </r>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>との重複期間に基づく額を控除した残額</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>退職金・DB「重複期間」図解</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>ケースC：DB → 退職金</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>DB加入期間</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DB 60歳 </t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>前年以前4年内</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>黄色の部分が、会社の勤続期間とDB加入期間の両方に含まれる範囲です。</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <r>
+      <t>緑色の部分が重複の調整範囲外のため、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>重複調整なし。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ミドリイロ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウフク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>チョウセイ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ガイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>チョウフク</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>ケースD：退職金 → DB</t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t xml:space="preserve">DB 65歳 </t>
+    <phoneticPr fontId="12"/>
+  </si>
+  <si>
+    <t>重複期間：30歳～65歳 ＝ 35年間</t>
+  </si>
+  <si>
+    <t>大切な注意</t>
+  </si>
+  <si>
+    <t>図中の重複期間は、指定された年齢範囲を比較した概念上の期間です。税務上の退職所得控除の調整年数と必ず一致するわけではありません。実際の調整は、受給年・受給順・退職手当等の種類・法令上の対象期間などを確認して行います。</t>
+  </si>
+  <si>
+    <t>年数の数え方</t>
+  </si>
+  <si>
+    <t>この図では「30歳～60歳」を30年間、「30歳～65歳」を35年間とする、年齢差（終了年齢－開始年齢）で表示しています。税務上の勤続年数・加入年数の端数処理とは別です。</t>
+  </si>
 </sst>
 </file>
 
@@ -943,7 +1272,7 @@
     <numFmt numFmtId="180" formatCode="0&quot;年&quot;"/>
     <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1029,8 +1358,76 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1068,8 +1465,30 @@
         <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF28E2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1142,16 +1561,99 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1409,10 +1911,57 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="13" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="標準 2" xfId="2" xr:uid="{32AC61CE-BE69-4D48-8FBD-690D7973CA59}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1457,7 +2006,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4387"/>
+                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4396"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1522,7 +2071,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4388"/>
+                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4397"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1587,7 +2136,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4389"/>
+                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4398"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1945,7 +2494,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="34" style="10" customWidth="1"/>
     <col min="2" max="2" width="22.25" style="10" customWidth="1"/>
@@ -1956,24 +2505,24 @@
     <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1">
       <c r="A1" s="62" t="s">
         <v>216</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6">
       <c r="A2" s="10" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6">
       <c r="A3" s="10" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
@@ -1984,7 +2533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6">
       <c r="A6" s="10" t="s">
         <v>213</v>
       </c>
@@ -1995,7 +2544,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1">
       <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
@@ -2012,7 +2561,7 @@
         <v>25689</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1">
       <c r="A8" s="13" t="s">
         <v>5</v>
       </c>
@@ -2030,7 +2579,7 @@
         <v>65歳0ヶ月</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1">
       <c r="A9" s="13" t="s">
         <v>7</v>
       </c>
@@ -2041,7 +2590,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1">
       <c r="A10" s="13" t="s">
         <v>9</v>
       </c>
@@ -2052,7 +2601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>$B$6&amp;"の控除計算用加入開始日"</f>
         <v>DCの控除計算用加入開始日</v>
@@ -2064,7 +2613,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="18.75" customHeight="1">
       <c r="A12" s="13" t="str">
         <f>$B$6&amp;"の控除計算用加入終了日"</f>
         <v>DCの控除計算用加入終了日</v>
@@ -2083,7 +2632,7 @@
         <v>66歳0ヶ月</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1">
       <c r="A13" s="13" t="str">
         <f>$B$6&amp;"一時金の受取日"</f>
         <v>DC一時金の受取日</v>
@@ -2095,7 +2644,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1">
       <c r="A14" s="13" t="str">
         <f>$B$6&amp;"一時金額"</f>
         <v>DC一時金額</v>
@@ -2107,7 +2656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6">
       <c r="A15" s="10" t="str">
         <f>"会社退職金→"&amp;B6&amp;"の調整対象期間"</f>
         <v>会社退職金→DCの調整対象期間</v>
@@ -2120,7 +2669,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6">
       <c r="A16" s="13" t="str">
         <f>B6&amp;"→会社退職金の調整対象期間"</f>
         <v>DC→会社退職金の調整対象期間</v>
@@ -2133,12 +2682,12 @@
         <v>218</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="18.75" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="18.75" customHeight="1">
       <c r="A18" s="10" t="s">
         <v>15</v>
       </c>
@@ -2150,7 +2699,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="18.75" customHeight="1">
       <c r="A19" s="12" t="s">
         <v>17</v>
       </c>
@@ -2161,7 +2710,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1">
       <c r="A20" s="13" t="s">
         <v>20</v>
       </c>
@@ -2173,7 +2722,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="18.75" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>22</v>
       </c>
@@ -2185,7 +2734,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="18.75" customHeight="1">
       <c r="A22" s="13" t="str">
         <f>$B$6&amp;"の加入年数"</f>
         <v>DCの加入年数</v>
@@ -2198,7 +2747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="18.75" customHeight="1">
       <c r="A23" s="13" t="str">
         <f>$B$6&amp;"の退職所得控除額"</f>
         <v>DCの退職所得控除額</v>
@@ -2211,7 +2760,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4">
       <c r="A24" s="10" t="s">
         <v>26</v>
       </c>
@@ -2219,7 +2768,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" ht="48" customHeight="1">
       <c r="A25" s="12" t="s">
         <v>27</v>
       </c>
@@ -2228,7 +2777,7 @@
       </c>
       <c r="C25" s="61"/>
     </row>
-    <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" ht="18.75" customHeight="1">
       <c r="A27" s="12" t="s">
         <v>28</v>
       </c>
@@ -2238,24 +2787,24 @@
       <c r="C27" s="61"/>
       <c r="D27" s="13"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4">
       <c r="B28" s="61"/>
       <c r="C28" s="61"/>
       <c r="D28" s="13"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4">
       <c r="B29" s="63"/>
       <c r="C29" s="63"/>
       <c r="D29" s="13"/>
     </row>
-    <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" ht="18.75" customHeight="1">
       <c r="A30" s="64" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="64"/>
       <c r="C30" s="64"/>
     </row>
-    <row r="31" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" ht="54.95" customHeight="1">
       <c r="A31" s="18" t="s">
         <v>30</v>
       </c>
@@ -2264,7 +2813,7 @@
       </c>
       <c r="C31" s="61"/>
     </row>
-    <row r="32" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" ht="54.95" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>31</v>
       </c>
@@ -2274,7 +2823,7 @@
       <c r="C32" s="61"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="54.95" customHeight="1">
       <c r="A33" s="18" t="s">
         <v>33</v>
       </c>
@@ -2284,7 +2833,7 @@
       <c r="C33" s="61"/>
       <c r="D33" s="17"/>
     </row>
-    <row r="34" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" ht="54.95" customHeight="1">
       <c r="A34" s="18" t="s">
         <v>34</v>
       </c>
@@ -2294,7 +2843,7 @@
       <c r="C34" s="61"/>
       <c r="D34" s="17"/>
     </row>
-    <row r="35" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" ht="54.95" customHeight="1">
       <c r="A35" s="18" t="s">
         <v>35</v>
       </c>
@@ -2304,7 +2853,7 @@
       <c r="C35" s="61"/>
       <c r="D35" s="17"/>
     </row>
-    <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" ht="18.75" customHeight="1">
       <c r="A36" s="18" t="s">
         <v>36</v>
       </c>
@@ -2313,7 +2862,7 @@
       </c>
       <c r="C36" s="61"/>
     </row>
-    <row r="37" spans="1:4" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" ht="50.1" customHeight="1">
       <c r="A37" s="19" t="s">
         <v>38</v>
       </c>
@@ -2323,7 +2872,7 @@
       <c r="C37" s="61"/>
       <c r="D37" s="17"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4">
       <c r="A38" s="10" t="s">
         <v>211</v>
       </c>
@@ -2366,9 +2915,2520 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{894AABEA-3A51-4F2B-8D15-E677D9A48641}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:BD70"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="9" style="74"/>
+    <col min="2" max="2" width="16.625" style="74" customWidth="1"/>
+    <col min="3" max="56" width="3.125" style="74" customWidth="1"/>
+    <col min="57" max="16384" width="9" style="74"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:56">
+      <c r="B2" s="74" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="2:56">
+      <c r="B3" s="74" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="2:56">
+      <c r="B4" s="74" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="5" spans="2:56">
+      <c r="B5" s="74" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="6" spans="2:56">
+      <c r="C6" s="75" t="s">
+        <v>233</v>
+      </c>
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="75" t="s">
+        <v>234</v>
+      </c>
+      <c r="N6" s="76"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="76"/>
+      <c r="Q6" s="76"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="76"/>
+      <c r="T6" s="76"/>
+      <c r="U6" s="76"/>
+      <c r="V6" s="76"/>
+      <c r="W6" s="76"/>
+      <c r="X6" s="76"/>
+      <c r="Y6" s="76"/>
+      <c r="Z6" s="76"/>
+      <c r="AA6" s="76"/>
+      <c r="AB6" s="76"/>
+      <c r="AC6" s="76"/>
+      <c r="AD6" s="76"/>
+      <c r="AE6" s="76"/>
+      <c r="AF6" s="76"/>
+      <c r="AG6" s="77"/>
+    </row>
+    <row r="7" spans="2:56">
+      <c r="C7" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="79"/>
+      <c r="G7" s="79"/>
+      <c r="H7" s="79"/>
+      <c r="I7" s="79"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="79"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="N7" s="79"/>
+      <c r="O7" s="79"/>
+      <c r="P7" s="79"/>
+      <c r="Q7" s="79"/>
+      <c r="R7" s="79"/>
+      <c r="S7" s="79"/>
+      <c r="T7" s="79"/>
+      <c r="U7" s="79"/>
+      <c r="V7" s="79"/>
+      <c r="W7" s="79"/>
+      <c r="X7" s="79"/>
+      <c r="Y7" s="79"/>
+      <c r="Z7" s="79"/>
+      <c r="AA7" s="79"/>
+      <c r="AB7" s="79"/>
+      <c r="AC7" s="79"/>
+      <c r="AD7" s="79"/>
+      <c r="AE7" s="79"/>
+      <c r="AF7" s="79"/>
+      <c r="AG7" s="80"/>
+    </row>
+    <row r="8" spans="2:56">
+      <c r="C8" s="75" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="77"/>
+      <c r="M8" s="75" t="s">
+        <v>238</v>
+      </c>
+      <c r="N8" s="76"/>
+      <c r="O8" s="76"/>
+      <c r="P8" s="76"/>
+      <c r="Q8" s="76"/>
+      <c r="R8" s="76"/>
+      <c r="S8" s="76"/>
+      <c r="T8" s="76"/>
+      <c r="U8" s="76"/>
+      <c r="V8" s="76"/>
+      <c r="W8" s="76"/>
+      <c r="X8" s="76"/>
+      <c r="Y8" s="76"/>
+      <c r="Z8" s="76"/>
+      <c r="AA8" s="76"/>
+      <c r="AB8" s="76"/>
+      <c r="AC8" s="76"/>
+      <c r="AD8" s="76"/>
+      <c r="AE8" s="76"/>
+      <c r="AF8" s="76"/>
+      <c r="AG8" s="77"/>
+    </row>
+    <row r="9" spans="2:56">
+      <c r="C9" s="78"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="79"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="79"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="78" t="s">
+        <v>239</v>
+      </c>
+      <c r="N9" s="79"/>
+      <c r="O9" s="79"/>
+      <c r="P9" s="79"/>
+      <c r="Q9" s="79"/>
+      <c r="R9" s="79"/>
+      <c r="S9" s="79"/>
+      <c r="T9" s="79"/>
+      <c r="U9" s="79"/>
+      <c r="V9" s="79"/>
+      <c r="W9" s="79"/>
+      <c r="X9" s="79"/>
+      <c r="Y9" s="79"/>
+      <c r="Z9" s="79"/>
+      <c r="AA9" s="79"/>
+      <c r="AB9" s="79"/>
+      <c r="AC9" s="79"/>
+      <c r="AD9" s="79"/>
+      <c r="AE9" s="79"/>
+      <c r="AF9" s="79"/>
+      <c r="AG9" s="80"/>
+    </row>
+    <row r="10" spans="2:56">
+      <c r="B10" s="74" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="2:56" ht="23.25">
+      <c r="B12" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="C12" s="82"/>
+      <c r="D12" s="82"/>
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="82"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="82"/>
+      <c r="L12" s="82"/>
+      <c r="M12" s="82"/>
+      <c r="N12" s="82"/>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
+      <c r="T12" s="82"/>
+      <c r="U12" s="82"/>
+      <c r="V12" s="82"/>
+      <c r="W12" s="82"/>
+      <c r="X12" s="82"/>
+      <c r="Y12" s="82"/>
+      <c r="Z12" s="82"/>
+      <c r="AA12" s="82"/>
+      <c r="AB12" s="82"/>
+      <c r="AC12" s="82"/>
+      <c r="AD12" s="82"/>
+      <c r="AE12" s="82"/>
+      <c r="AF12" s="82"/>
+      <c r="AG12" s="82"/>
+      <c r="AH12" s="82"/>
+      <c r="AI12" s="82"/>
+      <c r="AJ12" s="82"/>
+      <c r="AK12" s="82"/>
+      <c r="AL12" s="82"/>
+      <c r="AM12" s="82"/>
+      <c r="AN12" s="82"/>
+      <c r="AO12" s="82"/>
+      <c r="AP12" s="82"/>
+      <c r="AQ12" s="82"/>
+      <c r="AR12" s="82"/>
+      <c r="AS12" s="82"/>
+      <c r="AT12" s="82"/>
+      <c r="AU12" s="82"/>
+      <c r="AV12" s="82"/>
+      <c r="AW12" s="82"/>
+      <c r="AX12" s="82"/>
+      <c r="AY12" s="82"/>
+    </row>
+    <row r="13" spans="2:56">
+      <c r="B13" s="83" t="s">
+        <v>242</v>
+      </c>
+      <c r="C13" s="82"/>
+      <c r="D13" s="82"/>
+      <c r="E13" s="82"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="82"/>
+      <c r="H13" s="82"/>
+      <c r="I13" s="82"/>
+      <c r="J13" s="82"/>
+      <c r="K13" s="82"/>
+      <c r="L13" s="82"/>
+      <c r="M13" s="82"/>
+      <c r="N13" s="82"/>
+      <c r="O13" s="82"/>
+      <c r="P13" s="82"/>
+      <c r="Q13" s="82"/>
+      <c r="R13" s="82"/>
+      <c r="S13" s="82"/>
+      <c r="T13" s="82"/>
+      <c r="U13" s="82"/>
+      <c r="V13" s="82"/>
+      <c r="W13" s="82"/>
+      <c r="X13" s="82"/>
+      <c r="Y13" s="82"/>
+      <c r="Z13" s="82"/>
+      <c r="AA13" s="82"/>
+      <c r="AB13" s="82"/>
+      <c r="AC13" s="82"/>
+      <c r="AD13" s="82"/>
+      <c r="AE13" s="82"/>
+      <c r="AF13" s="82"/>
+      <c r="AG13" s="82"/>
+      <c r="AH13" s="82"/>
+      <c r="AI13" s="82"/>
+      <c r="AJ13" s="82"/>
+      <c r="AK13" s="82"/>
+      <c r="AL13" s="82"/>
+      <c r="AM13" s="82"/>
+      <c r="AN13" s="82"/>
+      <c r="AO13" s="82"/>
+      <c r="AP13" s="82"/>
+      <c r="AQ13" s="82"/>
+      <c r="AR13" s="82"/>
+      <c r="AS13" s="82"/>
+      <c r="AT13" s="82"/>
+      <c r="AU13" s="82"/>
+      <c r="AV13" s="82"/>
+      <c r="AW13" s="82"/>
+      <c r="AX13" s="82"/>
+      <c r="AY13" s="82"/>
+    </row>
+    <row r="14" spans="2:56">
+      <c r="B14" s="84"/>
+      <c r="C14" s="85" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="86" t="s">
+        <v>244</v>
+      </c>
+      <c r="H14" s="86"/>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="87" t="s">
+        <v>245</v>
+      </c>
+      <c r="N14" s="87"/>
+      <c r="O14" s="87"/>
+      <c r="P14" s="84"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="84"/>
+      <c r="S14" s="84"/>
+      <c r="T14" s="84"/>
+      <c r="U14" s="84"/>
+      <c r="V14" s="84"/>
+      <c r="W14" s="84"/>
+      <c r="X14" s="84"/>
+      <c r="Y14" s="84"/>
+      <c r="Z14" s="84"/>
+      <c r="AA14" s="84"/>
+      <c r="AB14" s="84"/>
+      <c r="AC14" s="84"/>
+      <c r="AD14" s="84"/>
+      <c r="AE14" s="84"/>
+      <c r="AF14" s="84"/>
+      <c r="AG14" s="84"/>
+      <c r="AH14" s="84"/>
+      <c r="AI14" s="84"/>
+      <c r="AJ14" s="84"/>
+      <c r="AK14" s="84"/>
+      <c r="AL14" s="84"/>
+      <c r="AM14" s="84"/>
+      <c r="AN14" s="84"/>
+      <c r="AO14" s="84"/>
+      <c r="AP14" s="84"/>
+      <c r="AQ14" s="84"/>
+      <c r="AR14" s="84"/>
+      <c r="AS14" s="84"/>
+      <c r="AT14" s="84"/>
+      <c r="AU14" s="84"/>
+      <c r="AV14" s="84"/>
+      <c r="AW14" s="84"/>
+      <c r="AX14" s="84"/>
+      <c r="AY14" s="84"/>
+    </row>
+    <row r="15" spans="2:56">
+      <c r="B15" s="88" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="89">
+        <v>18</v>
+      </c>
+      <c r="D15" s="89">
+        <v>19</v>
+      </c>
+      <c r="E15" s="89">
+        <v>20</v>
+      </c>
+      <c r="F15" s="89">
+        <v>21</v>
+      </c>
+      <c r="G15" s="89">
+        <v>22</v>
+      </c>
+      <c r="H15" s="89">
+        <v>23</v>
+      </c>
+      <c r="I15" s="89">
+        <v>24</v>
+      </c>
+      <c r="J15" s="89">
+        <v>25</v>
+      </c>
+      <c r="K15" s="89">
+        <v>26</v>
+      </c>
+      <c r="L15" s="89">
+        <v>27</v>
+      </c>
+      <c r="M15" s="89">
+        <v>28</v>
+      </c>
+      <c r="N15" s="89">
+        <v>29</v>
+      </c>
+      <c r="O15" s="89">
+        <v>30</v>
+      </c>
+      <c r="P15" s="89">
+        <v>31</v>
+      </c>
+      <c r="Q15" s="89">
+        <v>32</v>
+      </c>
+      <c r="R15" s="89">
+        <v>33</v>
+      </c>
+      <c r="S15" s="89">
+        <v>34</v>
+      </c>
+      <c r="T15" s="89">
+        <v>35</v>
+      </c>
+      <c r="U15" s="89">
+        <v>36</v>
+      </c>
+      <c r="V15" s="89">
+        <v>37</v>
+      </c>
+      <c r="W15" s="89">
+        <v>38</v>
+      </c>
+      <c r="X15" s="89">
+        <v>39</v>
+      </c>
+      <c r="Y15" s="89">
+        <v>40</v>
+      </c>
+      <c r="Z15" s="89">
+        <v>41</v>
+      </c>
+      <c r="AA15" s="89">
+        <v>42</v>
+      </c>
+      <c r="AB15" s="89">
+        <v>43</v>
+      </c>
+      <c r="AC15" s="89">
+        <v>44</v>
+      </c>
+      <c r="AD15" s="89">
+        <v>45</v>
+      </c>
+      <c r="AE15" s="89">
+        <v>46</v>
+      </c>
+      <c r="AF15" s="89">
+        <v>47</v>
+      </c>
+      <c r="AG15" s="89">
+        <v>48</v>
+      </c>
+      <c r="AH15" s="89">
+        <v>49</v>
+      </c>
+      <c r="AI15" s="89">
+        <v>50</v>
+      </c>
+      <c r="AJ15" s="89">
+        <v>51</v>
+      </c>
+      <c r="AK15" s="89">
+        <v>52</v>
+      </c>
+      <c r="AL15" s="89">
+        <v>53</v>
+      </c>
+      <c r="AM15" s="89">
+        <v>54</v>
+      </c>
+      <c r="AN15" s="89">
+        <v>55</v>
+      </c>
+      <c r="AO15" s="89">
+        <v>56</v>
+      </c>
+      <c r="AP15" s="89">
+        <v>57</v>
+      </c>
+      <c r="AQ15" s="89">
+        <v>58</v>
+      </c>
+      <c r="AR15" s="89">
+        <v>59</v>
+      </c>
+      <c r="AS15" s="89">
+        <v>60</v>
+      </c>
+      <c r="AT15" s="89">
+        <v>61</v>
+      </c>
+      <c r="AU15" s="89">
+        <v>62</v>
+      </c>
+      <c r="AV15" s="89">
+        <v>63</v>
+      </c>
+      <c r="AW15" s="89">
+        <v>64</v>
+      </c>
+      <c r="AX15" s="89">
+        <v>65</v>
+      </c>
+      <c r="AY15" s="89">
+        <v>66</v>
+      </c>
+      <c r="AZ15" s="89">
+        <v>67</v>
+      </c>
+      <c r="BA15" s="90"/>
+      <c r="BB15" s="90"/>
+      <c r="BC15" s="90"/>
+      <c r="BD15" s="90"/>
+    </row>
+    <row r="17" spans="2:56">
+      <c r="B17" s="91" t="s">
+        <v>247</v>
+      </c>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="92"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="92"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="92"/>
+      <c r="O17" s="92"/>
+      <c r="P17" s="92"/>
+      <c r="Q17" s="92"/>
+      <c r="R17" s="92"/>
+      <c r="S17" s="92"/>
+      <c r="T17" s="92"/>
+      <c r="U17" s="92"/>
+      <c r="V17" s="92"/>
+      <c r="W17" s="92"/>
+      <c r="X17" s="92"/>
+      <c r="Y17" s="92"/>
+      <c r="Z17" s="92"/>
+      <c r="AA17" s="92"/>
+      <c r="AB17" s="92"/>
+      <c r="AC17" s="92"/>
+      <c r="AD17" s="92"/>
+      <c r="AE17" s="92"/>
+      <c r="AF17" s="92"/>
+      <c r="AG17" s="92"/>
+      <c r="AH17" s="92"/>
+      <c r="AI17" s="92"/>
+      <c r="AJ17" s="92"/>
+      <c r="AK17" s="92"/>
+      <c r="AL17" s="92"/>
+      <c r="AM17" s="92"/>
+      <c r="AN17" s="92"/>
+      <c r="AO17" s="92"/>
+      <c r="AP17" s="92"/>
+      <c r="AQ17" s="92"/>
+      <c r="AR17" s="92"/>
+      <c r="AS17" s="92"/>
+      <c r="AT17" s="92"/>
+      <c r="AU17" s="92"/>
+      <c r="AV17" s="92"/>
+      <c r="AW17" s="92"/>
+      <c r="AX17" s="92" t="s">
+        <v>248</v>
+      </c>
+      <c r="AY17" s="92"/>
+      <c r="AZ17" s="92"/>
+      <c r="BA17" s="92"/>
+      <c r="BB17" s="92"/>
+      <c r="BC17" s="92"/>
+      <c r="BD17" s="92"/>
+    </row>
+    <row r="18" spans="2:56">
+      <c r="B18" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="94"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="94"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
+      <c r="T18" s="94"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="94"/>
+      <c r="W18" s="94"/>
+      <c r="X18" s="94"/>
+      <c r="Y18" s="94"/>
+      <c r="Z18" s="94"/>
+      <c r="AA18" s="94"/>
+      <c r="AB18" s="94"/>
+      <c r="AC18" s="94"/>
+      <c r="AD18" s="94"/>
+      <c r="AE18" s="94"/>
+      <c r="AF18" s="94"/>
+      <c r="AG18" s="94"/>
+      <c r="AH18" s="94"/>
+      <c r="AI18" s="94"/>
+      <c r="AJ18" s="94"/>
+      <c r="AK18" s="94"/>
+      <c r="AL18" s="94"/>
+      <c r="AM18" s="94"/>
+      <c r="AN18" s="94"/>
+      <c r="AO18" s="94"/>
+      <c r="AP18" s="94"/>
+      <c r="AQ18" s="94"/>
+      <c r="AR18" s="94"/>
+      <c r="AS18" s="94"/>
+      <c r="AT18" s="94"/>
+      <c r="AU18" s="94"/>
+      <c r="AV18" s="94"/>
+      <c r="AW18" s="94"/>
+      <c r="AX18" s="94"/>
+    </row>
+    <row r="19" spans="2:56">
+      <c r="B19" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="O19" s="95"/>
+      <c r="P19" s="95"/>
+      <c r="Q19" s="95"/>
+      <c r="R19" s="95"/>
+      <c r="S19" s="95"/>
+      <c r="T19" s="95"/>
+      <c r="U19" s="95"/>
+      <c r="V19" s="95"/>
+      <c r="W19" s="95"/>
+      <c r="X19" s="95"/>
+      <c r="Y19" s="95"/>
+      <c r="Z19" s="95"/>
+      <c r="AA19" s="95"/>
+      <c r="AB19" s="95"/>
+      <c r="AC19" s="95"/>
+      <c r="AD19" s="95"/>
+      <c r="AE19" s="95"/>
+      <c r="AF19" s="95"/>
+      <c r="AG19" s="95"/>
+      <c r="AH19" s="95"/>
+      <c r="AI19" s="95"/>
+      <c r="AJ19" s="95"/>
+      <c r="AK19" s="95"/>
+      <c r="AL19" s="95"/>
+      <c r="AM19" s="95"/>
+      <c r="AN19" s="95"/>
+      <c r="AO19" s="95"/>
+      <c r="AP19" s="95"/>
+      <c r="AQ19" s="95"/>
+      <c r="AR19" s="95"/>
+      <c r="AS19" s="95"/>
+    </row>
+    <row r="20" spans="2:56">
+      <c r="B20" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="O20" s="96"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="96"/>
+      <c r="U20" s="96"/>
+      <c r="V20" s="96"/>
+      <c r="W20" s="96"/>
+      <c r="X20" s="96"/>
+      <c r="Y20" s="96"/>
+      <c r="Z20" s="96"/>
+      <c r="AA20" s="96"/>
+      <c r="AB20" s="96"/>
+      <c r="AC20" s="96"/>
+      <c r="AD20" s="96"/>
+      <c r="AE20" s="96"/>
+      <c r="AF20" s="96"/>
+      <c r="AG20" s="96"/>
+      <c r="AH20" s="96"/>
+      <c r="AI20" s="96"/>
+      <c r="AJ20" s="96"/>
+      <c r="AK20" s="96"/>
+      <c r="AL20" s="96"/>
+      <c r="AM20" s="96"/>
+      <c r="AN20" s="96"/>
+      <c r="AO20" s="96"/>
+      <c r="AP20" s="96"/>
+      <c r="AQ20" s="96"/>
+      <c r="AR20" s="96"/>
+      <c r="AS20" s="96"/>
+    </row>
+    <row r="21" spans="2:56">
+      <c r="B21" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21" s="97"/>
+      <c r="F21" s="97"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="97"/>
+      <c r="M21" s="97"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="97"/>
+      <c r="Q21" s="97"/>
+      <c r="R21" s="97"/>
+      <c r="S21" s="97"/>
+      <c r="T21" s="97"/>
+      <c r="U21" s="97"/>
+      <c r="V21" s="97"/>
+      <c r="W21" s="97"/>
+      <c r="X21" s="97"/>
+      <c r="Y21" s="97"/>
+      <c r="Z21" s="97"/>
+      <c r="AA21" s="97"/>
+      <c r="AB21" s="97"/>
+      <c r="AC21" s="97"/>
+      <c r="AD21" s="97"/>
+      <c r="AE21" s="97"/>
+      <c r="AF21" s="97"/>
+      <c r="AG21" s="97"/>
+      <c r="AH21" s="97"/>
+      <c r="AI21" s="97"/>
+      <c r="AJ21" s="97"/>
+      <c r="AK21" s="97"/>
+      <c r="AL21" s="97"/>
+      <c r="AM21" s="97"/>
+      <c r="AN21" s="97"/>
+      <c r="AO21" s="97"/>
+      <c r="AP21" s="97"/>
+      <c r="AQ21" s="97"/>
+      <c r="AR21" s="97"/>
+      <c r="AS21" s="97" t="s">
+        <v>253</v>
+      </c>
+      <c r="AT21" s="97"/>
+      <c r="AU21" s="97"/>
+      <c r="AV21" s="97"/>
+      <c r="AW21" s="97"/>
+      <c r="AX21" s="97"/>
+      <c r="AY21" s="97"/>
+      <c r="AZ21" s="97"/>
+      <c r="BA21" s="97"/>
+      <c r="BB21" s="97"/>
+      <c r="BC21" s="97"/>
+      <c r="BD21" s="97"/>
+    </row>
+    <row r="22" spans="2:56">
+      <c r="E22" s="97"/>
+      <c r="F22" s="97"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="97"/>
+      <c r="I22" s="97"/>
+      <c r="J22" s="97"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="97"/>
+      <c r="M22" s="97"/>
+      <c r="N22" s="97"/>
+      <c r="O22" s="97"/>
+      <c r="P22" s="97"/>
+      <c r="Q22" s="97"/>
+      <c r="R22" s="97"/>
+      <c r="S22" s="97"/>
+      <c r="T22" s="97"/>
+      <c r="U22" s="97"/>
+      <c r="V22" s="97"/>
+      <c r="W22" s="97"/>
+      <c r="X22" s="97"/>
+      <c r="Y22" s="97"/>
+      <c r="Z22" s="97"/>
+      <c r="AA22" s="97"/>
+      <c r="AB22" s="97"/>
+      <c r="AC22" s="97"/>
+      <c r="AD22" s="97"/>
+      <c r="AE22" s="97"/>
+      <c r="AF22" s="97"/>
+      <c r="AG22" s="97"/>
+      <c r="AH22" s="97"/>
+      <c r="AI22" s="97"/>
+      <c r="AJ22" s="97"/>
+      <c r="AK22" s="97"/>
+      <c r="AL22" s="97"/>
+      <c r="AM22" s="97"/>
+      <c r="AN22" s="97"/>
+      <c r="AO22" s="97"/>
+      <c r="AP22" s="98"/>
+      <c r="AQ22" s="98"/>
+      <c r="AR22" s="98"/>
+      <c r="AS22" s="98"/>
+      <c r="AT22" s="98"/>
+      <c r="AU22" s="98"/>
+      <c r="AV22" s="98"/>
+      <c r="AW22" s="98"/>
+      <c r="AX22" s="98"/>
+      <c r="AY22" s="99" t="s">
+        <v>254</v>
+      </c>
+      <c r="AZ22" s="97"/>
+      <c r="BA22" s="97"/>
+      <c r="BB22" s="97"/>
+      <c r="BC22" s="97"/>
+      <c r="BD22" s="97"/>
+    </row>
+    <row r="23" spans="2:56">
+      <c r="B23" s="100" t="s">
+        <v>255</v>
+      </c>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="101"/>
+      <c r="I23" s="101"/>
+      <c r="J23" s="101"/>
+      <c r="K23" s="101"/>
+      <c r="L23" s="101"/>
+      <c r="M23" s="101"/>
+      <c r="N23" s="101"/>
+      <c r="O23" s="101"/>
+      <c r="P23" s="101"/>
+    </row>
+    <row r="24" spans="2:56">
+      <c r="B24" s="102" t="s">
+        <v>256</v>
+      </c>
+      <c r="C24" s="101"/>
+      <c r="D24" s="101"/>
+      <c r="E24" s="101"/>
+      <c r="F24" s="101"/>
+      <c r="G24" s="101"/>
+      <c r="H24" s="101"/>
+      <c r="I24" s="101"/>
+      <c r="J24" s="101"/>
+      <c r="K24" s="101"/>
+      <c r="L24" s="101"/>
+      <c r="M24" s="101"/>
+      <c r="N24" s="101"/>
+      <c r="O24" s="101"/>
+      <c r="P24" s="101"/>
+      <c r="Q24" s="101"/>
+      <c r="R24" s="101"/>
+      <c r="S24" s="101"/>
+      <c r="T24" s="101"/>
+      <c r="U24" s="101"/>
+      <c r="V24" s="101"/>
+      <c r="W24" s="101"/>
+      <c r="X24" s="101"/>
+      <c r="Y24" s="101"/>
+      <c r="Z24" s="101"/>
+    </row>
+    <row r="27" spans="2:56">
+      <c r="B27" s="91" t="s">
+        <v>257</v>
+      </c>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="91"/>
+      <c r="H27" s="91"/>
+      <c r="I27" s="92"/>
+      <c r="J27" s="92"/>
+      <c r="K27" s="92"/>
+      <c r="L27" s="92"/>
+      <c r="M27" s="92"/>
+      <c r="N27" s="92"/>
+      <c r="O27" s="92"/>
+      <c r="P27" s="92"/>
+      <c r="Q27" s="92"/>
+      <c r="R27" s="92"/>
+      <c r="S27" s="92"/>
+      <c r="T27" s="92"/>
+      <c r="U27" s="92"/>
+      <c r="V27" s="92"/>
+      <c r="W27" s="92"/>
+      <c r="X27" s="92"/>
+      <c r="Y27" s="92"/>
+      <c r="Z27" s="92"/>
+      <c r="AA27" s="92"/>
+      <c r="AB27" s="92"/>
+      <c r="AC27" s="92"/>
+      <c r="AD27" s="92"/>
+      <c r="AE27" s="92"/>
+      <c r="AF27" s="92"/>
+      <c r="AG27" s="92"/>
+      <c r="AH27" s="92"/>
+      <c r="AI27" s="92"/>
+      <c r="AJ27" s="92"/>
+      <c r="AK27" s="92"/>
+      <c r="AL27" s="92"/>
+      <c r="AM27" s="92"/>
+      <c r="AN27" s="92"/>
+      <c r="AO27" s="92"/>
+      <c r="AP27" s="92"/>
+      <c r="AQ27" s="92"/>
+      <c r="AR27" s="92"/>
+      <c r="AS27" s="92" t="s">
+        <v>258</v>
+      </c>
+      <c r="AT27" s="92"/>
+      <c r="AU27" s="92"/>
+      <c r="AV27" s="92"/>
+      <c r="AW27" s="92"/>
+      <c r="AX27" s="92"/>
+      <c r="AY27" s="92"/>
+      <c r="AZ27" s="92"/>
+      <c r="BA27" s="92"/>
+      <c r="BB27" s="92"/>
+      <c r="BC27" s="92"/>
+      <c r="BD27" s="92"/>
+    </row>
+    <row r="28" spans="2:56">
+      <c r="B28" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="94"/>
+      <c r="J28" s="94"/>
+      <c r="K28" s="94"/>
+      <c r="L28" s="94"/>
+      <c r="M28" s="94"/>
+      <c r="N28" s="94"/>
+      <c r="O28" s="94"/>
+      <c r="P28" s="94"/>
+      <c r="Q28" s="94"/>
+      <c r="R28" s="94"/>
+      <c r="S28" s="94"/>
+      <c r="T28" s="94"/>
+      <c r="U28" s="94"/>
+      <c r="V28" s="94"/>
+      <c r="W28" s="94"/>
+      <c r="X28" s="94"/>
+      <c r="Y28" s="94"/>
+      <c r="Z28" s="94"/>
+      <c r="AA28" s="94"/>
+      <c r="AB28" s="94"/>
+      <c r="AC28" s="94"/>
+      <c r="AD28" s="94"/>
+      <c r="AE28" s="94"/>
+      <c r="AF28" s="94"/>
+      <c r="AG28" s="94"/>
+      <c r="AH28" s="94"/>
+      <c r="AI28" s="94"/>
+      <c r="AJ28" s="94"/>
+      <c r="AK28" s="94"/>
+      <c r="AL28" s="94"/>
+      <c r="AM28" s="94"/>
+      <c r="AN28" s="94"/>
+      <c r="AO28" s="94"/>
+      <c r="AP28" s="94"/>
+      <c r="AQ28" s="94"/>
+      <c r="AR28" s="94"/>
+      <c r="AS28" s="94"/>
+    </row>
+    <row r="29" spans="2:56">
+      <c r="B29" s="93" t="s">
+        <v>250</v>
+      </c>
+      <c r="O29" s="95"/>
+      <c r="P29" s="95"/>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="95"/>
+      <c r="S29" s="95"/>
+      <c r="T29" s="95"/>
+      <c r="U29" s="95"/>
+      <c r="V29" s="95"/>
+      <c r="W29" s="95"/>
+      <c r="X29" s="95"/>
+      <c r="Y29" s="95"/>
+      <c r="Z29" s="95"/>
+      <c r="AA29" s="95"/>
+      <c r="AB29" s="95"/>
+      <c r="AC29" s="95"/>
+      <c r="AD29" s="95"/>
+      <c r="AE29" s="95"/>
+      <c r="AF29" s="95"/>
+      <c r="AG29" s="95"/>
+      <c r="AH29" s="95"/>
+      <c r="AI29" s="95"/>
+      <c r="AJ29" s="95"/>
+      <c r="AK29" s="95"/>
+      <c r="AL29" s="95"/>
+      <c r="AM29" s="95"/>
+      <c r="AN29" s="95"/>
+      <c r="AO29" s="95"/>
+      <c r="AP29" s="95"/>
+      <c r="AQ29" s="95"/>
+      <c r="AR29" s="95"/>
+      <c r="AS29" s="95"/>
+      <c r="AT29" s="95"/>
+      <c r="AU29" s="95"/>
+      <c r="AV29" s="95"/>
+      <c r="AW29" s="95"/>
+      <c r="AX29" s="95"/>
+    </row>
+    <row r="30" spans="2:56">
+      <c r="B30" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="O30" s="96"/>
+      <c r="P30" s="96"/>
+      <c r="Q30" s="96"/>
+      <c r="R30" s="96"/>
+      <c r="S30" s="96"/>
+      <c r="T30" s="96"/>
+      <c r="U30" s="96"/>
+      <c r="V30" s="96"/>
+      <c r="W30" s="96"/>
+      <c r="X30" s="96"/>
+      <c r="Y30" s="96"/>
+      <c r="Z30" s="96"/>
+      <c r="AA30" s="96"/>
+      <c r="AB30" s="96"/>
+      <c r="AC30" s="96"/>
+      <c r="AD30" s="96"/>
+      <c r="AE30" s="96"/>
+      <c r="AF30" s="96"/>
+      <c r="AG30" s="96"/>
+      <c r="AH30" s="96"/>
+      <c r="AI30" s="96"/>
+      <c r="AJ30" s="96"/>
+      <c r="AK30" s="96"/>
+      <c r="AL30" s="96"/>
+      <c r="AM30" s="96"/>
+      <c r="AN30" s="96"/>
+      <c r="AO30" s="96"/>
+      <c r="AP30" s="96"/>
+      <c r="AQ30" s="96"/>
+      <c r="AR30" s="96"/>
+      <c r="AS30" s="96"/>
+      <c r="AT30" s="96"/>
+      <c r="AU30" s="96"/>
+      <c r="AV30" s="96"/>
+      <c r="AW30" s="96"/>
+      <c r="AX30" s="96"/>
+    </row>
+    <row r="31" spans="2:56">
+      <c r="B31" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="E31" s="97"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="97"/>
+      <c r="I31" s="97"/>
+      <c r="J31" s="97"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="97"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="97"/>
+      <c r="Q31" s="97"/>
+      <c r="R31" s="97"/>
+      <c r="S31" s="97"/>
+      <c r="T31" s="97"/>
+      <c r="U31" s="97"/>
+      <c r="V31" s="97"/>
+      <c r="W31" s="97"/>
+      <c r="X31" s="97"/>
+      <c r="Y31" s="97"/>
+      <c r="Z31" s="97"/>
+      <c r="AA31" s="97"/>
+      <c r="AB31" s="97"/>
+      <c r="AC31" s="97"/>
+      <c r="AD31" s="97"/>
+      <c r="AE31" s="97"/>
+      <c r="AF31" s="97"/>
+      <c r="AG31" s="97"/>
+      <c r="AH31" s="97"/>
+      <c r="AI31" s="97"/>
+      <c r="AJ31" s="97"/>
+      <c r="AK31" s="97"/>
+      <c r="AL31" s="97"/>
+      <c r="AM31" s="97"/>
+      <c r="AN31" s="97"/>
+      <c r="AO31" s="97"/>
+      <c r="AP31" s="97"/>
+      <c r="AQ31" s="97"/>
+      <c r="AR31" s="97"/>
+      <c r="AS31" s="97"/>
+      <c r="AT31" s="97"/>
+      <c r="AU31" s="97"/>
+      <c r="AV31" s="97"/>
+      <c r="AW31" s="97"/>
+      <c r="AX31" s="97" t="s">
+        <v>259</v>
+      </c>
+      <c r="AY31" s="97"/>
+      <c r="AZ31" s="97"/>
+      <c r="BA31" s="97"/>
+      <c r="BB31" s="97"/>
+      <c r="BC31" s="97"/>
+      <c r="BD31" s="97"/>
+    </row>
+    <row r="32" spans="2:56">
+      <c r="E32" s="97"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="97"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="97"/>
+      <c r="M32" s="97"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="97"/>
+      <c r="Q32" s="97"/>
+      <c r="R32" s="97"/>
+      <c r="S32" s="97"/>
+      <c r="T32" s="97"/>
+      <c r="U32" s="97"/>
+      <c r="V32" s="97"/>
+      <c r="W32" s="97"/>
+      <c r="X32" s="97"/>
+      <c r="Y32" s="97"/>
+      <c r="Z32" s="97"/>
+      <c r="AA32" s="97"/>
+      <c r="AB32" s="97"/>
+      <c r="AC32" s="97"/>
+      <c r="AD32" s="97"/>
+      <c r="AE32" s="97"/>
+      <c r="AF32" s="98"/>
+      <c r="AG32" s="98"/>
+      <c r="AH32" s="98"/>
+      <c r="AI32" s="98"/>
+      <c r="AJ32" s="98"/>
+      <c r="AK32" s="98"/>
+      <c r="AL32" s="98"/>
+      <c r="AM32" s="98"/>
+      <c r="AN32" s="98"/>
+      <c r="AO32" s="98"/>
+      <c r="AP32" s="98"/>
+      <c r="AQ32" s="98"/>
+      <c r="AR32" s="98"/>
+      <c r="AS32" s="98"/>
+      <c r="AT32" s="98"/>
+      <c r="AU32" s="98"/>
+      <c r="AV32" s="98"/>
+      <c r="AW32" s="98"/>
+      <c r="AX32" s="98"/>
+      <c r="AY32" s="99" t="s">
+        <v>260</v>
+      </c>
+      <c r="AZ32" s="97"/>
+      <c r="BA32" s="97"/>
+      <c r="BB32" s="97"/>
+      <c r="BC32" s="97"/>
+      <c r="BD32" s="97"/>
+    </row>
+    <row r="34" spans="2:56">
+      <c r="B34" s="74" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="35" spans="2:56">
+      <c r="C35" s="75" t="s">
+        <v>262</v>
+      </c>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="76"/>
+      <c r="L35" s="77"/>
+      <c r="M35" s="75" t="s">
+        <v>263</v>
+      </c>
+      <c r="N35" s="76"/>
+      <c r="O35" s="76"/>
+      <c r="P35" s="76"/>
+      <c r="Q35" s="76"/>
+      <c r="R35" s="76"/>
+      <c r="S35" s="76"/>
+      <c r="T35" s="76"/>
+      <c r="U35" s="76"/>
+      <c r="V35" s="76"/>
+      <c r="W35" s="76"/>
+      <c r="X35" s="76"/>
+      <c r="Y35" s="76"/>
+      <c r="Z35" s="76"/>
+      <c r="AA35" s="76"/>
+      <c r="AB35" s="76"/>
+      <c r="AC35" s="76"/>
+      <c r="AD35" s="76"/>
+      <c r="AE35" s="76"/>
+      <c r="AF35" s="76"/>
+      <c r="AG35" s="76"/>
+      <c r="AH35" s="77"/>
+    </row>
+    <row r="36" spans="2:56">
+      <c r="C36" s="78" t="s">
+        <v>235</v>
+      </c>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
+      <c r="J36" s="79"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="80"/>
+      <c r="M36" s="78" t="s">
+        <v>236</v>
+      </c>
+      <c r="N36" s="79"/>
+      <c r="O36" s="79"/>
+      <c r="P36" s="79"/>
+      <c r="Q36" s="79"/>
+      <c r="R36" s="79"/>
+      <c r="S36" s="79"/>
+      <c r="T36" s="79"/>
+      <c r="U36" s="79"/>
+      <c r="V36" s="79"/>
+      <c r="W36" s="79"/>
+      <c r="X36" s="79"/>
+      <c r="Y36" s="79"/>
+      <c r="Z36" s="79"/>
+      <c r="AA36" s="79"/>
+      <c r="AB36" s="79"/>
+      <c r="AC36" s="79"/>
+      <c r="AD36" s="79"/>
+      <c r="AE36" s="79"/>
+      <c r="AF36" s="79"/>
+      <c r="AG36" s="79"/>
+      <c r="AH36" s="80"/>
+    </row>
+    <row r="37" spans="2:56">
+      <c r="C37" s="75" t="s">
+        <v>264</v>
+      </c>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+      <c r="I37" s="76"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="77"/>
+      <c r="M37" s="75" t="s">
+        <v>265</v>
+      </c>
+      <c r="N37" s="76"/>
+      <c r="O37" s="76"/>
+      <c r="P37" s="76"/>
+      <c r="Q37" s="76"/>
+      <c r="R37" s="76"/>
+      <c r="S37" s="76"/>
+      <c r="T37" s="76"/>
+      <c r="U37" s="76"/>
+      <c r="V37" s="76"/>
+      <c r="W37" s="76"/>
+      <c r="X37" s="76"/>
+      <c r="Y37" s="76"/>
+      <c r="Z37" s="76"/>
+      <c r="AA37" s="76"/>
+      <c r="AB37" s="76"/>
+      <c r="AC37" s="76"/>
+      <c r="AD37" s="76"/>
+      <c r="AE37" s="76"/>
+      <c r="AF37" s="76"/>
+      <c r="AG37" s="76"/>
+      <c r="AH37" s="77"/>
+    </row>
+    <row r="38" spans="2:56">
+      <c r="C38" s="78"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="79"/>
+      <c r="F38" s="79"/>
+      <c r="G38" s="79"/>
+      <c r="H38" s="79"/>
+      <c r="I38" s="79"/>
+      <c r="J38" s="79"/>
+      <c r="K38" s="79"/>
+      <c r="L38" s="80"/>
+      <c r="M38" s="78" t="s">
+        <v>266</v>
+      </c>
+      <c r="N38" s="79"/>
+      <c r="O38" s="79"/>
+      <c r="P38" s="79"/>
+      <c r="Q38" s="79"/>
+      <c r="R38" s="79"/>
+      <c r="S38" s="79"/>
+      <c r="T38" s="79"/>
+      <c r="U38" s="79"/>
+      <c r="V38" s="79"/>
+      <c r="W38" s="79"/>
+      <c r="X38" s="79"/>
+      <c r="Y38" s="79"/>
+      <c r="Z38" s="79"/>
+      <c r="AA38" s="79"/>
+      <c r="AB38" s="79"/>
+      <c r="AC38" s="79"/>
+      <c r="AD38" s="79"/>
+      <c r="AE38" s="79"/>
+      <c r="AF38" s="79"/>
+      <c r="AG38" s="79"/>
+      <c r="AH38" s="80"/>
+    </row>
+    <row r="40" spans="2:56" ht="23.25">
+      <c r="B40" s="81" t="s">
+        <v>267</v>
+      </c>
+      <c r="C40" s="82"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="82"/>
+      <c r="F40" s="82"/>
+      <c r="G40" s="82"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
+      <c r="K40" s="82"/>
+      <c r="L40" s="82"/>
+      <c r="M40" s="82"/>
+      <c r="N40" s="82"/>
+      <c r="O40" s="82"/>
+      <c r="P40" s="82"/>
+      <c r="Q40" s="82"/>
+      <c r="R40" s="82"/>
+      <c r="S40" s="82"/>
+      <c r="T40" s="82"/>
+      <c r="U40" s="82"/>
+      <c r="V40" s="82"/>
+      <c r="W40" s="82"/>
+      <c r="X40" s="82"/>
+      <c r="Y40" s="82"/>
+      <c r="Z40" s="82"/>
+      <c r="AA40" s="82"/>
+      <c r="AB40" s="82"/>
+      <c r="AC40" s="82"/>
+      <c r="AD40" s="82"/>
+      <c r="AE40" s="82"/>
+      <c r="AF40" s="82"/>
+      <c r="AG40" s="82"/>
+      <c r="AH40" s="82"/>
+      <c r="AI40" s="82"/>
+      <c r="AJ40" s="82"/>
+      <c r="AK40" s="82"/>
+      <c r="AL40" s="82"/>
+      <c r="AM40" s="82"/>
+      <c r="AN40" s="82"/>
+      <c r="AO40" s="82"/>
+      <c r="AP40" s="82"/>
+      <c r="AQ40" s="82"/>
+      <c r="AR40" s="82"/>
+      <c r="AS40" s="82"/>
+      <c r="AT40" s="82"/>
+      <c r="AU40" s="82"/>
+      <c r="AV40" s="82"/>
+      <c r="AW40" s="82"/>
+      <c r="AX40" s="82"/>
+      <c r="AY40" s="82"/>
+    </row>
+    <row r="41" spans="2:56">
+      <c r="B41" s="88" t="s">
+        <v>246</v>
+      </c>
+      <c r="C41" s="89">
+        <v>18</v>
+      </c>
+      <c r="D41" s="89">
+        <v>19</v>
+      </c>
+      <c r="E41" s="89">
+        <v>20</v>
+      </c>
+      <c r="F41" s="89">
+        <v>21</v>
+      </c>
+      <c r="G41" s="89">
+        <v>22</v>
+      </c>
+      <c r="H41" s="89">
+        <v>23</v>
+      </c>
+      <c r="I41" s="89">
+        <v>24</v>
+      </c>
+      <c r="J41" s="89">
+        <v>25</v>
+      </c>
+      <c r="K41" s="89">
+        <v>26</v>
+      </c>
+      <c r="L41" s="89">
+        <v>27</v>
+      </c>
+      <c r="M41" s="89">
+        <v>28</v>
+      </c>
+      <c r="N41" s="89">
+        <v>29</v>
+      </c>
+      <c r="O41" s="89">
+        <v>30</v>
+      </c>
+      <c r="P41" s="89">
+        <v>31</v>
+      </c>
+      <c r="Q41" s="89">
+        <v>32</v>
+      </c>
+      <c r="R41" s="89">
+        <v>33</v>
+      </c>
+      <c r="S41" s="89">
+        <v>34</v>
+      </c>
+      <c r="T41" s="89">
+        <v>35</v>
+      </c>
+      <c r="U41" s="89">
+        <v>36</v>
+      </c>
+      <c r="V41" s="89">
+        <v>37</v>
+      </c>
+      <c r="W41" s="89">
+        <v>38</v>
+      </c>
+      <c r="X41" s="89">
+        <v>39</v>
+      </c>
+      <c r="Y41" s="89">
+        <v>40</v>
+      </c>
+      <c r="Z41" s="89">
+        <v>41</v>
+      </c>
+      <c r="AA41" s="89">
+        <v>42</v>
+      </c>
+      <c r="AB41" s="89">
+        <v>43</v>
+      </c>
+      <c r="AC41" s="89">
+        <v>44</v>
+      </c>
+      <c r="AD41" s="89">
+        <v>45</v>
+      </c>
+      <c r="AE41" s="89">
+        <v>46</v>
+      </c>
+      <c r="AF41" s="89">
+        <v>47</v>
+      </c>
+      <c r="AG41" s="89">
+        <v>48</v>
+      </c>
+      <c r="AH41" s="89">
+        <v>49</v>
+      </c>
+      <c r="AI41" s="89">
+        <v>50</v>
+      </c>
+      <c r="AJ41" s="89">
+        <v>51</v>
+      </c>
+      <c r="AK41" s="89">
+        <v>52</v>
+      </c>
+      <c r="AL41" s="89">
+        <v>53</v>
+      </c>
+      <c r="AM41" s="89">
+        <v>54</v>
+      </c>
+      <c r="AN41" s="89">
+        <v>55</v>
+      </c>
+      <c r="AO41" s="89">
+        <v>56</v>
+      </c>
+      <c r="AP41" s="89">
+        <v>57</v>
+      </c>
+      <c r="AQ41" s="89">
+        <v>58</v>
+      </c>
+      <c r="AR41" s="89">
+        <v>59</v>
+      </c>
+      <c r="AS41" s="89">
+        <v>60</v>
+      </c>
+      <c r="AT41" s="89">
+        <v>61</v>
+      </c>
+      <c r="AU41" s="89">
+        <v>62</v>
+      </c>
+      <c r="AV41" s="89">
+        <v>63</v>
+      </c>
+      <c r="AW41" s="89">
+        <v>64</v>
+      </c>
+      <c r="AX41" s="89">
+        <v>65</v>
+      </c>
+      <c r="AY41" s="89">
+        <v>66</v>
+      </c>
+      <c r="AZ41" s="89">
+        <v>67</v>
+      </c>
+      <c r="BA41" s="90"/>
+      <c r="BB41" s="90"/>
+      <c r="BC41" s="90"/>
+      <c r="BD41" s="90"/>
+    </row>
+    <row r="43" spans="2:56">
+      <c r="B43" s="91" t="s">
+        <v>268</v>
+      </c>
+      <c r="C43" s="91"/>
+      <c r="D43" s="91"/>
+      <c r="E43" s="91"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="91"/>
+      <c r="H43" s="91"/>
+      <c r="I43" s="92"/>
+      <c r="J43" s="92"/>
+      <c r="K43" s="92"/>
+      <c r="L43" s="92"/>
+      <c r="M43" s="92"/>
+      <c r="N43" s="92"/>
+      <c r="O43" s="92"/>
+      <c r="P43" s="92"/>
+      <c r="Q43" s="92"/>
+      <c r="R43" s="92"/>
+      <c r="S43" s="92"/>
+      <c r="T43" s="92"/>
+      <c r="U43" s="92"/>
+      <c r="V43" s="92"/>
+      <c r="W43" s="92"/>
+      <c r="X43" s="92"/>
+      <c r="Y43" s="92"/>
+      <c r="Z43" s="92"/>
+      <c r="AA43" s="92"/>
+      <c r="AB43" s="92"/>
+      <c r="AC43" s="92"/>
+      <c r="AD43" s="92"/>
+      <c r="AE43" s="92"/>
+      <c r="AF43" s="92"/>
+      <c r="AG43" s="92"/>
+      <c r="AH43" s="92"/>
+      <c r="AI43" s="92"/>
+      <c r="AJ43" s="92"/>
+      <c r="AK43" s="92"/>
+      <c r="AL43" s="92"/>
+      <c r="AM43" s="92"/>
+      <c r="AN43" s="92"/>
+      <c r="AO43" s="92"/>
+      <c r="AP43" s="92"/>
+      <c r="AQ43" s="92"/>
+      <c r="AR43" s="92"/>
+      <c r="AS43" s="92"/>
+      <c r="AT43" s="92"/>
+      <c r="AU43" s="92"/>
+      <c r="AV43" s="92"/>
+      <c r="AW43" s="92"/>
+      <c r="AX43" s="92" t="s">
+        <v>248</v>
+      </c>
+      <c r="AY43" s="92"/>
+      <c r="AZ43" s="92"/>
+      <c r="BA43" s="92"/>
+      <c r="BB43" s="92"/>
+      <c r="BC43" s="92"/>
+      <c r="BD43" s="92"/>
+    </row>
+    <row r="44" spans="2:56">
+      <c r="B44" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="E44" s="94"/>
+      <c r="F44" s="94"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="94"/>
+      <c r="I44" s="94"/>
+      <c r="J44" s="94"/>
+      <c r="K44" s="94"/>
+      <c r="L44" s="94"/>
+      <c r="M44" s="94"/>
+      <c r="N44" s="94"/>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94"/>
+      <c r="Q44" s="94"/>
+      <c r="R44" s="94"/>
+      <c r="S44" s="94"/>
+      <c r="T44" s="94"/>
+      <c r="U44" s="94"/>
+      <c r="V44" s="94"/>
+      <c r="W44" s="94"/>
+      <c r="X44" s="94"/>
+      <c r="Y44" s="94"/>
+      <c r="Z44" s="94"/>
+      <c r="AA44" s="94"/>
+      <c r="AB44" s="94"/>
+      <c r="AC44" s="94"/>
+      <c r="AD44" s="94"/>
+      <c r="AE44" s="94"/>
+      <c r="AF44" s="94"/>
+      <c r="AG44" s="94"/>
+      <c r="AH44" s="94"/>
+      <c r="AI44" s="94"/>
+      <c r="AJ44" s="94"/>
+      <c r="AK44" s="94"/>
+      <c r="AL44" s="94"/>
+      <c r="AM44" s="94"/>
+      <c r="AN44" s="94"/>
+      <c r="AO44" s="94"/>
+      <c r="AP44" s="94"/>
+      <c r="AQ44" s="94"/>
+      <c r="AR44" s="94"/>
+      <c r="AS44" s="94"/>
+      <c r="AT44" s="94"/>
+      <c r="AU44" s="94"/>
+      <c r="AV44" s="94"/>
+      <c r="AW44" s="94"/>
+      <c r="AX44" s="94"/>
+    </row>
+    <row r="45" spans="2:56">
+      <c r="B45" s="93" t="s">
+        <v>269</v>
+      </c>
+      <c r="O45" s="95"/>
+      <c r="P45" s="95"/>
+      <c r="Q45" s="95"/>
+      <c r="R45" s="95"/>
+      <c r="S45" s="95"/>
+      <c r="T45" s="95"/>
+      <c r="U45" s="95"/>
+      <c r="V45" s="95"/>
+      <c r="W45" s="95"/>
+      <c r="X45" s="95"/>
+      <c r="Y45" s="95"/>
+      <c r="Z45" s="95"/>
+      <c r="AA45" s="95"/>
+      <c r="AB45" s="95"/>
+      <c r="AC45" s="95"/>
+      <c r="AD45" s="95"/>
+      <c r="AE45" s="95"/>
+      <c r="AF45" s="95"/>
+      <c r="AG45" s="95"/>
+      <c r="AH45" s="95"/>
+      <c r="AI45" s="95"/>
+      <c r="AJ45" s="95"/>
+      <c r="AK45" s="95"/>
+      <c r="AL45" s="95"/>
+      <c r="AM45" s="95"/>
+      <c r="AN45" s="95"/>
+      <c r="AO45" s="95"/>
+      <c r="AP45" s="95"/>
+      <c r="AQ45" s="95"/>
+      <c r="AR45" s="95"/>
+      <c r="AS45" s="95"/>
+    </row>
+    <row r="46" spans="2:56">
+      <c r="B46" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="O46" s="96"/>
+      <c r="P46" s="96"/>
+      <c r="Q46" s="96"/>
+      <c r="R46" s="96"/>
+      <c r="S46" s="96"/>
+      <c r="T46" s="96"/>
+      <c r="U46" s="96"/>
+      <c r="V46" s="96"/>
+      <c r="W46" s="96"/>
+      <c r="X46" s="96"/>
+      <c r="Y46" s="96"/>
+      <c r="Z46" s="96"/>
+      <c r="AA46" s="96"/>
+      <c r="AB46" s="96"/>
+      <c r="AC46" s="96"/>
+      <c r="AD46" s="96"/>
+      <c r="AE46" s="96"/>
+      <c r="AF46" s="96"/>
+      <c r="AG46" s="96"/>
+      <c r="AH46" s="96"/>
+      <c r="AI46" s="96"/>
+      <c r="AJ46" s="96"/>
+      <c r="AK46" s="96"/>
+      <c r="AL46" s="96"/>
+      <c r="AM46" s="96"/>
+      <c r="AN46" s="96"/>
+      <c r="AO46" s="96"/>
+      <c r="AP46" s="96"/>
+      <c r="AQ46" s="96"/>
+      <c r="AR46" s="96"/>
+      <c r="AS46" s="96"/>
+    </row>
+    <row r="47" spans="2:56">
+      <c r="B47" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="E47" s="97"/>
+      <c r="F47" s="97"/>
+      <c r="G47" s="97"/>
+      <c r="H47" s="97"/>
+      <c r="I47" s="97"/>
+      <c r="J47" s="97"/>
+      <c r="K47" s="97"/>
+      <c r="L47" s="97"/>
+      <c r="M47" s="97"/>
+      <c r="N47" s="97"/>
+      <c r="O47" s="97"/>
+      <c r="P47" s="97"/>
+      <c r="Q47" s="97"/>
+      <c r="R47" s="97"/>
+      <c r="S47" s="97"/>
+      <c r="T47" s="97"/>
+      <c r="U47" s="97"/>
+      <c r="V47" s="97"/>
+      <c r="W47" s="97"/>
+      <c r="X47" s="97"/>
+      <c r="Y47" s="97"/>
+      <c r="Z47" s="97"/>
+      <c r="AA47" s="97"/>
+      <c r="AB47" s="97"/>
+      <c r="AC47" s="97"/>
+      <c r="AD47" s="97"/>
+      <c r="AE47" s="97"/>
+      <c r="AF47" s="97"/>
+      <c r="AG47" s="97"/>
+      <c r="AH47" s="97"/>
+      <c r="AI47" s="97"/>
+      <c r="AJ47" s="97"/>
+      <c r="AK47" s="97"/>
+      <c r="AL47" s="97"/>
+      <c r="AM47" s="97"/>
+      <c r="AN47" s="97"/>
+      <c r="AO47" s="97"/>
+      <c r="AP47" s="97"/>
+      <c r="AQ47" s="97"/>
+      <c r="AR47" s="97"/>
+      <c r="AS47" s="97" t="s">
+        <v>270</v>
+      </c>
+      <c r="AT47" s="97"/>
+      <c r="AU47" s="97"/>
+      <c r="AV47" s="97"/>
+      <c r="AW47" s="97"/>
+      <c r="AX47" s="97"/>
+      <c r="AY47" s="97"/>
+      <c r="AZ47" s="97"/>
+      <c r="BA47" s="97"/>
+      <c r="BB47" s="97"/>
+      <c r="BC47" s="97"/>
+      <c r="BD47" s="97"/>
+    </row>
+    <row r="48" spans="2:56">
+      <c r="E48" s="97"/>
+      <c r="F48" s="97"/>
+      <c r="G48" s="97"/>
+      <c r="H48" s="97"/>
+      <c r="I48" s="97"/>
+      <c r="J48" s="97"/>
+      <c r="K48" s="97"/>
+      <c r="L48" s="97"/>
+      <c r="M48" s="97"/>
+      <c r="N48" s="97"/>
+      <c r="O48" s="97"/>
+      <c r="P48" s="97"/>
+      <c r="Q48" s="97"/>
+      <c r="R48" s="97"/>
+      <c r="S48" s="97"/>
+      <c r="T48" s="97"/>
+      <c r="U48" s="97"/>
+      <c r="V48" s="97"/>
+      <c r="W48" s="97"/>
+      <c r="X48" s="97"/>
+      <c r="Y48" s="97"/>
+      <c r="Z48" s="97"/>
+      <c r="AA48" s="97"/>
+      <c r="AB48" s="97"/>
+      <c r="AC48" s="97"/>
+      <c r="AD48" s="97"/>
+      <c r="AE48" s="97"/>
+      <c r="AF48" s="97"/>
+      <c r="AG48" s="97"/>
+      <c r="AH48" s="97"/>
+      <c r="AI48" s="97"/>
+      <c r="AJ48" s="97"/>
+      <c r="AK48" s="97"/>
+      <c r="AL48" s="97"/>
+      <c r="AM48" s="97"/>
+      <c r="AN48" s="97"/>
+      <c r="AO48" s="97"/>
+      <c r="AU48" s="98"/>
+      <c r="AV48" s="98"/>
+      <c r="AW48" s="98"/>
+      <c r="AX48" s="98"/>
+      <c r="AY48" s="99" t="s">
+        <v>271</v>
+      </c>
+      <c r="AZ48" s="97"/>
+      <c r="BA48" s="97"/>
+      <c r="BB48" s="97"/>
+      <c r="BC48" s="97"/>
+      <c r="BD48" s="97"/>
+    </row>
+    <row r="49" spans="2:56">
+      <c r="B49" s="100" t="s">
+        <v>255</v>
+      </c>
+      <c r="C49" s="101"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="101"/>
+      <c r="F49" s="101"/>
+      <c r="G49" s="101"/>
+      <c r="H49" s="101"/>
+      <c r="I49" s="101"/>
+      <c r="J49" s="101"/>
+      <c r="K49" s="101"/>
+      <c r="L49" s="101"/>
+      <c r="M49" s="101"/>
+      <c r="N49" s="101"/>
+      <c r="O49" s="101"/>
+      <c r="P49" s="101"/>
+    </row>
+    <row r="50" spans="2:56">
+      <c r="B50" s="102" t="s">
+        <v>272</v>
+      </c>
+      <c r="C50" s="101"/>
+      <c r="D50" s="101"/>
+      <c r="E50" s="101"/>
+      <c r="F50" s="101"/>
+      <c r="G50" s="101"/>
+      <c r="H50" s="101"/>
+      <c r="I50" s="101"/>
+      <c r="J50" s="101"/>
+      <c r="K50" s="101"/>
+      <c r="L50" s="101"/>
+      <c r="M50" s="101"/>
+      <c r="N50" s="101"/>
+      <c r="O50" s="101"/>
+      <c r="P50" s="101"/>
+      <c r="Q50" s="101"/>
+      <c r="R50" s="101"/>
+      <c r="S50" s="101"/>
+      <c r="T50" s="101"/>
+      <c r="U50" s="101"/>
+      <c r="V50" s="101"/>
+      <c r="W50" s="101"/>
+      <c r="X50" s="101"/>
+      <c r="Y50" s="101"/>
+      <c r="Z50" s="101"/>
+    </row>
+    <row r="51" spans="2:56">
+      <c r="B51" s="74" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="53" spans="2:56">
+      <c r="B53" s="91" t="s">
+        <v>274</v>
+      </c>
+      <c r="C53" s="91"/>
+      <c r="D53" s="91"/>
+      <c r="E53" s="91"/>
+      <c r="F53" s="91"/>
+      <c r="G53" s="91"/>
+      <c r="H53" s="91"/>
+      <c r="I53" s="92"/>
+      <c r="J53" s="92"/>
+      <c r="K53" s="92"/>
+      <c r="L53" s="92"/>
+      <c r="M53" s="92"/>
+      <c r="N53" s="92"/>
+      <c r="O53" s="92"/>
+      <c r="P53" s="92"/>
+      <c r="Q53" s="92"/>
+      <c r="R53" s="92"/>
+      <c r="S53" s="92"/>
+      <c r="T53" s="92"/>
+      <c r="U53" s="92"/>
+      <c r="V53" s="92"/>
+      <c r="W53" s="92"/>
+      <c r="X53" s="92"/>
+      <c r="Y53" s="92"/>
+      <c r="Z53" s="92"/>
+      <c r="AA53" s="92"/>
+      <c r="AB53" s="92"/>
+      <c r="AC53" s="92"/>
+      <c r="AD53" s="92"/>
+      <c r="AE53" s="92"/>
+      <c r="AF53" s="92"/>
+      <c r="AG53" s="92"/>
+      <c r="AH53" s="92"/>
+      <c r="AI53" s="92"/>
+      <c r="AJ53" s="92"/>
+      <c r="AK53" s="92"/>
+      <c r="AL53" s="92"/>
+      <c r="AM53" s="92"/>
+      <c r="AN53" s="92"/>
+      <c r="AO53" s="92"/>
+      <c r="AP53" s="92"/>
+      <c r="AQ53" s="92"/>
+      <c r="AR53" s="92"/>
+      <c r="AS53" s="92" t="s">
+        <v>258</v>
+      </c>
+      <c r="AT53" s="92"/>
+      <c r="AU53" s="92"/>
+      <c r="AV53" s="92"/>
+      <c r="AW53" s="92"/>
+      <c r="AX53" s="92"/>
+      <c r="AY53" s="92"/>
+      <c r="AZ53" s="92"/>
+      <c r="BA53" s="92"/>
+      <c r="BB53" s="92"/>
+      <c r="BC53" s="92"/>
+      <c r="BD53" s="92"/>
+    </row>
+    <row r="54" spans="2:56">
+      <c r="B54" s="93" t="s">
+        <v>249</v>
+      </c>
+      <c r="E54" s="94"/>
+      <c r="F54" s="94"/>
+      <c r="G54" s="94"/>
+      <c r="H54" s="94"/>
+      <c r="I54" s="94"/>
+      <c r="J54" s="94"/>
+      <c r="K54" s="94"/>
+      <c r="L54" s="94"/>
+      <c r="M54" s="94"/>
+      <c r="N54" s="94"/>
+      <c r="O54" s="94"/>
+      <c r="P54" s="94"/>
+      <c r="Q54" s="94"/>
+      <c r="R54" s="94"/>
+      <c r="S54" s="94"/>
+      <c r="T54" s="94"/>
+      <c r="U54" s="94"/>
+      <c r="V54" s="94"/>
+      <c r="W54" s="94"/>
+      <c r="X54" s="94"/>
+      <c r="Y54" s="94"/>
+      <c r="Z54" s="94"/>
+      <c r="AA54" s="94"/>
+      <c r="AB54" s="94"/>
+      <c r="AC54" s="94"/>
+      <c r="AD54" s="94"/>
+      <c r="AE54" s="94"/>
+      <c r="AF54" s="94"/>
+      <c r="AG54" s="94"/>
+      <c r="AH54" s="94"/>
+      <c r="AI54" s="94"/>
+      <c r="AJ54" s="94"/>
+      <c r="AK54" s="94"/>
+      <c r="AL54" s="94"/>
+      <c r="AM54" s="94"/>
+      <c r="AN54" s="94"/>
+      <c r="AO54" s="94"/>
+      <c r="AP54" s="94"/>
+      <c r="AQ54" s="94"/>
+      <c r="AR54" s="94"/>
+      <c r="AS54" s="94"/>
+    </row>
+    <row r="55" spans="2:56">
+      <c r="B55" s="93" t="s">
+        <v>269</v>
+      </c>
+      <c r="O55" s="95"/>
+      <c r="P55" s="95"/>
+      <c r="Q55" s="95"/>
+      <c r="R55" s="95"/>
+      <c r="S55" s="95"/>
+      <c r="T55" s="95"/>
+      <c r="U55" s="95"/>
+      <c r="V55" s="95"/>
+      <c r="W55" s="95"/>
+      <c r="X55" s="95"/>
+      <c r="Y55" s="95"/>
+      <c r="Z55" s="95"/>
+      <c r="AA55" s="95"/>
+      <c r="AB55" s="95"/>
+      <c r="AC55" s="95"/>
+      <c r="AD55" s="95"/>
+      <c r="AE55" s="95"/>
+      <c r="AF55" s="95"/>
+      <c r="AG55" s="95"/>
+      <c r="AH55" s="95"/>
+      <c r="AI55" s="95"/>
+      <c r="AJ55" s="95"/>
+      <c r="AK55" s="95"/>
+      <c r="AL55" s="95"/>
+      <c r="AM55" s="95"/>
+      <c r="AN55" s="95"/>
+      <c r="AO55" s="95"/>
+      <c r="AP55" s="95"/>
+      <c r="AQ55" s="95"/>
+      <c r="AR55" s="95"/>
+      <c r="AS55" s="95"/>
+      <c r="AT55" s="95"/>
+      <c r="AU55" s="95"/>
+      <c r="AV55" s="95"/>
+      <c r="AW55" s="95"/>
+      <c r="AX55" s="95"/>
+    </row>
+    <row r="56" spans="2:56">
+      <c r="B56" s="93" t="s">
+        <v>251</v>
+      </c>
+      <c r="O56" s="96"/>
+      <c r="P56" s="96"/>
+      <c r="Q56" s="96"/>
+      <c r="R56" s="96"/>
+      <c r="S56" s="96"/>
+      <c r="T56" s="96"/>
+      <c r="U56" s="96"/>
+      <c r="V56" s="96"/>
+      <c r="W56" s="96"/>
+      <c r="X56" s="96"/>
+      <c r="Y56" s="96"/>
+      <c r="Z56" s="96"/>
+      <c r="AA56" s="96"/>
+      <c r="AB56" s="96"/>
+      <c r="AC56" s="96"/>
+      <c r="AD56" s="96"/>
+      <c r="AE56" s="96"/>
+      <c r="AF56" s="96"/>
+      <c r="AG56" s="96"/>
+      <c r="AH56" s="96"/>
+      <c r="AI56" s="96"/>
+      <c r="AJ56" s="96"/>
+      <c r="AK56" s="96"/>
+      <c r="AL56" s="96"/>
+      <c r="AM56" s="96"/>
+      <c r="AN56" s="96"/>
+      <c r="AO56" s="96"/>
+      <c r="AP56" s="96"/>
+      <c r="AQ56" s="96"/>
+      <c r="AR56" s="96"/>
+      <c r="AS56" s="96"/>
+      <c r="AT56" s="96"/>
+      <c r="AU56" s="96"/>
+      <c r="AV56" s="96"/>
+      <c r="AW56" s="96"/>
+      <c r="AX56" s="96"/>
+    </row>
+    <row r="57" spans="2:56">
+      <c r="B57" s="93" t="s">
+        <v>252</v>
+      </c>
+      <c r="E57" s="97"/>
+      <c r="F57" s="97"/>
+      <c r="G57" s="97"/>
+      <c r="H57" s="97"/>
+      <c r="I57" s="97"/>
+      <c r="J57" s="97"/>
+      <c r="K57" s="97"/>
+      <c r="L57" s="97"/>
+      <c r="M57" s="97"/>
+      <c r="N57" s="97"/>
+      <c r="O57" s="97"/>
+      <c r="P57" s="97"/>
+      <c r="Q57" s="97"/>
+      <c r="R57" s="97"/>
+      <c r="S57" s="97"/>
+      <c r="T57" s="97"/>
+      <c r="U57" s="97"/>
+      <c r="V57" s="97"/>
+      <c r="W57" s="97"/>
+      <c r="X57" s="97"/>
+      <c r="Y57" s="97"/>
+      <c r="Z57" s="97"/>
+      <c r="AA57" s="97"/>
+      <c r="AB57" s="97"/>
+      <c r="AC57" s="97"/>
+      <c r="AD57" s="97"/>
+      <c r="AE57" s="97"/>
+      <c r="AF57" s="97"/>
+      <c r="AG57" s="97"/>
+      <c r="AH57" s="97"/>
+      <c r="AI57" s="97"/>
+      <c r="AJ57" s="97"/>
+      <c r="AK57" s="97"/>
+      <c r="AL57" s="97"/>
+      <c r="AM57" s="97"/>
+      <c r="AN57" s="97"/>
+      <c r="AO57" s="97"/>
+      <c r="AP57" s="97"/>
+      <c r="AQ57" s="97"/>
+      <c r="AR57" s="97"/>
+      <c r="AS57" s="97"/>
+      <c r="AT57" s="97"/>
+      <c r="AU57" s="97"/>
+      <c r="AV57" s="97"/>
+      <c r="AW57" s="97"/>
+      <c r="AX57" s="97" t="s">
+        <v>275</v>
+      </c>
+      <c r="AY57" s="97"/>
+      <c r="AZ57" s="97"/>
+      <c r="BA57" s="97"/>
+      <c r="BB57" s="97"/>
+      <c r="BC57" s="97"/>
+      <c r="BD57" s="97"/>
+    </row>
+    <row r="58" spans="2:56">
+      <c r="E58" s="97"/>
+      <c r="F58" s="97"/>
+      <c r="G58" s="97"/>
+      <c r="H58" s="97"/>
+      <c r="I58" s="97"/>
+      <c r="J58" s="97"/>
+      <c r="K58" s="97"/>
+      <c r="L58" s="97"/>
+      <c r="M58" s="97"/>
+      <c r="N58" s="97"/>
+      <c r="O58" s="97"/>
+      <c r="P58" s="97"/>
+      <c r="Q58" s="97"/>
+      <c r="R58" s="97"/>
+      <c r="S58" s="97"/>
+      <c r="T58" s="97"/>
+      <c r="U58" s="97"/>
+      <c r="V58" s="97"/>
+      <c r="W58" s="97"/>
+      <c r="X58" s="97"/>
+      <c r="Y58" s="97"/>
+      <c r="Z58" s="97"/>
+      <c r="AA58" s="97"/>
+      <c r="AB58" s="97"/>
+      <c r="AC58" s="97"/>
+      <c r="AU58" s="98"/>
+      <c r="AV58" s="98"/>
+      <c r="AW58" s="98"/>
+      <c r="AX58" s="98"/>
+      <c r="AY58" s="99" t="s">
+        <v>271</v>
+      </c>
+      <c r="AZ58" s="97"/>
+      <c r="BA58" s="97"/>
+      <c r="BB58" s="97"/>
+      <c r="BC58" s="97"/>
+      <c r="BD58" s="97"/>
+    </row>
+    <row r="59" spans="2:56">
+      <c r="B59" s="100" t="s">
+        <v>276</v>
+      </c>
+      <c r="C59" s="101"/>
+      <c r="D59" s="101"/>
+      <c r="E59" s="101"/>
+      <c r="F59" s="101"/>
+      <c r="G59" s="101"/>
+      <c r="H59" s="101"/>
+      <c r="I59" s="101"/>
+      <c r="J59" s="101"/>
+      <c r="K59" s="101"/>
+      <c r="L59" s="101"/>
+      <c r="M59" s="101"/>
+      <c r="N59" s="101"/>
+      <c r="O59" s="101"/>
+      <c r="P59" s="101"/>
+    </row>
+    <row r="60" spans="2:56">
+      <c r="B60" s="102" t="s">
+        <v>272</v>
+      </c>
+      <c r="C60" s="101"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="101"/>
+      <c r="F60" s="101"/>
+      <c r="G60" s="101"/>
+      <c r="H60" s="101"/>
+      <c r="I60" s="101"/>
+      <c r="J60" s="101"/>
+      <c r="K60" s="101"/>
+      <c r="L60" s="101"/>
+      <c r="M60" s="101"/>
+      <c r="N60" s="101"/>
+      <c r="O60" s="101"/>
+      <c r="P60" s="101"/>
+      <c r="Q60" s="101"/>
+      <c r="R60" s="101"/>
+      <c r="S60" s="101"/>
+      <c r="T60" s="101"/>
+      <c r="U60" s="101"/>
+      <c r="V60" s="101"/>
+      <c r="W60" s="101"/>
+      <c r="X60" s="101"/>
+      <c r="Y60" s="101"/>
+      <c r="Z60" s="101"/>
+    </row>
+    <row r="61" spans="2:56">
+      <c r="B61" s="74" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="63" spans="2:56">
+      <c r="B63" s="91" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="64" spans="2:56">
+      <c r="B64" s="103" t="s">
+        <v>278</v>
+      </c>
+      <c r="C64" s="101"/>
+      <c r="D64" s="101"/>
+      <c r="E64" s="101"/>
+      <c r="F64" s="101"/>
+      <c r="G64" s="101"/>
+      <c r="H64" s="101"/>
+      <c r="I64" s="101"/>
+      <c r="J64" s="101"/>
+      <c r="K64" s="101"/>
+      <c r="L64" s="101"/>
+      <c r="M64" s="101"/>
+      <c r="N64" s="101"/>
+      <c r="O64" s="101"/>
+      <c r="P64" s="101"/>
+      <c r="Q64" s="101"/>
+      <c r="R64" s="101"/>
+      <c r="S64" s="101"/>
+      <c r="T64" s="101"/>
+      <c r="U64" s="101"/>
+      <c r="V64" s="101"/>
+      <c r="W64" s="101"/>
+      <c r="X64" s="101"/>
+      <c r="Y64" s="101"/>
+      <c r="Z64" s="101"/>
+      <c r="AA64" s="101"/>
+      <c r="AB64" s="101"/>
+      <c r="AC64" s="101"/>
+      <c r="AD64" s="101"/>
+      <c r="AE64" s="101"/>
+      <c r="AF64" s="101"/>
+      <c r="AG64" s="101"/>
+      <c r="AH64" s="101"/>
+      <c r="AI64" s="101"/>
+      <c r="AJ64" s="101"/>
+      <c r="AK64" s="101"/>
+      <c r="AL64" s="101"/>
+      <c r="AM64" s="101"/>
+      <c r="AN64" s="101"/>
+      <c r="AO64" s="101"/>
+      <c r="AP64" s="101"/>
+      <c r="AQ64" s="101"/>
+      <c r="AR64" s="101"/>
+      <c r="AS64" s="101"/>
+      <c r="AT64" s="101"/>
+      <c r="AU64" s="101"/>
+      <c r="AV64" s="101"/>
+      <c r="AW64" s="101"/>
+      <c r="AX64" s="101"/>
+      <c r="AY64" s="101"/>
+    </row>
+    <row r="65" spans="2:51">
+      <c r="B65" s="101"/>
+      <c r="C65" s="101"/>
+      <c r="D65" s="101"/>
+      <c r="E65" s="101"/>
+      <c r="F65" s="101"/>
+      <c r="G65" s="101"/>
+      <c r="H65" s="101"/>
+      <c r="I65" s="101"/>
+      <c r="J65" s="101"/>
+      <c r="K65" s="101"/>
+      <c r="L65" s="101"/>
+      <c r="M65" s="101"/>
+      <c r="N65" s="101"/>
+      <c r="O65" s="101"/>
+      <c r="P65" s="101"/>
+      <c r="Q65" s="101"/>
+      <c r="R65" s="101"/>
+      <c r="S65" s="101"/>
+      <c r="T65" s="101"/>
+      <c r="U65" s="101"/>
+      <c r="V65" s="101"/>
+      <c r="W65" s="101"/>
+      <c r="X65" s="101"/>
+      <c r="Y65" s="101"/>
+      <c r="Z65" s="101"/>
+      <c r="AA65" s="101"/>
+      <c r="AB65" s="101"/>
+      <c r="AC65" s="101"/>
+      <c r="AD65" s="101"/>
+      <c r="AE65" s="101"/>
+      <c r="AF65" s="101"/>
+      <c r="AG65" s="101"/>
+      <c r="AH65" s="101"/>
+      <c r="AI65" s="101"/>
+      <c r="AJ65" s="101"/>
+      <c r="AK65" s="101"/>
+      <c r="AL65" s="101"/>
+      <c r="AM65" s="101"/>
+      <c r="AN65" s="101"/>
+      <c r="AO65" s="101"/>
+      <c r="AP65" s="101"/>
+      <c r="AQ65" s="101"/>
+      <c r="AR65" s="101"/>
+      <c r="AS65" s="101"/>
+      <c r="AT65" s="101"/>
+      <c r="AU65" s="101"/>
+      <c r="AV65" s="101"/>
+      <c r="AW65" s="101"/>
+      <c r="AX65" s="101"/>
+      <c r="AY65" s="101"/>
+    </row>
+    <row r="66" spans="2:51">
+      <c r="B66" s="101"/>
+      <c r="C66" s="101"/>
+      <c r="D66" s="101"/>
+      <c r="E66" s="101"/>
+      <c r="F66" s="101"/>
+      <c r="G66" s="101"/>
+      <c r="H66" s="101"/>
+      <c r="I66" s="101"/>
+      <c r="J66" s="101"/>
+      <c r="K66" s="101"/>
+      <c r="L66" s="101"/>
+      <c r="M66" s="101"/>
+      <c r="N66" s="101"/>
+      <c r="O66" s="101"/>
+      <c r="P66" s="101"/>
+      <c r="Q66" s="101"/>
+      <c r="R66" s="101"/>
+      <c r="S66" s="101"/>
+      <c r="T66" s="101"/>
+      <c r="U66" s="101"/>
+      <c r="V66" s="101"/>
+      <c r="W66" s="101"/>
+      <c r="X66" s="101"/>
+      <c r="Y66" s="101"/>
+      <c r="Z66" s="101"/>
+      <c r="AA66" s="101"/>
+      <c r="AB66" s="101"/>
+      <c r="AC66" s="101"/>
+      <c r="AD66" s="101"/>
+      <c r="AE66" s="101"/>
+      <c r="AF66" s="101"/>
+      <c r="AG66" s="101"/>
+      <c r="AH66" s="101"/>
+      <c r="AI66" s="101"/>
+      <c r="AJ66" s="101"/>
+      <c r="AK66" s="101"/>
+      <c r="AL66" s="101"/>
+      <c r="AM66" s="101"/>
+      <c r="AN66" s="101"/>
+      <c r="AO66" s="101"/>
+      <c r="AP66" s="101"/>
+      <c r="AQ66" s="101"/>
+      <c r="AR66" s="101"/>
+      <c r="AS66" s="101"/>
+      <c r="AT66" s="101"/>
+      <c r="AU66" s="101"/>
+      <c r="AV66" s="101"/>
+      <c r="AW66" s="101"/>
+      <c r="AX66" s="101"/>
+      <c r="AY66" s="101"/>
+    </row>
+    <row r="68" spans="2:51">
+      <c r="B68" s="91" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="69" spans="2:51">
+      <c r="B69" s="103" t="s">
+        <v>280</v>
+      </c>
+      <c r="C69" s="101"/>
+      <c r="D69" s="101"/>
+      <c r="E69" s="101"/>
+      <c r="F69" s="101"/>
+      <c r="G69" s="101"/>
+      <c r="H69" s="101"/>
+      <c r="I69" s="101"/>
+      <c r="J69" s="101"/>
+      <c r="K69" s="101"/>
+      <c r="L69" s="101"/>
+      <c r="M69" s="101"/>
+      <c r="N69" s="101"/>
+      <c r="O69" s="101"/>
+      <c r="P69" s="101"/>
+      <c r="Q69" s="101"/>
+      <c r="R69" s="101"/>
+      <c r="S69" s="101"/>
+      <c r="T69" s="101"/>
+      <c r="U69" s="101"/>
+      <c r="V69" s="101"/>
+      <c r="W69" s="101"/>
+      <c r="X69" s="101"/>
+      <c r="Y69" s="101"/>
+      <c r="Z69" s="101"/>
+      <c r="AA69" s="101"/>
+      <c r="AB69" s="101"/>
+      <c r="AC69" s="101"/>
+      <c r="AD69" s="101"/>
+      <c r="AE69" s="101"/>
+      <c r="AF69" s="101"/>
+      <c r="AG69" s="101"/>
+      <c r="AH69" s="101"/>
+      <c r="AI69" s="101"/>
+      <c r="AJ69" s="101"/>
+      <c r="AK69" s="101"/>
+      <c r="AL69" s="101"/>
+      <c r="AM69" s="101"/>
+      <c r="AN69" s="101"/>
+      <c r="AO69" s="101"/>
+      <c r="AP69" s="101"/>
+      <c r="AQ69" s="101"/>
+      <c r="AR69" s="101"/>
+      <c r="AS69" s="101"/>
+      <c r="AT69" s="101"/>
+      <c r="AU69" s="101"/>
+      <c r="AV69" s="101"/>
+      <c r="AW69" s="101"/>
+      <c r="AX69" s="101"/>
+      <c r="AY69" s="101"/>
+    </row>
+    <row r="70" spans="2:51">
+      <c r="B70" s="101"/>
+      <c r="C70" s="101"/>
+      <c r="D70" s="101"/>
+      <c r="E70" s="101"/>
+      <c r="F70" s="101"/>
+      <c r="G70" s="101"/>
+      <c r="H70" s="101"/>
+      <c r="I70" s="101"/>
+      <c r="J70" s="101"/>
+      <c r="K70" s="101"/>
+      <c r="L70" s="101"/>
+      <c r="M70" s="101"/>
+      <c r="N70" s="101"/>
+      <c r="O70" s="101"/>
+      <c r="P70" s="101"/>
+      <c r="Q70" s="101"/>
+      <c r="R70" s="101"/>
+      <c r="S70" s="101"/>
+      <c r="T70" s="101"/>
+      <c r="U70" s="101"/>
+      <c r="V70" s="101"/>
+      <c r="W70" s="101"/>
+      <c r="X70" s="101"/>
+      <c r="Y70" s="101"/>
+      <c r="Z70" s="101"/>
+      <c r="AA70" s="101"/>
+      <c r="AB70" s="101"/>
+      <c r="AC70" s="101"/>
+      <c r="AD70" s="101"/>
+      <c r="AE70" s="101"/>
+      <c r="AF70" s="101"/>
+      <c r="AG70" s="101"/>
+      <c r="AH70" s="101"/>
+      <c r="AI70" s="101"/>
+      <c r="AJ70" s="101"/>
+      <c r="AK70" s="101"/>
+      <c r="AL70" s="101"/>
+      <c r="AM70" s="101"/>
+      <c r="AN70" s="101"/>
+      <c r="AO70" s="101"/>
+      <c r="AP70" s="101"/>
+      <c r="AQ70" s="101"/>
+      <c r="AR70" s="101"/>
+      <c r="AS70" s="101"/>
+      <c r="AT70" s="101"/>
+      <c r="AU70" s="101"/>
+      <c r="AV70" s="101"/>
+      <c r="AW70" s="101"/>
+      <c r="AX70" s="101"/>
+      <c r="AY70" s="101"/>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="HjnSr6/z+DWbCE5dEQ8q0L9b0iou1MBSo9NDjlNZVF0ZAgwjx0HOwtNHcyl0X5HcqIkvYPCopGg1OBqrRdi6Xg==" saltValue="tITU+hQj6qHx1yeztZAbmg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="11">
+    <mergeCell ref="B50:Z50"/>
+    <mergeCell ref="B59:P59"/>
+    <mergeCell ref="B60:Z60"/>
+    <mergeCell ref="B64:AY66"/>
+    <mergeCell ref="B69:AY70"/>
+    <mergeCell ref="B12:AY12"/>
+    <mergeCell ref="B13:AY13"/>
+    <mergeCell ref="B23:P23"/>
+    <mergeCell ref="B24:Z24"/>
+    <mergeCell ref="B40:AY40"/>
+    <mergeCell ref="B49:P49"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="30" style="10" customWidth="1"/>
     <col min="2" max="2" width="22.625" style="10" customWidth="1"/>
@@ -2379,7 +5439,7 @@
     <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6">
       <c r="A1" s="67" t="s">
         <v>40</v>
       </c>
@@ -2389,7 +5449,7 @@
       <c r="E1" s="66"/>
       <c r="F1" s="66"/>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="18.75" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>41</v>
       </c>
@@ -2407,7 +5467,7 @@
       </c>
       <c r="F3" s="12"/>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="18.75" customHeight="1">
       <c r="A4" s="13" t="s">
         <v>45</v>
       </c>
@@ -2424,7 +5484,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1">
       <c r="A5" s="13" t="s">
         <v>48</v>
       </c>
@@ -2441,7 +5501,7 @@
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
     </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="18.75" customHeight="1">
       <c r="A6" s="13" t="s">
         <v>51</v>
       </c>
@@ -2458,7 +5518,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1">
       <c r="A7" s="13" t="s">
         <v>53</v>
       </c>
@@ -2475,7 +5535,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1">
       <c r="A8" s="13" t="s">
         <v>55</v>
       </c>
@@ -2492,7 +5552,7 @@
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1">
       <c r="A9" s="13" t="s">
         <v>57</v>
       </c>
@@ -2509,7 +5569,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1">
       <c r="A10" s="13" t="s">
         <v>59</v>
       </c>
@@ -2526,7 +5586,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1">
       <c r="A11" s="13" t="s">
         <v>62</v>
       </c>
@@ -2545,7 +5605,7 @@
       </c>
       <c r="F11" s="13"/>
     </row>
-    <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="37.5" customHeight="1">
       <c r="A12" s="13" t="s">
         <v>25</v>
       </c>
@@ -2562,7 +5622,7 @@
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>66</v>
       </c>
@@ -2581,7 +5641,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1">
       <c r="A14" s="13" t="s">
         <v>69</v>
       </c>
@@ -2602,7 +5662,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" ht="18.75" customHeight="1">
       <c r="A15" s="13" t="s">
         <v>72</v>
       </c>
@@ -2623,7 +5683,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" ht="18.75" customHeight="1">
       <c r="A16" s="10" t="s">
         <v>75</v>
       </c>
@@ -2634,7 +5694,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" ht="18.75" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>26</v>
       </c>
@@ -2642,8 +5702,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="18.75" customHeight="1"/>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1">
       <c r="A19" s="12" t="s">
         <v>79</v>
       </c>
@@ -2655,22 +5715,22 @@
       <c r="E19" s="66"/>
       <c r="F19" s="66"/>
     </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="18.75" customHeight="1">
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
       <c r="D20" s="66"/>
       <c r="E20" s="66"/>
       <c r="F20" s="66"/>
     </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="18.75" customHeight="1">
       <c r="B21" s="66"/>
       <c r="C21" s="66"/>
       <c r="D21" s="66"/>
       <c r="E21" s="66"/>
       <c r="F21" s="66"/>
     </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" ht="18.75" customHeight="1"/>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1">
       <c r="A23" s="65" t="s">
         <v>81</v>
       </c>
@@ -2678,7 +5738,7 @@
       <c r="C23" s="66"/>
       <c r="D23" s="66"/>
     </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" ht="18.75" customHeight="1">
       <c r="A24" s="13" t="s">
         <v>82</v>
       </c>
@@ -2688,7 +5748,7 @@
       <c r="C24" s="66"/>
       <c r="D24" s="66"/>
     </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" ht="18.75" customHeight="1">
       <c r="A25" s="13" t="s">
         <v>83</v>
       </c>
@@ -2698,7 +5758,7 @@
       <c r="C25" s="66"/>
       <c r="D25" s="66"/>
     </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" ht="18.75" customHeight="1">
       <c r="A26" s="13" t="s">
         <v>27</v>
       </c>
@@ -2708,7 +5768,7 @@
       <c r="C26" s="66"/>
       <c r="D26" s="66"/>
     </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="ifNBCZqiO8+mmYbAfzrWPolPVTHUv+Zsm6KmmW171D9RHCqIPBdvIGE9pu+fl3sU2jGKIoXL64H/EFud49HRHg==" saltValue="Ql9f02+LZ1pla8xJcjabWA==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="6">
@@ -2725,10 +5785,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="10" customWidth="1"/>
     <col min="2" max="2" width="13" style="10" customWidth="1"/>
@@ -2762,7 +5822,7 @@
     <col min="44" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="24" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:43" ht="24">
       <c r="A1" s="69" t="s">
         <v>86</v>
       </c>
@@ -2776,7 +5836,7 @@
       <c r="I1" s="69"/>
       <c r="J1" s="69"/>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:43">
       <c r="A2" s="11" t="s">
         <v>87</v>
       </c>
@@ -2786,7 +5846,7 @@
       </c>
       <c r="AN2" s="10"/>
     </row>
-    <row r="3" spans="1:43" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" ht="60" customHeight="1">
       <c r="A3" s="22" t="s">
         <v>89</v>
       </c>
@@ -2917,7 +5977,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:43" ht="18.75" customHeight="1">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -3257,7 +6317,7 @@
         <v>10452828</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:43" ht="18.75" customHeight="1">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -3586,7 +6646,7 @@
         <v>10493248</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:43" ht="18.75" customHeight="1">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -3915,7 +6975,7 @@
         <v>10533668</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:43" ht="18.75" customHeight="1">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -4244,7 +7304,7 @@
         <v>10574088</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:43" ht="18.75" customHeight="1">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -4573,7 +7633,7 @@
         <v>10614508</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:43" ht="18.75" customHeight="1">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -4902,7 +7962,7 @@
         <v>11000000</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:43" ht="18.75" customHeight="1">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -5231,7 +8291,7 @@
         <v>10695348</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:43" ht="18.75" customHeight="1">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -5560,7 +8620,7 @@
         <v>10728110</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:43" ht="18.75" customHeight="1">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -5889,7 +8949,7 @@
         <v>10758320</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:43" ht="18.75" customHeight="1">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -6218,16 +9278,16 @@
         <v>10788530</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:43">
       <c r="AJ14" s="11"/>
     </row>
-    <row r="15" spans="1:43" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:43" ht="19.5">
       <c r="A15" s="36" t="s">
         <v>117</v>
       </c>
       <c r="O15" s="37"/>
     </row>
-    <row r="16" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:43" ht="18.75" customHeight="1">
       <c r="A16" s="38" t="s">
         <v>118</v>
       </c>
@@ -6243,7 +9303,7 @@
       <c r="I16" s="40"/>
       <c r="J16" s="40"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10">
       <c r="B17" s="40"/>
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
@@ -6254,7 +9314,7 @@
       <c r="I17" s="40"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10">
       <c r="B18" s="40"/>
       <c r="C18" s="40"/>
       <c r="D18" s="40"/>
@@ -6265,7 +9325,7 @@
       <c r="I18" s="40"/>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10">
       <c r="A19" s="41" t="s">
         <v>120</v>
       </c>
@@ -6273,7 +9333,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10">
       <c r="A20" s="41" t="s">
         <v>196</v>
       </c>
@@ -6281,19 +9341,19 @@
         <v>194</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10">
       <c r="A21" s="41"/>
       <c r="C21" s="39" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10">
       <c r="A22" s="41"/>
       <c r="C22" s="39" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10">
       <c r="A23" s="41" t="s">
         <v>122</v>
       </c>
@@ -6301,7 +9361,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10">
       <c r="A24" s="41" t="s">
         <v>124</v>
       </c>
@@ -6309,7 +9369,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" ht="19.5">
       <c r="A25" s="41" t="s">
         <v>126</v>
       </c>
@@ -6334,13 +9394,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="18" style="10" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="10" bestFit="1" customWidth="1"/>
@@ -6360,17 +9420,17 @@
     <col min="23" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25">
       <c r="A1" s="10" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:25">
       <c r="A3" s="11" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:25">
       <c r="A4" s="43" t="s">
         <v>129</v>
       </c>
@@ -6378,7 +9438,7 @@
         <v>25689</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:25">
       <c r="A5" s="43" t="s">
         <v>130</v>
       </c>
@@ -6386,7 +9446,7 @@
         <v>32599</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25">
       <c r="A6" s="43" t="s">
         <v>131</v>
       </c>
@@ -6401,7 +9461,7 @@
         <v>65歳0ヶ月</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25">
       <c r="A7" s="43" t="s">
         <v>133</v>
       </c>
@@ -6410,7 +9470,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:25">
       <c r="A8" s="43" t="s">
         <v>122</v>
       </c>
@@ -6422,7 +9482,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:25">
       <c r="A9" s="43" t="s">
         <v>135</v>
       </c>
@@ -6430,7 +9490,7 @@
         <v>10000000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:25">
       <c r="A10" s="43" t="s">
         <v>124</v>
       </c>
@@ -6442,7 +9502,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:25">
       <c r="A11" s="43" t="s">
         <v>137</v>
       </c>
@@ -6457,7 +9517,7 @@
       <c r="S11" s="47"/>
       <c r="T11" s="47"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:25">
       <c r="A12" s="43" t="s">
         <v>139</v>
       </c>
@@ -6486,7 +9546,7 @@
       <c r="X12" s="47"/>
       <c r="Y12" s="47"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:25">
       <c r="A13" s="43" t="s">
         <v>143</v>
       </c>
@@ -6521,7 +9581,7 @@
       <c r="X13" s="47"/>
       <c r="Y13" s="47"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:25">
       <c r="A14" s="43" t="s">
         <v>150</v>
       </c>
@@ -6556,7 +9616,7 @@
       <c r="X14" s="47"/>
       <c r="Y14" s="47"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:25">
       <c r="A15" s="43" t="s">
         <v>108</v>
       </c>
@@ -6587,7 +9647,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:25">
       <c r="A16" s="43" t="s">
         <v>155</v>
       </c>
@@ -6619,7 +9679,7 @@
       <c r="X16" s="47"/>
       <c r="Y16" s="47"/>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:25">
       <c r="B17" s="34"/>
       <c r="N17" s="53"/>
       <c r="O17" s="54" t="s">
@@ -6643,7 +9703,7 @@
       <c r="X17" s="47"/>
       <c r="Y17" s="47"/>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:25">
       <c r="N18" s="48" t="s">
         <v>165</v>
       </c>
@@ -6668,7 +9728,7 @@
       <c r="X18" s="47"/>
       <c r="Y18" s="47"/>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:25">
       <c r="N19" s="47"/>
       <c r="O19" s="47"/>
       <c r="P19" s="47"/>
@@ -6689,7 +9749,7 @@
       <c r="X19" s="47"/>
       <c r="Y19" s="47"/>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:25">
       <c r="N20" s="47"/>
       <c r="O20" s="47"/>
       <c r="P20" s="47"/>
@@ -6710,7 +9770,7 @@
       <c r="X20" s="47"/>
       <c r="Y20" s="47"/>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:25">
       <c r="N21" s="47"/>
       <c r="O21" s="47"/>
       <c r="P21" s="47"/>
@@ -6719,57 +9779,57 @@
       <c r="X21" s="47"/>
       <c r="Y21" s="47"/>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:25">
       <c r="W22" s="47"/>
       <c r="X22" s="47"/>
       <c r="Y22" s="47"/>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:25">
       <c r="W23" s="47"/>
       <c r="X23" s="47"/>
       <c r="Y23" s="47"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:1">
       <c r="A33" s="11" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:1">
       <c r="A34" s="11" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:1">
       <c r="A35" s="55" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:1">
       <c r="A36" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:1">
       <c r="A37" s="55" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:1">
       <c r="A38" s="11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:1">
       <c r="A39" s="55" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:1">
       <c r="A40" s="11" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:1">
       <c r="A41" s="55" t="s">
         <v>177</v>
       </c>
@@ -6796,17 +9856,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="38" style="2" customWidth="1"/>
     <col min="2" max="2" width="42" style="2" customWidth="1"/>
     <col min="3" max="6" width="20" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="24">
       <c r="A1" s="70" t="s">
         <v>178</v>
       </c>
@@ -6814,7 +9874,7 @@
       <c r="C1" s="71"/>
       <c r="D1" s="71"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>179</v>
       </c>
@@ -6826,21 +9886,21 @@
       <c r="E3" s="71"/>
       <c r="F3" s="71"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6">
       <c r="B4" s="71"/>
       <c r="C4" s="71"/>
       <c r="D4" s="71"/>
       <c r="E4" s="71"/>
       <c r="F4" s="71"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6">
       <c r="B5" s="71"/>
       <c r="C5" s="71"/>
       <c r="D5" s="71"/>
       <c r="E5" s="71"/>
       <c r="F5" s="71"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
         <v>181</v>
       </c>
@@ -6850,17 +9910,17 @@
       <c r="C6" s="71"/>
       <c r="D6" s="71"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6">
       <c r="B7" s="71"/>
       <c r="C7" s="71"/>
       <c r="D7" s="71"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6">
       <c r="B8" s="71"/>
       <c r="C8" s="71"/>
       <c r="D8" s="71"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
         <v>183</v>
       </c>
@@ -6872,21 +9932,21 @@
       <c r="E9" s="71"/>
       <c r="F9" s="71"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6">
       <c r="B10" s="71"/>
       <c r="C10" s="71"/>
       <c r="D10" s="71"/>
       <c r="E10" s="71"/>
       <c r="F10" s="71"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6">
       <c r="B11" s="71"/>
       <c r="C11" s="71"/>
       <c r="D11" s="71"/>
       <c r="E11" s="71"/>
       <c r="F11" s="71"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
         <v>185</v>
       </c>
@@ -6896,21 +9956,21 @@
       <c r="E12" s="71"/>
       <c r="F12" s="71"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6">
       <c r="B13" s="71"/>
       <c r="C13" s="71"/>
       <c r="D13" s="71"/>
       <c r="E13" s="71"/>
       <c r="F13" s="71"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6">
       <c r="B14" s="71"/>
       <c r="C14" s="71"/>
       <c r="D14" s="71"/>
       <c r="E14" s="71"/>
       <c r="F14" s="71"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
         <v>186</v>
       </c>
@@ -6918,7 +9978,7 @@
       <c r="C16" s="71"/>
       <c r="D16" s="71"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>187</v>
       </c>
@@ -6928,7 +9988,7 @@
       <c r="C17" s="73"/>
       <c r="D17" s="73"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>188</v>
       </c>
@@ -6938,22 +9998,22 @@
       <c r="C18" s="73"/>
       <c r="D18" s="73"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4">
       <c r="A20"/>
       <c r="B20" s="9" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4">
       <c r="A21"/>
       <c r="B21"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4">
       <c r="A22"/>
       <c r="B22"/>
     </row>
@@ -6981,16 +10041,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
     <col min="2" max="3" width="12" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="56" t="s">
         <v>190</v>
       </c>
@@ -7001,7 +10061,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3">
       <c r="A2" s="58">
         <v>0</v>
       </c>
@@ -7012,7 +10072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3">
       <c r="A3" s="58">
         <v>1950000</v>
       </c>
@@ -7023,7 +10083,7 @@
         <v>97500</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3">
       <c r="A4" s="58">
         <v>3300000</v>
       </c>
@@ -7034,7 +10094,7 @@
         <v>427500</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3">
       <c r="A5" s="58">
         <v>6950000</v>
       </c>
@@ -7045,7 +10105,7 @@
         <v>636000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3">
       <c r="A6" s="58">
         <v>9000000</v>
       </c>
@@ -7056,7 +10116,7 @@
         <v>1536000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3">
       <c r="A7" s="58">
         <v>18000000</v>
       </c>
@@ -7067,7 +10127,7 @@
         <v>2796000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3">
       <c r="A8" s="58">
         <v>40000000</v>
       </c>

--- a/退職金_DC・DB_重複調整シミュレーション.xlsx
+++ b/退職金_DC・DB_重複調整シミュレーション.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\40_個人年金\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA9450F-0C9D-47F7-9413-372A510AD1DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCE2FD7-EFF2-44BA-B10D-B5DCB129DCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="xDy3cd6TjsApx1SYHegDGF3A84e1AD38me84/BeuVDCiF8QUyic1TygQQScbJfuh4omJj/k1OOWDR6319YaKYw==" workbookSaltValue="nU/5cJljJzN7UnsxmBLLvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -1915,18 +1915,18 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2004,7 +2004,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4447"/>
+                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4453"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2069,7 +2069,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4448"/>
+                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4454"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2134,7 +2134,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4449"/>
+                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4455"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -3100,112 +3100,112 @@
       </c>
     </row>
     <row r="12" spans="2:56" ht="23.25" x14ac:dyDescent="0.4">
-      <c r="B12" s="90" t="s">
+      <c r="B12" s="92" t="s">
         <v>237</v>
       </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="91"/>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="91"/>
-      <c r="K12" s="91"/>
-      <c r="L12" s="91"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="91"/>
-      <c r="O12" s="91"/>
-      <c r="P12" s="91"/>
-      <c r="Q12" s="91"/>
-      <c r="R12" s="91"/>
-      <c r="S12" s="91"/>
-      <c r="T12" s="91"/>
-      <c r="U12" s="91"/>
-      <c r="V12" s="91"/>
-      <c r="W12" s="91"/>
-      <c r="X12" s="91"/>
-      <c r="Y12" s="91"/>
-      <c r="Z12" s="91"/>
-      <c r="AA12" s="91"/>
-      <c r="AB12" s="91"/>
-      <c r="AC12" s="91"/>
-      <c r="AD12" s="91"/>
-      <c r="AE12" s="91"/>
-      <c r="AF12" s="91"/>
-      <c r="AG12" s="91"/>
-      <c r="AH12" s="91"/>
-      <c r="AI12" s="91"/>
-      <c r="AJ12" s="91"/>
-      <c r="AK12" s="91"/>
-      <c r="AL12" s="91"/>
-      <c r="AM12" s="91"/>
-      <c r="AN12" s="91"/>
-      <c r="AO12" s="91"/>
-      <c r="AP12" s="91"/>
-      <c r="AQ12" s="91"/>
-      <c r="AR12" s="91"/>
-      <c r="AS12" s="91"/>
-      <c r="AT12" s="91"/>
-      <c r="AU12" s="91"/>
-      <c r="AV12" s="91"/>
-      <c r="AW12" s="91"/>
-      <c r="AX12" s="91"/>
-      <c r="AY12" s="91"/>
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
+      <c r="P12" s="93"/>
+      <c r="Q12" s="93"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="93"/>
+      <c r="T12" s="93"/>
+      <c r="U12" s="93"/>
+      <c r="V12" s="93"/>
+      <c r="W12" s="93"/>
+      <c r="X12" s="93"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="93"/>
+      <c r="AB12" s="93"/>
+      <c r="AC12" s="93"/>
+      <c r="AD12" s="93"/>
+      <c r="AE12" s="93"/>
+      <c r="AF12" s="93"/>
+      <c r="AG12" s="93"/>
+      <c r="AH12" s="93"/>
+      <c r="AI12" s="93"/>
+      <c r="AJ12" s="93"/>
+      <c r="AK12" s="93"/>
+      <c r="AL12" s="93"/>
+      <c r="AM12" s="93"/>
+      <c r="AN12" s="93"/>
+      <c r="AO12" s="93"/>
+      <c r="AP12" s="93"/>
+      <c r="AQ12" s="93"/>
+      <c r="AR12" s="93"/>
+      <c r="AS12" s="93"/>
+      <c r="AT12" s="93"/>
+      <c r="AU12" s="93"/>
+      <c r="AV12" s="93"/>
+      <c r="AW12" s="93"/>
+      <c r="AX12" s="93"/>
+      <c r="AY12" s="93"/>
     </row>
     <row r="13" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="94" t="s">
         <v>238</v>
       </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="91"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="91"/>
-      <c r="K13" s="91"/>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="91"/>
-      <c r="O13" s="91"/>
-      <c r="P13" s="91"/>
-      <c r="Q13" s="91"/>
-      <c r="R13" s="91"/>
-      <c r="S13" s="91"/>
-      <c r="T13" s="91"/>
-      <c r="U13" s="91"/>
-      <c r="V13" s="91"/>
-      <c r="W13" s="91"/>
-      <c r="X13" s="91"/>
-      <c r="Y13" s="91"/>
-      <c r="Z13" s="91"/>
-      <c r="AA13" s="91"/>
-      <c r="AB13" s="91"/>
-      <c r="AC13" s="91"/>
-      <c r="AD13" s="91"/>
-      <c r="AE13" s="91"/>
-      <c r="AF13" s="91"/>
-      <c r="AG13" s="91"/>
-      <c r="AH13" s="91"/>
-      <c r="AI13" s="91"/>
-      <c r="AJ13" s="91"/>
-      <c r="AK13" s="91"/>
-      <c r="AL13" s="91"/>
-      <c r="AM13" s="91"/>
-      <c r="AN13" s="91"/>
-      <c r="AO13" s="91"/>
-      <c r="AP13" s="91"/>
-      <c r="AQ13" s="91"/>
-      <c r="AR13" s="91"/>
-      <c r="AS13" s="91"/>
-      <c r="AT13" s="91"/>
-      <c r="AU13" s="91"/>
-      <c r="AV13" s="91"/>
-      <c r="AW13" s="91"/>
-      <c r="AX13" s="91"/>
-      <c r="AY13" s="91"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="93"/>
+      <c r="O13" s="93"/>
+      <c r="P13" s="93"/>
+      <c r="Q13" s="93"/>
+      <c r="R13" s="93"/>
+      <c r="S13" s="93"/>
+      <c r="T13" s="93"/>
+      <c r="U13" s="93"/>
+      <c r="V13" s="93"/>
+      <c r="W13" s="93"/>
+      <c r="X13" s="93"/>
+      <c r="Y13" s="93"/>
+      <c r="Z13" s="93"/>
+      <c r="AA13" s="93"/>
+      <c r="AB13" s="93"/>
+      <c r="AC13" s="93"/>
+      <c r="AD13" s="93"/>
+      <c r="AE13" s="93"/>
+      <c r="AF13" s="93"/>
+      <c r="AG13" s="93"/>
+      <c r="AH13" s="93"/>
+      <c r="AI13" s="93"/>
+      <c r="AJ13" s="93"/>
+      <c r="AK13" s="93"/>
+      <c r="AL13" s="93"/>
+      <c r="AM13" s="93"/>
+      <c r="AN13" s="93"/>
+      <c r="AO13" s="93"/>
+      <c r="AP13" s="93"/>
+      <c r="AQ13" s="93"/>
+      <c r="AR13" s="93"/>
+      <c r="AS13" s="93"/>
+      <c r="AT13" s="93"/>
+      <c r="AU13" s="93"/>
+      <c r="AV13" s="93"/>
+      <c r="AW13" s="93"/>
+      <c r="AX13" s="93"/>
+      <c r="AY13" s="93"/>
     </row>
     <row r="14" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B14" s="68"/>
@@ -3724,7 +3724,7 @@
       <c r="BD22" s="81"/>
     </row>
     <row r="23" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B23" s="88" t="s">
+      <c r="B23" s="90" t="s">
         <v>251</v>
       </c>
       <c r="C23" s="89"/>
@@ -3743,7 +3743,7 @@
       <c r="P23" s="89"/>
     </row>
     <row r="24" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B24" s="93" t="s">
+      <c r="B24" s="88" t="s">
         <v>252</v>
       </c>
       <c r="C24" s="89"/>
@@ -4231,58 +4231,58 @@
       <c r="AH38" s="67"/>
     </row>
     <row r="40" spans="2:56" ht="23.25" x14ac:dyDescent="0.4">
-      <c r="B40" s="90" t="s">
+      <c r="B40" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="C40" s="91"/>
-      <c r="D40" s="91"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="91"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="91"/>
-      <c r="I40" s="91"/>
-      <c r="J40" s="91"/>
-      <c r="K40" s="91"/>
-      <c r="L40" s="91"/>
-      <c r="M40" s="91"/>
-      <c r="N40" s="91"/>
-      <c r="O40" s="91"/>
-      <c r="P40" s="91"/>
-      <c r="Q40" s="91"/>
-      <c r="R40" s="91"/>
-      <c r="S40" s="91"/>
-      <c r="T40" s="91"/>
-      <c r="U40" s="91"/>
-      <c r="V40" s="91"/>
-      <c r="W40" s="91"/>
-      <c r="X40" s="91"/>
-      <c r="Y40" s="91"/>
-      <c r="Z40" s="91"/>
-      <c r="AA40" s="91"/>
-      <c r="AB40" s="91"/>
-      <c r="AC40" s="91"/>
-      <c r="AD40" s="91"/>
-      <c r="AE40" s="91"/>
-      <c r="AF40" s="91"/>
-      <c r="AG40" s="91"/>
-      <c r="AH40" s="91"/>
-      <c r="AI40" s="91"/>
-      <c r="AJ40" s="91"/>
-      <c r="AK40" s="91"/>
-      <c r="AL40" s="91"/>
-      <c r="AM40" s="91"/>
-      <c r="AN40" s="91"/>
-      <c r="AO40" s="91"/>
-      <c r="AP40" s="91"/>
-      <c r="AQ40" s="91"/>
-      <c r="AR40" s="91"/>
-      <c r="AS40" s="91"/>
-      <c r="AT40" s="91"/>
-      <c r="AU40" s="91"/>
-      <c r="AV40" s="91"/>
-      <c r="AW40" s="91"/>
-      <c r="AX40" s="91"/>
-      <c r="AY40" s="91"/>
+      <c r="C40" s="93"/>
+      <c r="D40" s="93"/>
+      <c r="E40" s="93"/>
+      <c r="F40" s="93"/>
+      <c r="G40" s="93"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="93"/>
+      <c r="M40" s="93"/>
+      <c r="N40" s="93"/>
+      <c r="O40" s="93"/>
+      <c r="P40" s="93"/>
+      <c r="Q40" s="93"/>
+      <c r="R40" s="93"/>
+      <c r="S40" s="93"/>
+      <c r="T40" s="93"/>
+      <c r="U40" s="93"/>
+      <c r="V40" s="93"/>
+      <c r="W40" s="93"/>
+      <c r="X40" s="93"/>
+      <c r="Y40" s="93"/>
+      <c r="Z40" s="93"/>
+      <c r="AA40" s="93"/>
+      <c r="AB40" s="93"/>
+      <c r="AC40" s="93"/>
+      <c r="AD40" s="93"/>
+      <c r="AE40" s="93"/>
+      <c r="AF40" s="93"/>
+      <c r="AG40" s="93"/>
+      <c r="AH40" s="93"/>
+      <c r="AI40" s="93"/>
+      <c r="AJ40" s="93"/>
+      <c r="AK40" s="93"/>
+      <c r="AL40" s="93"/>
+      <c r="AM40" s="93"/>
+      <c r="AN40" s="93"/>
+      <c r="AO40" s="93"/>
+      <c r="AP40" s="93"/>
+      <c r="AQ40" s="93"/>
+      <c r="AR40" s="93"/>
+      <c r="AS40" s="93"/>
+      <c r="AT40" s="93"/>
+      <c r="AU40" s="93"/>
+      <c r="AV40" s="93"/>
+      <c r="AW40" s="93"/>
+      <c r="AX40" s="93"/>
+      <c r="AY40" s="93"/>
     </row>
     <row r="41" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B41" s="72" t="s">
@@ -4738,7 +4738,7 @@
       <c r="BD48" s="81"/>
     </row>
     <row r="49" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B49" s="88" t="s">
+      <c r="B49" s="90" t="s">
         <v>251</v>
       </c>
       <c r="C49" s="89"/>
@@ -4757,7 +4757,7 @@
       <c r="P49" s="89"/>
     </row>
     <row r="50" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B50" s="93" t="s">
+      <c r="B50" s="88" t="s">
         <v>268</v>
       </c>
       <c r="C50" s="89"/>
@@ -5078,7 +5078,7 @@
       <c r="BD58" s="81"/>
     </row>
     <row r="59" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B59" s="88" t="s">
+      <c r="B59" s="90" t="s">
         <v>272</v>
       </c>
       <c r="C59" s="89"/>
@@ -5097,7 +5097,7 @@
       <c r="P59" s="89"/>
     </row>
     <row r="60" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B60" s="93" t="s">
+      <c r="B60" s="88" t="s">
         <v>268</v>
       </c>
       <c r="C60" s="89"/>
@@ -5136,7 +5136,7 @@
       </c>
     </row>
     <row r="64" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B64" s="94" t="s">
+      <c r="B64" s="91" t="s">
         <v>274</v>
       </c>
       <c r="C64" s="89"/>
@@ -5299,7 +5299,7 @@
       </c>
     </row>
     <row r="69" spans="2:51" x14ac:dyDescent="0.4">
-      <c r="B69" s="94" t="s">
+      <c r="B69" s="91" t="s">
         <v>276</v>
       </c>
       <c r="C69" s="89"/>
@@ -5407,17 +5407,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="oRew7oK5RrebL3ikYbb5mrrqCwtYk96SN7lm2yyxRaPIrPICb7DS7sYEbupYaTok13XO6PM3C0vgC2TZ6/xVQA==" saltValue="3tduD31ZVtNoKEQtwr17xQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
-    <mergeCell ref="B50:Z50"/>
-    <mergeCell ref="B59:P59"/>
-    <mergeCell ref="B60:Z60"/>
-    <mergeCell ref="B64:AY66"/>
-    <mergeCell ref="B69:AY70"/>
     <mergeCell ref="B49:P49"/>
     <mergeCell ref="B12:AY12"/>
     <mergeCell ref="B13:AY13"/>
     <mergeCell ref="B23:P23"/>
     <mergeCell ref="B24:Z24"/>
     <mergeCell ref="B40:AY40"/>
+    <mergeCell ref="B50:Z50"/>
+    <mergeCell ref="B59:P59"/>
+    <mergeCell ref="B60:Z60"/>
+    <mergeCell ref="B64:AY66"/>
+    <mergeCell ref="B69:AY70"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/退職金_DC・DB_重複調整シミュレーション.xlsx
+++ b/退職金_DC・DB_重複調整シミュレーション.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\40_個人年金\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCE2FD7-EFF2-44BA-B10D-B5DCB129DCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F43D8E-F7D3-478B-B218-CA857ADF0C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="xDy3cd6TjsApx1SYHegDGF3A84e1AD38me84/BeuVDCiF8QUyic1TygQQScbJfuh4omJj/k1OOWDR6319YaKYw==" workbookSaltValue="nU/5cJljJzN7UnsxmBLLvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -1270,7 +1270,7 @@
     <numFmt numFmtId="180" formatCode="0&quot;年&quot;"/>
     <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1899,6 +1899,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
@@ -1915,18 +1919,18 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1941,10 +1945,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2004,7 +2004,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4453"/>
+                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4471"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2069,7 +2069,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4454"/>
+                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4472"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2134,7 +2134,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4455"/>
+                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4473"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2492,7 +2492,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="34" style="10" customWidth="1"/>
     <col min="2" max="2" width="22.25" style="10" customWidth="1"/>
@@ -2503,24 +2503,24 @@
     <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1">
+      <c r="A1" s="86" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6">
       <c r="A3" s="10" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6">
       <c r="A6" s="10" t="s">
         <v>210</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1">
       <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>25689</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1">
       <c r="A8" s="13" t="s">
         <v>5</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>60歳0ヶ月</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1">
       <c r="A9" s="13" t="s">
         <v>6</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1">
       <c r="A10" s="13" t="s">
         <v>8</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1">
       <c r="A11" s="13" t="str">
         <f>$B$6&amp;"の控除計算用加入開始日"</f>
         <v>DCの控除計算用加入開始日</v>
@@ -2611,7 +2611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="18.75" customHeight="1">
       <c r="A12" s="13" t="str">
         <f>$B$6&amp;"の控除計算用加入終了日"</f>
         <v>DCの控除計算用加入終了日</v>
@@ -2630,7 +2630,7 @@
         <v>65歳0ヶ月</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1">
       <c r="A13" s="13" t="str">
         <f>$B$6&amp;"一時金の受取日"</f>
         <v>DC一時金の受取日</v>
@@ -2642,7 +2642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1">
       <c r="A14" s="13" t="str">
         <f>$B$6&amp;"一時金額"</f>
         <v>DC一時金額</v>
@@ -2654,7 +2654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6">
       <c r="A15" s="10" t="str">
         <f>B6&amp;"→会社退職金の調整対象期間"</f>
         <v>DC→会社退職金の調整対象期間</v>
@@ -2668,7 +2668,7 @@
         <v>DC一時金を先に受け取る場合、2026年1月1日以後に支払を受けたDC一時金について、国税庁の定める条件に該当する前年以前9年内の退職手当等が調整対象となります。</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6">
       <c r="A16" s="13" t="str">
         <f>"会社退職金→"&amp;B6&amp;"の調整対象期間"</f>
         <v>会社退職金→DCの調整対象期間</v>
@@ -2682,12 +2682,12 @@
         <v>会社退職金を先に受け取り、DC一時金を後で受け取る場合は19年の取扱い。</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" ht="18.75" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" ht="18.75" customHeight="1">
       <c r="A18" s="10" t="s">
         <v>14</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" ht="18.75" customHeight="1">
       <c r="A19" s="12" t="s">
         <v>16</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1">
       <c r="A20" s="13" t="s">
         <v>19</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" ht="18.75" customHeight="1">
       <c r="A21" s="13" t="s">
         <v>21</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" ht="18.75" customHeight="1">
       <c r="A22" s="13" t="str">
         <f>$B$6&amp;"の加入年数"</f>
         <v>DCの加入年数</v>
@@ -2747,7 +2747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" ht="18.75" customHeight="1">
       <c r="A23" s="13" t="str">
         <f>$B$6&amp;"の退職所得控除額"</f>
         <v>DCの退職所得控除額</v>
@@ -2760,7 +2760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4">
       <c r="A24" s="10" t="s">
         <v>25</v>
       </c>
@@ -2768,111 +2768,111 @@
         <v>216</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" ht="48" customHeight="1">
       <c r="A25" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="85" t="s">
         <v>217</v>
       </c>
-      <c r="C25" s="84"/>
-    </row>
-    <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C25" s="85"/>
+    </row>
+    <row r="27" spans="1:4" ht="18.75" customHeight="1">
       <c r="A27" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="85" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="84"/>
+      <c r="C27" s="85"/>
       <c r="D27" s="13"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B28" s="84"/>
-      <c r="C28" s="84"/>
+    <row r="28" spans="1:4">
+      <c r="B28" s="85"/>
+      <c r="C28" s="85"/>
       <c r="D28" s="13"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="B29" s="86"/>
-      <c r="C29" s="86"/>
+    <row r="29" spans="1:4">
+      <c r="B29" s="87"/>
+      <c r="C29" s="87"/>
       <c r="D29" s="13"/>
     </row>
-    <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="87" t="s">
+    <row r="30" spans="1:4" ht="18.75" customHeight="1">
+      <c r="A30" s="88" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="87"/>
-      <c r="C30" s="87"/>
-    </row>
-    <row r="31" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B30" s="88"/>
+      <c r="C30" s="88"/>
+    </row>
+    <row r="31" spans="1:4" ht="54.95" customHeight="1">
       <c r="A31" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="84" t="s">
+      <c r="B31" s="85" t="s">
         <v>219</v>
       </c>
-      <c r="C31" s="84"/>
-    </row>
-    <row r="32" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C31" s="85"/>
+    </row>
+    <row r="32" spans="1:4" ht="54.95" customHeight="1">
       <c r="A32" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="84" t="s">
+      <c r="B32" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="84"/>
+      <c r="C32" s="85"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" ht="54.95" customHeight="1">
       <c r="A33" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="84" t="s">
+      <c r="B33" s="85" t="s">
         <v>220</v>
       </c>
-      <c r="C33" s="84"/>
+      <c r="C33" s="85"/>
       <c r="D33" s="17"/>
     </row>
-    <row r="34" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" ht="54.95" customHeight="1">
       <c r="A34" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="84" t="s">
+      <c r="B34" s="85" t="s">
         <v>221</v>
       </c>
-      <c r="C34" s="84"/>
+      <c r="C34" s="85"/>
       <c r="D34" s="17"/>
     </row>
-    <row r="35" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" ht="54.95" customHeight="1">
       <c r="A35" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="84" t="s">
+      <c r="B35" s="85" t="s">
         <v>222</v>
       </c>
-      <c r="C35" s="84"/>
+      <c r="C35" s="85"/>
       <c r="D35" s="17"/>
     </row>
-    <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" ht="18.75" customHeight="1">
       <c r="A36" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="84" t="s">
+      <c r="B36" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="84"/>
-    </row>
-    <row r="37" spans="1:4" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C36" s="85"/>
+    </row>
+    <row r="37" spans="1:4" ht="50.1" customHeight="1">
       <c r="A37" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="84" t="s">
+      <c r="B37" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="84"/>
+      <c r="C37" s="85"/>
       <c r="D37" s="17"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4">
       <c r="A38" s="10" t="s">
         <v>208</v>
       </c>
@@ -2881,7 +2881,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dcCvgbcKays9Qd6YWyGd8XyUKKm7y/0+ncbJ3d/16GqrE/IX/gOxy7HnViyr3kxlY5thoDtlvLBQaJH7mj1niQ==" saltValue="x3e4VUMr7xG9ZVmqpCNAZA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="ERnHc8J7kjsQBz3ST3lE867VwG+ZIRG+FxfEXa2xg04FcgmEeyfoQkNsBSGlxWCRjK75D/IFPs65s7LTGrGa4Q==" saltValue="9gMkRekPo/0TdSbMM/Zy5Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -2920,7 +2920,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:BD70"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="61"/>
     <col min="2" max="2" width="16.625" style="61" customWidth="1"/>
@@ -2928,27 +2928,27 @@
     <col min="57" max="16384" width="9" style="61"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:56">
       <c r="B2" s="61" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:56">
       <c r="B3" s="61" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="4" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:56">
       <c r="B4" s="61" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:56">
       <c r="B5" s="61" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="6" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:56">
       <c r="C6" s="62" t="s">
         <v>229</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="AF6" s="63"/>
       <c r="AG6" s="64"/>
     </row>
-    <row r="7" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:56">
       <c r="C7" s="65" t="s">
         <v>231</v>
       </c>
@@ -3022,7 +3022,7 @@
       <c r="AF7" s="66"/>
       <c r="AG7" s="67"/>
     </row>
-    <row r="8" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:56">
       <c r="C8" s="62" t="s">
         <v>233</v>
       </c>
@@ -3059,7 +3059,7 @@
       <c r="AF8" s="63"/>
       <c r="AG8" s="64"/>
     </row>
-    <row r="9" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:56">
       <c r="C9" s="65"/>
       <c r="D9" s="66"/>
       <c r="E9" s="66"/>
@@ -3094,120 +3094,120 @@
       <c r="AF9" s="66"/>
       <c r="AG9" s="67"/>
     </row>
-    <row r="10" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:56">
       <c r="B10" s="61" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="12" spans="2:56" ht="23.25" x14ac:dyDescent="0.4">
-      <c r="B12" s="92" t="s">
+    <row r="12" spans="2:56" ht="23.25">
+      <c r="B12" s="91" t="s">
         <v>237</v>
       </c>
-      <c r="C12" s="93"/>
-      <c r="D12" s="93"/>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="93"/>
-      <c r="T12" s="93"/>
-      <c r="U12" s="93"/>
-      <c r="V12" s="93"/>
-      <c r="W12" s="93"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="93"/>
-      <c r="Z12" s="93"/>
-      <c r="AA12" s="93"/>
-      <c r="AB12" s="93"/>
-      <c r="AC12" s="93"/>
-      <c r="AD12" s="93"/>
-      <c r="AE12" s="93"/>
-      <c r="AF12" s="93"/>
-      <c r="AG12" s="93"/>
-      <c r="AH12" s="93"/>
-      <c r="AI12" s="93"/>
-      <c r="AJ12" s="93"/>
-      <c r="AK12" s="93"/>
-      <c r="AL12" s="93"/>
-      <c r="AM12" s="93"/>
-      <c r="AN12" s="93"/>
-      <c r="AO12" s="93"/>
-      <c r="AP12" s="93"/>
-      <c r="AQ12" s="93"/>
-      <c r="AR12" s="93"/>
-      <c r="AS12" s="93"/>
-      <c r="AT12" s="93"/>
-      <c r="AU12" s="93"/>
-      <c r="AV12" s="93"/>
-      <c r="AW12" s="93"/>
-      <c r="AX12" s="93"/>
-      <c r="AY12" s="93"/>
-    </row>
-    <row r="13" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B13" s="94" t="s">
+      <c r="C12" s="92"/>
+      <c r="D12" s="92"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="92"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="92"/>
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="92"/>
+      <c r="P12" s="92"/>
+      <c r="Q12" s="92"/>
+      <c r="R12" s="92"/>
+      <c r="S12" s="92"/>
+      <c r="T12" s="92"/>
+      <c r="U12" s="92"/>
+      <c r="V12" s="92"/>
+      <c r="W12" s="92"/>
+      <c r="X12" s="92"/>
+      <c r="Y12" s="92"/>
+      <c r="Z12" s="92"/>
+      <c r="AA12" s="92"/>
+      <c r="AB12" s="92"/>
+      <c r="AC12" s="92"/>
+      <c r="AD12" s="92"/>
+      <c r="AE12" s="92"/>
+      <c r="AF12" s="92"/>
+      <c r="AG12" s="92"/>
+      <c r="AH12" s="92"/>
+      <c r="AI12" s="92"/>
+      <c r="AJ12" s="92"/>
+      <c r="AK12" s="92"/>
+      <c r="AL12" s="92"/>
+      <c r="AM12" s="92"/>
+      <c r="AN12" s="92"/>
+      <c r="AO12" s="92"/>
+      <c r="AP12" s="92"/>
+      <c r="AQ12" s="92"/>
+      <c r="AR12" s="92"/>
+      <c r="AS12" s="92"/>
+      <c r="AT12" s="92"/>
+      <c r="AU12" s="92"/>
+      <c r="AV12" s="92"/>
+      <c r="AW12" s="92"/>
+      <c r="AX12" s="92"/>
+      <c r="AY12" s="92"/>
+    </row>
+    <row r="13" spans="2:56">
+      <c r="B13" s="93" t="s">
         <v>238</v>
       </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="93"/>
-      <c r="F13" s="93"/>
-      <c r="G13" s="93"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="93"/>
-      <c r="J13" s="93"/>
-      <c r="K13" s="93"/>
-      <c r="L13" s="93"/>
-      <c r="M13" s="93"/>
-      <c r="N13" s="93"/>
-      <c r="O13" s="93"/>
-      <c r="P13" s="93"/>
-      <c r="Q13" s="93"/>
-      <c r="R13" s="93"/>
-      <c r="S13" s="93"/>
-      <c r="T13" s="93"/>
-      <c r="U13" s="93"/>
-      <c r="V13" s="93"/>
-      <c r="W13" s="93"/>
-      <c r="X13" s="93"/>
-      <c r="Y13" s="93"/>
-      <c r="Z13" s="93"/>
-      <c r="AA13" s="93"/>
-      <c r="AB13" s="93"/>
-      <c r="AC13" s="93"/>
-      <c r="AD13" s="93"/>
-      <c r="AE13" s="93"/>
-      <c r="AF13" s="93"/>
-      <c r="AG13" s="93"/>
-      <c r="AH13" s="93"/>
-      <c r="AI13" s="93"/>
-      <c r="AJ13" s="93"/>
-      <c r="AK13" s="93"/>
-      <c r="AL13" s="93"/>
-      <c r="AM13" s="93"/>
-      <c r="AN13" s="93"/>
-      <c r="AO13" s="93"/>
-      <c r="AP13" s="93"/>
-      <c r="AQ13" s="93"/>
-      <c r="AR13" s="93"/>
-      <c r="AS13" s="93"/>
-      <c r="AT13" s="93"/>
-      <c r="AU13" s="93"/>
-      <c r="AV13" s="93"/>
-      <c r="AW13" s="93"/>
-      <c r="AX13" s="93"/>
-      <c r="AY13" s="93"/>
-    </row>
-    <row r="14" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="92"/>
+      <c r="F13" s="92"/>
+      <c r="G13" s="92"/>
+      <c r="H13" s="92"/>
+      <c r="I13" s="92"/>
+      <c r="J13" s="92"/>
+      <c r="K13" s="92"/>
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="92"/>
+      <c r="O13" s="92"/>
+      <c r="P13" s="92"/>
+      <c r="Q13" s="92"/>
+      <c r="R13" s="92"/>
+      <c r="S13" s="92"/>
+      <c r="T13" s="92"/>
+      <c r="U13" s="92"/>
+      <c r="V13" s="92"/>
+      <c r="W13" s="92"/>
+      <c r="X13" s="92"/>
+      <c r="Y13" s="92"/>
+      <c r="Z13" s="92"/>
+      <c r="AA13" s="92"/>
+      <c r="AB13" s="92"/>
+      <c r="AC13" s="92"/>
+      <c r="AD13" s="92"/>
+      <c r="AE13" s="92"/>
+      <c r="AF13" s="92"/>
+      <c r="AG13" s="92"/>
+      <c r="AH13" s="92"/>
+      <c r="AI13" s="92"/>
+      <c r="AJ13" s="92"/>
+      <c r="AK13" s="92"/>
+      <c r="AL13" s="92"/>
+      <c r="AM13" s="92"/>
+      <c r="AN13" s="92"/>
+      <c r="AO13" s="92"/>
+      <c r="AP13" s="92"/>
+      <c r="AQ13" s="92"/>
+      <c r="AR13" s="92"/>
+      <c r="AS13" s="92"/>
+      <c r="AT13" s="92"/>
+      <c r="AU13" s="92"/>
+      <c r="AV13" s="92"/>
+      <c r="AW13" s="92"/>
+      <c r="AX13" s="92"/>
+      <c r="AY13" s="92"/>
+    </row>
+    <row r="14" spans="2:56">
       <c r="B14" s="68"/>
       <c r="C14" s="69" t="s">
         <v>239</v>
@@ -3265,7 +3265,7 @@
       <c r="AX14" s="68"/>
       <c r="AY14" s="68"/>
     </row>
-    <row r="15" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:56">
       <c r="B15" s="72" t="s">
         <v>242</v>
       </c>
@@ -3424,7 +3424,7 @@
       <c r="BC15" s="74"/>
       <c r="BD15" s="74"/>
     </row>
-    <row r="17" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:56">
       <c r="B17" s="75" t="s">
         <v>243</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="BC17" s="76"/>
       <c r="BD17" s="76"/>
     </row>
-    <row r="18" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:56">
       <c r="B18" s="77" t="s">
         <v>245</v>
       </c>
@@ -3536,7 +3536,7 @@
       <c r="AW18" s="78"/>
       <c r="AX18" s="78"/>
     </row>
-    <row r="19" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:56">
       <c r="B19" s="77" t="s">
         <v>246</v>
       </c>
@@ -3572,7 +3572,7 @@
       <c r="AR19" s="79"/>
       <c r="AS19" s="79"/>
     </row>
-    <row r="20" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:56">
       <c r="B20" s="77" t="s">
         <v>247</v>
       </c>
@@ -3608,7 +3608,7 @@
       <c r="AR20" s="80"/>
       <c r="AS20" s="80"/>
     </row>
-    <row r="21" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:56">
       <c r="B21" s="77" t="s">
         <v>248</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="BC21" s="81"/>
       <c r="BD21" s="81"/>
     </row>
-    <row r="22" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:56">
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
       <c r="G22" s="81"/>
@@ -3723,55 +3723,55 @@
       <c r="BC22" s="81"/>
       <c r="BD22" s="81"/>
     </row>
-    <row r="23" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B23" s="90" t="s">
+    <row r="23" spans="2:56">
+      <c r="B23" s="89" t="s">
         <v>251</v>
       </c>
-      <c r="C23" s="89"/>
-      <c r="D23" s="89"/>
-      <c r="E23" s="89"/>
-      <c r="F23" s="89"/>
-      <c r="G23" s="89"/>
-      <c r="H23" s="89"/>
-      <c r="I23" s="89"/>
-      <c r="J23" s="89"/>
-      <c r="K23" s="89"/>
-      <c r="L23" s="89"/>
-      <c r="M23" s="89"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="89"/>
-      <c r="P23" s="89"/>
-    </row>
-    <row r="24" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B24" s="88" t="s">
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="90"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="90"/>
+      <c r="J23" s="90"/>
+      <c r="K23" s="90"/>
+      <c r="L23" s="90"/>
+      <c r="M23" s="90"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="90"/>
+    </row>
+    <row r="24" spans="2:56">
+      <c r="B24" s="94" t="s">
         <v>252</v>
       </c>
-      <c r="C24" s="89"/>
-      <c r="D24" s="89"/>
-      <c r="E24" s="89"/>
-      <c r="F24" s="89"/>
-      <c r="G24" s="89"/>
-      <c r="H24" s="89"/>
-      <c r="I24" s="89"/>
-      <c r="J24" s="89"/>
-      <c r="K24" s="89"/>
-      <c r="L24" s="89"/>
-      <c r="M24" s="89"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="89"/>
-      <c r="P24" s="89"/>
-      <c r="Q24" s="89"/>
-      <c r="R24" s="89"/>
-      <c r="S24" s="89"/>
-      <c r="T24" s="89"/>
-      <c r="U24" s="89"/>
-      <c r="V24" s="89"/>
-      <c r="W24" s="89"/>
-      <c r="X24" s="89"/>
-      <c r="Y24" s="89"/>
-      <c r="Z24" s="89"/>
-    </row>
-    <row r="27" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="90"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="90"/>
+      <c r="J24" s="90"/>
+      <c r="K24" s="90"/>
+      <c r="L24" s="90"/>
+      <c r="M24" s="90"/>
+      <c r="N24" s="90"/>
+      <c r="O24" s="90"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="90"/>
+      <c r="R24" s="90"/>
+      <c r="S24" s="90"/>
+      <c r="T24" s="90"/>
+      <c r="U24" s="90"/>
+      <c r="V24" s="90"/>
+      <c r="W24" s="90"/>
+      <c r="X24" s="90"/>
+      <c r="Y24" s="90"/>
+      <c r="Z24" s="90"/>
+    </row>
+    <row r="27" spans="2:56">
       <c r="B27" s="75" t="s">
         <v>253</v>
       </c>
@@ -3832,7 +3832,7 @@
       <c r="BC27" s="76"/>
       <c r="BD27" s="76"/>
     </row>
-    <row r="28" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:56">
       <c r="B28" s="77" t="s">
         <v>245</v>
       </c>
@@ -3878,7 +3878,7 @@
       <c r="AR28" s="78"/>
       <c r="AS28" s="78"/>
     </row>
-    <row r="29" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:56">
       <c r="B29" s="77" t="s">
         <v>246</v>
       </c>
@@ -3919,7 +3919,7 @@
       <c r="AW29" s="79"/>
       <c r="AX29" s="79"/>
     </row>
-    <row r="30" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:56">
       <c r="B30" s="77" t="s">
         <v>247</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="AW30" s="80"/>
       <c r="AX30" s="80"/>
     </row>
-    <row r="31" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:56">
       <c r="B31" s="77" t="s">
         <v>248</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="BC31" s="81"/>
       <c r="BD31" s="81"/>
     </row>
-    <row r="32" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:56">
       <c r="E32" s="81"/>
       <c r="F32" s="81"/>
       <c r="G32" s="81"/>
@@ -4075,12 +4075,12 @@
       <c r="BC32" s="81"/>
       <c r="BD32" s="81"/>
     </row>
-    <row r="34" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:56">
       <c r="B34" s="61" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="35" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:56">
       <c r="C35" s="62" t="s">
         <v>258</v>
       </c>
@@ -4118,7 +4118,7 @@
       <c r="AG35" s="63"/>
       <c r="AH35" s="64"/>
     </row>
-    <row r="36" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:56">
       <c r="C36" s="65" t="s">
         <v>231</v>
       </c>
@@ -4156,7 +4156,7 @@
       <c r="AG36" s="66"/>
       <c r="AH36" s="67"/>
     </row>
-    <row r="37" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:56">
       <c r="C37" s="62" t="s">
         <v>260</v>
       </c>
@@ -4194,7 +4194,7 @@
       <c r="AG37" s="63"/>
       <c r="AH37" s="64"/>
     </row>
-    <row r="38" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:56">
       <c r="C38" s="65"/>
       <c r="D38" s="66"/>
       <c r="E38" s="66"/>
@@ -4230,61 +4230,61 @@
       <c r="AG38" s="66"/>
       <c r="AH38" s="67"/>
     </row>
-    <row r="40" spans="2:56" ht="23.25" x14ac:dyDescent="0.4">
-      <c r="B40" s="92" t="s">
+    <row r="40" spans="2:56" ht="23.25">
+      <c r="B40" s="91" t="s">
         <v>263</v>
       </c>
-      <c r="C40" s="93"/>
-      <c r="D40" s="93"/>
-      <c r="E40" s="93"/>
-      <c r="F40" s="93"/>
-      <c r="G40" s="93"/>
-      <c r="H40" s="93"/>
-      <c r="I40" s="93"/>
-      <c r="J40" s="93"/>
-      <c r="K40" s="93"/>
-      <c r="L40" s="93"/>
-      <c r="M40" s="93"/>
-      <c r="N40" s="93"/>
-      <c r="O40" s="93"/>
-      <c r="P40" s="93"/>
-      <c r="Q40" s="93"/>
-      <c r="R40" s="93"/>
-      <c r="S40" s="93"/>
-      <c r="T40" s="93"/>
-      <c r="U40" s="93"/>
-      <c r="V40" s="93"/>
-      <c r="W40" s="93"/>
-      <c r="X40" s="93"/>
-      <c r="Y40" s="93"/>
-      <c r="Z40" s="93"/>
-      <c r="AA40" s="93"/>
-      <c r="AB40" s="93"/>
-      <c r="AC40" s="93"/>
-      <c r="AD40" s="93"/>
-      <c r="AE40" s="93"/>
-      <c r="AF40" s="93"/>
-      <c r="AG40" s="93"/>
-      <c r="AH40" s="93"/>
-      <c r="AI40" s="93"/>
-      <c r="AJ40" s="93"/>
-      <c r="AK40" s="93"/>
-      <c r="AL40" s="93"/>
-      <c r="AM40" s="93"/>
-      <c r="AN40" s="93"/>
-      <c r="AO40" s="93"/>
-      <c r="AP40" s="93"/>
-      <c r="AQ40" s="93"/>
-      <c r="AR40" s="93"/>
-      <c r="AS40" s="93"/>
-      <c r="AT40" s="93"/>
-      <c r="AU40" s="93"/>
-      <c r="AV40" s="93"/>
-      <c r="AW40" s="93"/>
-      <c r="AX40" s="93"/>
-      <c r="AY40" s="93"/>
-    </row>
-    <row r="41" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="C40" s="92"/>
+      <c r="D40" s="92"/>
+      <c r="E40" s="92"/>
+      <c r="F40" s="92"/>
+      <c r="G40" s="92"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="92"/>
+      <c r="J40" s="92"/>
+      <c r="K40" s="92"/>
+      <c r="L40" s="92"/>
+      <c r="M40" s="92"/>
+      <c r="N40" s="92"/>
+      <c r="O40" s="92"/>
+      <c r="P40" s="92"/>
+      <c r="Q40" s="92"/>
+      <c r="R40" s="92"/>
+      <c r="S40" s="92"/>
+      <c r="T40" s="92"/>
+      <c r="U40" s="92"/>
+      <c r="V40" s="92"/>
+      <c r="W40" s="92"/>
+      <c r="X40" s="92"/>
+      <c r="Y40" s="92"/>
+      <c r="Z40" s="92"/>
+      <c r="AA40" s="92"/>
+      <c r="AB40" s="92"/>
+      <c r="AC40" s="92"/>
+      <c r="AD40" s="92"/>
+      <c r="AE40" s="92"/>
+      <c r="AF40" s="92"/>
+      <c r="AG40" s="92"/>
+      <c r="AH40" s="92"/>
+      <c r="AI40" s="92"/>
+      <c r="AJ40" s="92"/>
+      <c r="AK40" s="92"/>
+      <c r="AL40" s="92"/>
+      <c r="AM40" s="92"/>
+      <c r="AN40" s="92"/>
+      <c r="AO40" s="92"/>
+      <c r="AP40" s="92"/>
+      <c r="AQ40" s="92"/>
+      <c r="AR40" s="92"/>
+      <c r="AS40" s="92"/>
+      <c r="AT40" s="92"/>
+      <c r="AU40" s="92"/>
+      <c r="AV40" s="92"/>
+      <c r="AW40" s="92"/>
+      <c r="AX40" s="92"/>
+      <c r="AY40" s="92"/>
+    </row>
+    <row r="41" spans="2:56">
       <c r="B41" s="72" t="s">
         <v>242</v>
       </c>
@@ -4443,7 +4443,7 @@
       <c r="BC41" s="74"/>
       <c r="BD41" s="74"/>
     </row>
-    <row r="43" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:56">
       <c r="B43" s="75" t="s">
         <v>264</v>
       </c>
@@ -4504,7 +4504,7 @@
       <c r="BC43" s="76"/>
       <c r="BD43" s="76"/>
     </row>
-    <row r="44" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:56">
       <c r="B44" s="77" t="s">
         <v>245</v>
       </c>
@@ -4555,7 +4555,7 @@
       <c r="AW44" s="78"/>
       <c r="AX44" s="78"/>
     </row>
-    <row r="45" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:56">
       <c r="B45" s="77" t="s">
         <v>265</v>
       </c>
@@ -4591,7 +4591,7 @@
       <c r="AR45" s="79"/>
       <c r="AS45" s="79"/>
     </row>
-    <row r="46" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:56">
       <c r="B46" s="77" t="s">
         <v>247</v>
       </c>
@@ -4627,7 +4627,7 @@
       <c r="AR46" s="80"/>
       <c r="AS46" s="80"/>
     </row>
-    <row r="47" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:56">
       <c r="B47" s="77" t="s">
         <v>248</v>
       </c>
@@ -4686,7 +4686,7 @@
       <c r="BC47" s="81"/>
       <c r="BD47" s="81"/>
     </row>
-    <row r="48" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:56">
       <c r="E48" s="81"/>
       <c r="F48" s="81"/>
       <c r="G48" s="81"/>
@@ -4737,60 +4737,60 @@
       <c r="BC48" s="81"/>
       <c r="BD48" s="81"/>
     </row>
-    <row r="49" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B49" s="90" t="s">
+    <row r="49" spans="2:56">
+      <c r="B49" s="89" t="s">
         <v>251</v>
       </c>
-      <c r="C49" s="89"/>
-      <c r="D49" s="89"/>
-      <c r="E49" s="89"/>
-      <c r="F49" s="89"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="89"/>
-      <c r="I49" s="89"/>
-      <c r="J49" s="89"/>
-      <c r="K49" s="89"/>
-      <c r="L49" s="89"/>
-      <c r="M49" s="89"/>
-      <c r="N49" s="89"/>
-      <c r="O49" s="89"/>
-      <c r="P49" s="89"/>
-    </row>
-    <row r="50" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B50" s="88" t="s">
+      <c r="C49" s="90"/>
+      <c r="D49" s="90"/>
+      <c r="E49" s="90"/>
+      <c r="F49" s="90"/>
+      <c r="G49" s="90"/>
+      <c r="H49" s="90"/>
+      <c r="I49" s="90"/>
+      <c r="J49" s="90"/>
+      <c r="K49" s="90"/>
+      <c r="L49" s="90"/>
+      <c r="M49" s="90"/>
+      <c r="N49" s="90"/>
+      <c r="O49" s="90"/>
+      <c r="P49" s="90"/>
+    </row>
+    <row r="50" spans="2:56">
+      <c r="B50" s="94" t="s">
         <v>268</v>
       </c>
-      <c r="C50" s="89"/>
-      <c r="D50" s="89"/>
-      <c r="E50" s="89"/>
-      <c r="F50" s="89"/>
-      <c r="G50" s="89"/>
-      <c r="H50" s="89"/>
-      <c r="I50" s="89"/>
-      <c r="J50" s="89"/>
-      <c r="K50" s="89"/>
-      <c r="L50" s="89"/>
-      <c r="M50" s="89"/>
-      <c r="N50" s="89"/>
-      <c r="O50" s="89"/>
-      <c r="P50" s="89"/>
-      <c r="Q50" s="89"/>
-      <c r="R50" s="89"/>
-      <c r="S50" s="89"/>
-      <c r="T50" s="89"/>
-      <c r="U50" s="89"/>
-      <c r="V50" s="89"/>
-      <c r="W50" s="89"/>
-      <c r="X50" s="89"/>
-      <c r="Y50" s="89"/>
-      <c r="Z50" s="89"/>
-    </row>
-    <row r="51" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="C50" s="90"/>
+      <c r="D50" s="90"/>
+      <c r="E50" s="90"/>
+      <c r="F50" s="90"/>
+      <c r="G50" s="90"/>
+      <c r="H50" s="90"/>
+      <c r="I50" s="90"/>
+      <c r="J50" s="90"/>
+      <c r="K50" s="90"/>
+      <c r="L50" s="90"/>
+      <c r="M50" s="90"/>
+      <c r="N50" s="90"/>
+      <c r="O50" s="90"/>
+      <c r="P50" s="90"/>
+      <c r="Q50" s="90"/>
+      <c r="R50" s="90"/>
+      <c r="S50" s="90"/>
+      <c r="T50" s="90"/>
+      <c r="U50" s="90"/>
+      <c r="V50" s="90"/>
+      <c r="W50" s="90"/>
+      <c r="X50" s="90"/>
+      <c r="Y50" s="90"/>
+      <c r="Z50" s="90"/>
+    </row>
+    <row r="51" spans="2:56">
       <c r="B51" s="61" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="53" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:56">
       <c r="B53" s="75" t="s">
         <v>270</v>
       </c>
@@ -4851,7 +4851,7 @@
       <c r="BC53" s="76"/>
       <c r="BD53" s="76"/>
     </row>
-    <row r="54" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:56">
       <c r="B54" s="77" t="s">
         <v>245</v>
       </c>
@@ -4897,7 +4897,7 @@
       <c r="AR54" s="78"/>
       <c r="AS54" s="78"/>
     </row>
-    <row r="55" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:56">
       <c r="B55" s="77" t="s">
         <v>265</v>
       </c>
@@ -4938,7 +4938,7 @@
       <c r="AW55" s="79"/>
       <c r="AX55" s="79"/>
     </row>
-    <row r="56" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:56">
       <c r="B56" s="77" t="s">
         <v>247</v>
       </c>
@@ -4979,7 +4979,7 @@
       <c r="AW56" s="80"/>
       <c r="AX56" s="80"/>
     </row>
-    <row r="57" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:56">
       <c r="B57" s="77" t="s">
         <v>248</v>
       </c>
@@ -5038,7 +5038,7 @@
       <c r="BC57" s="81"/>
       <c r="BD57" s="81"/>
     </row>
-    <row r="58" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:56">
       <c r="E58" s="81"/>
       <c r="F58" s="81"/>
       <c r="G58" s="81"/>
@@ -5077,347 +5077,347 @@
       <c r="BC58" s="81"/>
       <c r="BD58" s="81"/>
     </row>
-    <row r="59" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B59" s="90" t="s">
+    <row r="59" spans="2:56">
+      <c r="B59" s="89" t="s">
         <v>272</v>
       </c>
-      <c r="C59" s="89"/>
-      <c r="D59" s="89"/>
-      <c r="E59" s="89"/>
-      <c r="F59" s="89"/>
-      <c r="G59" s="89"/>
-      <c r="H59" s="89"/>
-      <c r="I59" s="89"/>
-      <c r="J59" s="89"/>
-      <c r="K59" s="89"/>
-      <c r="L59" s="89"/>
-      <c r="M59" s="89"/>
-      <c r="N59" s="89"/>
-      <c r="O59" s="89"/>
-      <c r="P59" s="89"/>
-    </row>
-    <row r="60" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B60" s="88" t="s">
+      <c r="C59" s="90"/>
+      <c r="D59" s="90"/>
+      <c r="E59" s="90"/>
+      <c r="F59" s="90"/>
+      <c r="G59" s="90"/>
+      <c r="H59" s="90"/>
+      <c r="I59" s="90"/>
+      <c r="J59" s="90"/>
+      <c r="K59" s="90"/>
+      <c r="L59" s="90"/>
+      <c r="M59" s="90"/>
+      <c r="N59" s="90"/>
+      <c r="O59" s="90"/>
+      <c r="P59" s="90"/>
+    </row>
+    <row r="60" spans="2:56">
+      <c r="B60" s="94" t="s">
         <v>268</v>
       </c>
-      <c r="C60" s="89"/>
-      <c r="D60" s="89"/>
-      <c r="E60" s="89"/>
-      <c r="F60" s="89"/>
-      <c r="G60" s="89"/>
-      <c r="H60" s="89"/>
-      <c r="I60" s="89"/>
-      <c r="J60" s="89"/>
-      <c r="K60" s="89"/>
-      <c r="L60" s="89"/>
-      <c r="M60" s="89"/>
-      <c r="N60" s="89"/>
-      <c r="O60" s="89"/>
-      <c r="P60" s="89"/>
-      <c r="Q60" s="89"/>
-      <c r="R60" s="89"/>
-      <c r="S60" s="89"/>
-      <c r="T60" s="89"/>
-      <c r="U60" s="89"/>
-      <c r="V60" s="89"/>
-      <c r="W60" s="89"/>
-      <c r="X60" s="89"/>
-      <c r="Y60" s="89"/>
-      <c r="Z60" s="89"/>
-    </row>
-    <row r="61" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="C60" s="90"/>
+      <c r="D60" s="90"/>
+      <c r="E60" s="90"/>
+      <c r="F60" s="90"/>
+      <c r="G60" s="90"/>
+      <c r="H60" s="90"/>
+      <c r="I60" s="90"/>
+      <c r="J60" s="90"/>
+      <c r="K60" s="90"/>
+      <c r="L60" s="90"/>
+      <c r="M60" s="90"/>
+      <c r="N60" s="90"/>
+      <c r="O60" s="90"/>
+      <c r="P60" s="90"/>
+      <c r="Q60" s="90"/>
+      <c r="R60" s="90"/>
+      <c r="S60" s="90"/>
+      <c r="T60" s="90"/>
+      <c r="U60" s="90"/>
+      <c r="V60" s="90"/>
+      <c r="W60" s="90"/>
+      <c r="X60" s="90"/>
+      <c r="Y60" s="90"/>
+      <c r="Z60" s="90"/>
+    </row>
+    <row r="61" spans="2:56">
       <c r="B61" s="61" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="63" spans="2:56" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:56">
       <c r="B63" s="75" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:56" x14ac:dyDescent="0.4">
-      <c r="B64" s="91" t="s">
+    <row r="64" spans="2:56">
+      <c r="B64" s="95" t="s">
         <v>274</v>
       </c>
-      <c r="C64" s="89"/>
-      <c r="D64" s="89"/>
-      <c r="E64" s="89"/>
-      <c r="F64" s="89"/>
-      <c r="G64" s="89"/>
-      <c r="H64" s="89"/>
-      <c r="I64" s="89"/>
-      <c r="J64" s="89"/>
-      <c r="K64" s="89"/>
-      <c r="L64" s="89"/>
-      <c r="M64" s="89"/>
-      <c r="N64" s="89"/>
-      <c r="O64" s="89"/>
-      <c r="P64" s="89"/>
-      <c r="Q64" s="89"/>
-      <c r="R64" s="89"/>
-      <c r="S64" s="89"/>
-      <c r="T64" s="89"/>
-      <c r="U64" s="89"/>
-      <c r="V64" s="89"/>
-      <c r="W64" s="89"/>
-      <c r="X64" s="89"/>
-      <c r="Y64" s="89"/>
-      <c r="Z64" s="89"/>
-      <c r="AA64" s="89"/>
-      <c r="AB64" s="89"/>
-      <c r="AC64" s="89"/>
-      <c r="AD64" s="89"/>
-      <c r="AE64" s="89"/>
-      <c r="AF64" s="89"/>
-      <c r="AG64" s="89"/>
-      <c r="AH64" s="89"/>
-      <c r="AI64" s="89"/>
-      <c r="AJ64" s="89"/>
-      <c r="AK64" s="89"/>
-      <c r="AL64" s="89"/>
-      <c r="AM64" s="89"/>
-      <c r="AN64" s="89"/>
-      <c r="AO64" s="89"/>
-      <c r="AP64" s="89"/>
-      <c r="AQ64" s="89"/>
-      <c r="AR64" s="89"/>
-      <c r="AS64" s="89"/>
-      <c r="AT64" s="89"/>
-      <c r="AU64" s="89"/>
-      <c r="AV64" s="89"/>
-      <c r="AW64" s="89"/>
-      <c r="AX64" s="89"/>
-      <c r="AY64" s="89"/>
-    </row>
-    <row r="65" spans="2:51" x14ac:dyDescent="0.4">
-      <c r="B65" s="89"/>
-      <c r="C65" s="89"/>
-      <c r="D65" s="89"/>
-      <c r="E65" s="89"/>
-      <c r="F65" s="89"/>
-      <c r="G65" s="89"/>
-      <c r="H65" s="89"/>
-      <c r="I65" s="89"/>
-      <c r="J65" s="89"/>
-      <c r="K65" s="89"/>
-      <c r="L65" s="89"/>
-      <c r="M65" s="89"/>
-      <c r="N65" s="89"/>
-      <c r="O65" s="89"/>
-      <c r="P65" s="89"/>
-      <c r="Q65" s="89"/>
-      <c r="R65" s="89"/>
-      <c r="S65" s="89"/>
-      <c r="T65" s="89"/>
-      <c r="U65" s="89"/>
-      <c r="V65" s="89"/>
-      <c r="W65" s="89"/>
-      <c r="X65" s="89"/>
-      <c r="Y65" s="89"/>
-      <c r="Z65" s="89"/>
-      <c r="AA65" s="89"/>
-      <c r="AB65" s="89"/>
-      <c r="AC65" s="89"/>
-      <c r="AD65" s="89"/>
-      <c r="AE65" s="89"/>
-      <c r="AF65" s="89"/>
-      <c r="AG65" s="89"/>
-      <c r="AH65" s="89"/>
-      <c r="AI65" s="89"/>
-      <c r="AJ65" s="89"/>
-      <c r="AK65" s="89"/>
-      <c r="AL65" s="89"/>
-      <c r="AM65" s="89"/>
-      <c r="AN65" s="89"/>
-      <c r="AO65" s="89"/>
-      <c r="AP65" s="89"/>
-      <c r="AQ65" s="89"/>
-      <c r="AR65" s="89"/>
-      <c r="AS65" s="89"/>
-      <c r="AT65" s="89"/>
-      <c r="AU65" s="89"/>
-      <c r="AV65" s="89"/>
-      <c r="AW65" s="89"/>
-      <c r="AX65" s="89"/>
-      <c r="AY65" s="89"/>
-    </row>
-    <row r="66" spans="2:51" x14ac:dyDescent="0.4">
-      <c r="B66" s="89"/>
-      <c r="C66" s="89"/>
-      <c r="D66" s="89"/>
-      <c r="E66" s="89"/>
-      <c r="F66" s="89"/>
-      <c r="G66" s="89"/>
-      <c r="H66" s="89"/>
-      <c r="I66" s="89"/>
-      <c r="J66" s="89"/>
-      <c r="K66" s="89"/>
-      <c r="L66" s="89"/>
-      <c r="M66" s="89"/>
-      <c r="N66" s="89"/>
-      <c r="O66" s="89"/>
-      <c r="P66" s="89"/>
-      <c r="Q66" s="89"/>
-      <c r="R66" s="89"/>
-      <c r="S66" s="89"/>
-      <c r="T66" s="89"/>
-      <c r="U66" s="89"/>
-      <c r="V66" s="89"/>
-      <c r="W66" s="89"/>
-      <c r="X66" s="89"/>
-      <c r="Y66" s="89"/>
-      <c r="Z66" s="89"/>
-      <c r="AA66" s="89"/>
-      <c r="AB66" s="89"/>
-      <c r="AC66" s="89"/>
-      <c r="AD66" s="89"/>
-      <c r="AE66" s="89"/>
-      <c r="AF66" s="89"/>
-      <c r="AG66" s="89"/>
-      <c r="AH66" s="89"/>
-      <c r="AI66" s="89"/>
-      <c r="AJ66" s="89"/>
-      <c r="AK66" s="89"/>
-      <c r="AL66" s="89"/>
-      <c r="AM66" s="89"/>
-      <c r="AN66" s="89"/>
-      <c r="AO66" s="89"/>
-      <c r="AP66" s="89"/>
-      <c r="AQ66" s="89"/>
-      <c r="AR66" s="89"/>
-      <c r="AS66" s="89"/>
-      <c r="AT66" s="89"/>
-      <c r="AU66" s="89"/>
-      <c r="AV66" s="89"/>
-      <c r="AW66" s="89"/>
-      <c r="AX66" s="89"/>
-      <c r="AY66" s="89"/>
-    </row>
-    <row r="68" spans="2:51" x14ac:dyDescent="0.4">
+      <c r="C64" s="90"/>
+      <c r="D64" s="90"/>
+      <c r="E64" s="90"/>
+      <c r="F64" s="90"/>
+      <c r="G64" s="90"/>
+      <c r="H64" s="90"/>
+      <c r="I64" s="90"/>
+      <c r="J64" s="90"/>
+      <c r="K64" s="90"/>
+      <c r="L64" s="90"/>
+      <c r="M64" s="90"/>
+      <c r="N64" s="90"/>
+      <c r="O64" s="90"/>
+      <c r="P64" s="90"/>
+      <c r="Q64" s="90"/>
+      <c r="R64" s="90"/>
+      <c r="S64" s="90"/>
+      <c r="T64" s="90"/>
+      <c r="U64" s="90"/>
+      <c r="V64" s="90"/>
+      <c r="W64" s="90"/>
+      <c r="X64" s="90"/>
+      <c r="Y64" s="90"/>
+      <c r="Z64" s="90"/>
+      <c r="AA64" s="90"/>
+      <c r="AB64" s="90"/>
+      <c r="AC64" s="90"/>
+      <c r="AD64" s="90"/>
+      <c r="AE64" s="90"/>
+      <c r="AF64" s="90"/>
+      <c r="AG64" s="90"/>
+      <c r="AH64" s="90"/>
+      <c r="AI64" s="90"/>
+      <c r="AJ64" s="90"/>
+      <c r="AK64" s="90"/>
+      <c r="AL64" s="90"/>
+      <c r="AM64" s="90"/>
+      <c r="AN64" s="90"/>
+      <c r="AO64" s="90"/>
+      <c r="AP64" s="90"/>
+      <c r="AQ64" s="90"/>
+      <c r="AR64" s="90"/>
+      <c r="AS64" s="90"/>
+      <c r="AT64" s="90"/>
+      <c r="AU64" s="90"/>
+      <c r="AV64" s="90"/>
+      <c r="AW64" s="90"/>
+      <c r="AX64" s="90"/>
+      <c r="AY64" s="90"/>
+    </row>
+    <row r="65" spans="2:51">
+      <c r="B65" s="90"/>
+      <c r="C65" s="90"/>
+      <c r="D65" s="90"/>
+      <c r="E65" s="90"/>
+      <c r="F65" s="90"/>
+      <c r="G65" s="90"/>
+      <c r="H65" s="90"/>
+      <c r="I65" s="90"/>
+      <c r="J65" s="90"/>
+      <c r="K65" s="90"/>
+      <c r="L65" s="90"/>
+      <c r="M65" s="90"/>
+      <c r="N65" s="90"/>
+      <c r="O65" s="90"/>
+      <c r="P65" s="90"/>
+      <c r="Q65" s="90"/>
+      <c r="R65" s="90"/>
+      <c r="S65" s="90"/>
+      <c r="T65" s="90"/>
+      <c r="U65" s="90"/>
+      <c r="V65" s="90"/>
+      <c r="W65" s="90"/>
+      <c r="X65" s="90"/>
+      <c r="Y65" s="90"/>
+      <c r="Z65" s="90"/>
+      <c r="AA65" s="90"/>
+      <c r="AB65" s="90"/>
+      <c r="AC65" s="90"/>
+      <c r="AD65" s="90"/>
+      <c r="AE65" s="90"/>
+      <c r="AF65" s="90"/>
+      <c r="AG65" s="90"/>
+      <c r="AH65" s="90"/>
+      <c r="AI65" s="90"/>
+      <c r="AJ65" s="90"/>
+      <c r="AK65" s="90"/>
+      <c r="AL65" s="90"/>
+      <c r="AM65" s="90"/>
+      <c r="AN65" s="90"/>
+      <c r="AO65" s="90"/>
+      <c r="AP65" s="90"/>
+      <c r="AQ65" s="90"/>
+      <c r="AR65" s="90"/>
+      <c r="AS65" s="90"/>
+      <c r="AT65" s="90"/>
+      <c r="AU65" s="90"/>
+      <c r="AV65" s="90"/>
+      <c r="AW65" s="90"/>
+      <c r="AX65" s="90"/>
+      <c r="AY65" s="90"/>
+    </row>
+    <row r="66" spans="2:51">
+      <c r="B66" s="90"/>
+      <c r="C66" s="90"/>
+      <c r="D66" s="90"/>
+      <c r="E66" s="90"/>
+      <c r="F66" s="90"/>
+      <c r="G66" s="90"/>
+      <c r="H66" s="90"/>
+      <c r="I66" s="90"/>
+      <c r="J66" s="90"/>
+      <c r="K66" s="90"/>
+      <c r="L66" s="90"/>
+      <c r="M66" s="90"/>
+      <c r="N66" s="90"/>
+      <c r="O66" s="90"/>
+      <c r="P66" s="90"/>
+      <c r="Q66" s="90"/>
+      <c r="R66" s="90"/>
+      <c r="S66" s="90"/>
+      <c r="T66" s="90"/>
+      <c r="U66" s="90"/>
+      <c r="V66" s="90"/>
+      <c r="W66" s="90"/>
+      <c r="X66" s="90"/>
+      <c r="Y66" s="90"/>
+      <c r="Z66" s="90"/>
+      <c r="AA66" s="90"/>
+      <c r="AB66" s="90"/>
+      <c r="AC66" s="90"/>
+      <c r="AD66" s="90"/>
+      <c r="AE66" s="90"/>
+      <c r="AF66" s="90"/>
+      <c r="AG66" s="90"/>
+      <c r="AH66" s="90"/>
+      <c r="AI66" s="90"/>
+      <c r="AJ66" s="90"/>
+      <c r="AK66" s="90"/>
+      <c r="AL66" s="90"/>
+      <c r="AM66" s="90"/>
+      <c r="AN66" s="90"/>
+      <c r="AO66" s="90"/>
+      <c r="AP66" s="90"/>
+      <c r="AQ66" s="90"/>
+      <c r="AR66" s="90"/>
+      <c r="AS66" s="90"/>
+      <c r="AT66" s="90"/>
+      <c r="AU66" s="90"/>
+      <c r="AV66" s="90"/>
+      <c r="AW66" s="90"/>
+      <c r="AX66" s="90"/>
+      <c r="AY66" s="90"/>
+    </row>
+    <row r="68" spans="2:51">
       <c r="B68" s="75" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="69" spans="2:51" x14ac:dyDescent="0.4">
-      <c r="B69" s="91" t="s">
+    <row r="69" spans="2:51">
+      <c r="B69" s="95" t="s">
         <v>276</v>
       </c>
-      <c r="C69" s="89"/>
-      <c r="D69" s="89"/>
-      <c r="E69" s="89"/>
-      <c r="F69" s="89"/>
-      <c r="G69" s="89"/>
-      <c r="H69" s="89"/>
-      <c r="I69" s="89"/>
-      <c r="J69" s="89"/>
-      <c r="K69" s="89"/>
-      <c r="L69" s="89"/>
-      <c r="M69" s="89"/>
-      <c r="N69" s="89"/>
-      <c r="O69" s="89"/>
-      <c r="P69" s="89"/>
-      <c r="Q69" s="89"/>
-      <c r="R69" s="89"/>
-      <c r="S69" s="89"/>
-      <c r="T69" s="89"/>
-      <c r="U69" s="89"/>
-      <c r="V69" s="89"/>
-      <c r="W69" s="89"/>
-      <c r="X69" s="89"/>
-      <c r="Y69" s="89"/>
-      <c r="Z69" s="89"/>
-      <c r="AA69" s="89"/>
-      <c r="AB69" s="89"/>
-      <c r="AC69" s="89"/>
-      <c r="AD69" s="89"/>
-      <c r="AE69" s="89"/>
-      <c r="AF69" s="89"/>
-      <c r="AG69" s="89"/>
-      <c r="AH69" s="89"/>
-      <c r="AI69" s="89"/>
-      <c r="AJ69" s="89"/>
-      <c r="AK69" s="89"/>
-      <c r="AL69" s="89"/>
-      <c r="AM69" s="89"/>
-      <c r="AN69" s="89"/>
-      <c r="AO69" s="89"/>
-      <c r="AP69" s="89"/>
-      <c r="AQ69" s="89"/>
-      <c r="AR69" s="89"/>
-      <c r="AS69" s="89"/>
-      <c r="AT69" s="89"/>
-      <c r="AU69" s="89"/>
-      <c r="AV69" s="89"/>
-      <c r="AW69" s="89"/>
-      <c r="AX69" s="89"/>
-      <c r="AY69" s="89"/>
-    </row>
-    <row r="70" spans="2:51" x14ac:dyDescent="0.4">
-      <c r="B70" s="89"/>
-      <c r="C70" s="89"/>
-      <c r="D70" s="89"/>
-      <c r="E70" s="89"/>
-      <c r="F70" s="89"/>
-      <c r="G70" s="89"/>
-      <c r="H70" s="89"/>
-      <c r="I70" s="89"/>
-      <c r="J70" s="89"/>
-      <c r="K70" s="89"/>
-      <c r="L70" s="89"/>
-      <c r="M70" s="89"/>
-      <c r="N70" s="89"/>
-      <c r="O70" s="89"/>
-      <c r="P70" s="89"/>
-      <c r="Q70" s="89"/>
-      <c r="R70" s="89"/>
-      <c r="S70" s="89"/>
-      <c r="T70" s="89"/>
-      <c r="U70" s="89"/>
-      <c r="V70" s="89"/>
-      <c r="W70" s="89"/>
-      <c r="X70" s="89"/>
-      <c r="Y70" s="89"/>
-      <c r="Z70" s="89"/>
-      <c r="AA70" s="89"/>
-      <c r="AB70" s="89"/>
-      <c r="AC70" s="89"/>
-      <c r="AD70" s="89"/>
-      <c r="AE70" s="89"/>
-      <c r="AF70" s="89"/>
-      <c r="AG70" s="89"/>
-      <c r="AH70" s="89"/>
-      <c r="AI70" s="89"/>
-      <c r="AJ70" s="89"/>
-      <c r="AK70" s="89"/>
-      <c r="AL70" s="89"/>
-      <c r="AM70" s="89"/>
-      <c r="AN70" s="89"/>
-      <c r="AO70" s="89"/>
-      <c r="AP70" s="89"/>
-      <c r="AQ70" s="89"/>
-      <c r="AR70" s="89"/>
-      <c r="AS70" s="89"/>
-      <c r="AT70" s="89"/>
-      <c r="AU70" s="89"/>
-      <c r="AV70" s="89"/>
-      <c r="AW70" s="89"/>
-      <c r="AX70" s="89"/>
-      <c r="AY70" s="89"/>
+      <c r="C69" s="90"/>
+      <c r="D69" s="90"/>
+      <c r="E69" s="90"/>
+      <c r="F69" s="90"/>
+      <c r="G69" s="90"/>
+      <c r="H69" s="90"/>
+      <c r="I69" s="90"/>
+      <c r="J69" s="90"/>
+      <c r="K69" s="90"/>
+      <c r="L69" s="90"/>
+      <c r="M69" s="90"/>
+      <c r="N69" s="90"/>
+      <c r="O69" s="90"/>
+      <c r="P69" s="90"/>
+      <c r="Q69" s="90"/>
+      <c r="R69" s="90"/>
+      <c r="S69" s="90"/>
+      <c r="T69" s="90"/>
+      <c r="U69" s="90"/>
+      <c r="V69" s="90"/>
+      <c r="W69" s="90"/>
+      <c r="X69" s="90"/>
+      <c r="Y69" s="90"/>
+      <c r="Z69" s="90"/>
+      <c r="AA69" s="90"/>
+      <c r="AB69" s="90"/>
+      <c r="AC69" s="90"/>
+      <c r="AD69" s="90"/>
+      <c r="AE69" s="90"/>
+      <c r="AF69" s="90"/>
+      <c r="AG69" s="90"/>
+      <c r="AH69" s="90"/>
+      <c r="AI69" s="90"/>
+      <c r="AJ69" s="90"/>
+      <c r="AK69" s="90"/>
+      <c r="AL69" s="90"/>
+      <c r="AM69" s="90"/>
+      <c r="AN69" s="90"/>
+      <c r="AO69" s="90"/>
+      <c r="AP69" s="90"/>
+      <c r="AQ69" s="90"/>
+      <c r="AR69" s="90"/>
+      <c r="AS69" s="90"/>
+      <c r="AT69" s="90"/>
+      <c r="AU69" s="90"/>
+      <c r="AV69" s="90"/>
+      <c r="AW69" s="90"/>
+      <c r="AX69" s="90"/>
+      <c r="AY69" s="90"/>
+    </row>
+    <row r="70" spans="2:51">
+      <c r="B70" s="90"/>
+      <c r="C70" s="90"/>
+      <c r="D70" s="90"/>
+      <c r="E70" s="90"/>
+      <c r="F70" s="90"/>
+      <c r="G70" s="90"/>
+      <c r="H70" s="90"/>
+      <c r="I70" s="90"/>
+      <c r="J70" s="90"/>
+      <c r="K70" s="90"/>
+      <c r="L70" s="90"/>
+      <c r="M70" s="90"/>
+      <c r="N70" s="90"/>
+      <c r="O70" s="90"/>
+      <c r="P70" s="90"/>
+      <c r="Q70" s="90"/>
+      <c r="R70" s="90"/>
+      <c r="S70" s="90"/>
+      <c r="T70" s="90"/>
+      <c r="U70" s="90"/>
+      <c r="V70" s="90"/>
+      <c r="W70" s="90"/>
+      <c r="X70" s="90"/>
+      <c r="Y70" s="90"/>
+      <c r="Z70" s="90"/>
+      <c r="AA70" s="90"/>
+      <c r="AB70" s="90"/>
+      <c r="AC70" s="90"/>
+      <c r="AD70" s="90"/>
+      <c r="AE70" s="90"/>
+      <c r="AF70" s="90"/>
+      <c r="AG70" s="90"/>
+      <c r="AH70" s="90"/>
+      <c r="AI70" s="90"/>
+      <c r="AJ70" s="90"/>
+      <c r="AK70" s="90"/>
+      <c r="AL70" s="90"/>
+      <c r="AM70" s="90"/>
+      <c r="AN70" s="90"/>
+      <c r="AO70" s="90"/>
+      <c r="AP70" s="90"/>
+      <c r="AQ70" s="90"/>
+      <c r="AR70" s="90"/>
+      <c r="AS70" s="90"/>
+      <c r="AT70" s="90"/>
+      <c r="AU70" s="90"/>
+      <c r="AV70" s="90"/>
+      <c r="AW70" s="90"/>
+      <c r="AX70" s="90"/>
+      <c r="AY70" s="90"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="oRew7oK5RrebL3ikYbb5mrrqCwtYk96SN7lm2yyxRaPIrPICb7DS7sYEbupYaTok13XO6PM3C0vgC2TZ6/xVQA==" saltValue="3tduD31ZVtNoKEQtwr17xQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
+    <mergeCell ref="B50:Z50"/>
+    <mergeCell ref="B59:P59"/>
+    <mergeCell ref="B60:Z60"/>
+    <mergeCell ref="B64:AY66"/>
+    <mergeCell ref="B69:AY70"/>
     <mergeCell ref="B49:P49"/>
     <mergeCell ref="B12:AY12"/>
     <mergeCell ref="B13:AY13"/>
     <mergeCell ref="B23:P23"/>
     <mergeCell ref="B24:Z24"/>
     <mergeCell ref="B40:AY40"/>
-    <mergeCell ref="B50:Z50"/>
-    <mergeCell ref="B59:P59"/>
-    <mergeCell ref="B60:Z60"/>
-    <mergeCell ref="B64:AY66"/>
-    <mergeCell ref="B69:AY70"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5428,7 +5428,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="30" style="10" customWidth="1"/>
     <col min="2" max="2" width="22.625" style="10" customWidth="1"/>
@@ -5439,17 +5439,17 @@
     <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A1" s="97" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="96"/>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1">
       <c r="A3" s="12" t="s">
         <v>40</v>
       </c>
@@ -5467,12 +5467,12 @@
       </c>
       <c r="F3" s="12"/>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="18.75" customHeight="1">
       <c r="A4" s="13" t="s">
         <v>44</v>
       </c>
       <c r="B4" s="20" t="str">
-        <f>IF(入力!B18="DC → 会社退職金","企業型DC",IF(入力!B18="会社退職金 → DC","会社退職金","要確認"))</f>
+        <f>IF(ISNUMBER(SEARCH("→ 会社退職金",入力!B18)),IF(入力!B6="DC","企業型DC","DB"),IF(ISNUMBER(SEARCH("会社退職金 →",入力!B18)),"会社退職金","要確認"))</f>
         <v>会社退職金</v>
       </c>
       <c r="C4" s="20" t="s">
@@ -5484,7 +5484,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1">
       <c r="A5" s="13" t="s">
         <v>47</v>
       </c>
@@ -5501,7 +5501,7 @@
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
     </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6" ht="18.75" customHeight="1">
       <c r="A6" s="13" t="s">
         <v>50</v>
       </c>
@@ -5518,7 +5518,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -5535,7 +5535,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1">
       <c r="A8" s="13" t="s">
         <v>54</v>
       </c>
@@ -5552,7 +5552,7 @@
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1">
       <c r="A9" s="13" t="s">
         <v>56</v>
       </c>
@@ -5569,7 +5569,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1">
       <c r="A10" s="13" t="s">
         <v>58</v>
       </c>
@@ -5586,7 +5586,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1">
       <c r="A11" s="13" t="s">
         <v>61</v>
       </c>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="F11" s="13"/>
     </row>
-    <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="37.5" customHeight="1">
       <c r="A12" s="13" t="s">
         <v>24</v>
       </c>
@@ -5622,7 +5622,7 @@
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>65</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1">
       <c r="A14" s="13" t="s">
         <v>68</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:6" ht="18.75" customHeight="1">
       <c r="A15" s="13" t="s">
         <v>71</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6" ht="18.75" customHeight="1">
       <c r="A16" s="10" t="s">
         <v>74</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" ht="18.75" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>25</v>
       </c>
@@ -5702,75 +5702,75 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="18.75" customHeight="1"/>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1">
       <c r="A19" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="99" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="96"/>
-      <c r="D19" s="96"/>
-      <c r="E19" s="96"/>
-      <c r="F19" s="96"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="96"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="96"/>
-      <c r="F20" s="96"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="96"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="96"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="96"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="95" t="s">
+      <c r="C19" s="97"/>
+      <c r="D19" s="97"/>
+      <c r="E19" s="97"/>
+      <c r="F19" s="97"/>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" customHeight="1">
+      <c r="B20" s="97"/>
+      <c r="C20" s="97"/>
+      <c r="D20" s="97"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1">
+      <c r="B21" s="97"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="97"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1"/>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1">
+      <c r="A23" s="96" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="97"/>
+      <c r="C23" s="97"/>
+      <c r="D23" s="97"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1">
       <c r="A24" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="98" t="s">
+      <c r="B24" s="99" t="s">
         <v>224</v>
       </c>
-      <c r="C24" s="96"/>
-      <c r="D24" s="96"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C24" s="97"/>
+      <c r="D24" s="97"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1">
       <c r="A25" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="98" t="s">
+      <c r="B25" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="96"/>
-      <c r="D25" s="96"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C25" s="97"/>
+      <c r="D25" s="97"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1">
       <c r="A26" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="98" t="s">
+      <c r="B26" s="99" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="96"/>
-      <c r="D26" s="96"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+      <c r="C26" s="97"/>
+      <c r="D26" s="97"/>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kU4JOACS7Y3snHZ24/jj0LHhgUwg7xncxnwlDuGM1kNo48B59v7PE5ExkbivON7oeLgPf53g5D23s7Yr/U2LKQ==" saltValue="t1IHPnrwDjMu6919k/85Ig==" spinCount="100000" sheet="1" selectLockedCells="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="RL8xUoJgQXr1o0YCUzHa1TR5jGiwEormafv3pgBz5bAwpR0uYdjHMctOBkQSE8cnspnulXwIKRl4qUNlj3YcNg==" saltValue="Qor62r+Udy9XQqoKoo04LQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="6">
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A1:F1"/>
@@ -5788,7 +5788,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="10" customWidth="1"/>
     <col min="2" max="2" width="13" style="10" customWidth="1"/>
@@ -5822,21 +5822,21 @@
     <col min="44" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="24" x14ac:dyDescent="0.5">
-      <c r="A1" s="99" t="s">
+    <row r="1" spans="1:43" ht="24">
+      <c r="A1" s="84" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="99"/>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
-    </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.4">
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="J1" s="84"/>
+    </row>
+    <row r="2" spans="1:43">
       <c r="A2" s="11" t="s">
         <v>86</v>
       </c>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="AN2" s="10"/>
     </row>
-    <row r="3" spans="1:43" ht="60" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:43" ht="60" customHeight="1">
       <c r="A3" s="22" t="s">
         <v>87</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:43" ht="18.75" customHeight="1">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -6008,12 +6008,12 @@
   OR(G4="同年受取",G4=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G4)),
     入力!$B$15,
     IF(
-      G4="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G4)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -6057,14 +6057,14 @@
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
      IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(G4="DC → 会社退職金",
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G4)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B4,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(G4="会社退職金 → DC",
+         IF(ISNUMBER(SEARCH("会社退職金 →",G4)),
            _xlpm.会勤年,
            ""
          )
@@ -6076,7 +6076,18 @@
         <v/>
       </c>
       <c r="N4" s="30" t="str">
-        <f>IF(G4="同年受取","",IF(I4&lt;&gt;"対象","",MAX(IF(G4="DC → 会社退職金",入力!$B$11,入力!$B$7),IF(G4="DC → 会社退職金",入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G4="同年受取",
+  "",
+  IF(
+    I4&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G4)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G4)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v/>
       </c>
       <c r="O4" s="30" t="str">
@@ -6088,19 +6099,19 @@
   _xlpm.前換算年,M4,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B4,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B4,
   _xlpm.重複終了上限,IF(
-    _xlpm.受取順="DC → 会社退職金",
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        _xlpm.受取順="DC → 会社退職金",
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -6150,7 +6161,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-_xlpm.受取順="DC → 会社退職金",
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I4="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -6257,7 +6268,19 @@
         <v/>
       </c>
       <c r="AG4" s="32" t="str">
-        <f>IF(OR(J4="",K4="",G4="同年受取"),"",IF(J4&lt;K4,AF4,IF(G4="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J4="",K4="",G4="同年受取"),
+  "",
+  IF(
+    J4&lt;K4,
+    AF4,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G4)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v/>
       </c>
       <c r="AH4" s="33">
@@ -6317,7 +6340,7 @@
         <v>25695348</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:43" ht="18.75" customHeight="1">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -6348,12 +6371,12 @@
   OR(G5="同年受取",G5=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G5)),
     入力!$B$15,
     IF(
-      G5="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G5)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -6390,22 +6413,21 @@
       </c>
       <c r="M5" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L5,
  _xlpm.前退,J5,
  _xlpm.前控,K5,
  _xlpm.会勤年,入力!$B$20,
  IF(G5="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G5)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G5)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B5,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G5)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G5)),
            _xlpm.会勤年,
            ""
          )
@@ -6417,7 +6439,18 @@
         <v>2</v>
       </c>
       <c r="N5" s="30">
-        <f>IF(G5="同年受取","",IF(I5&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G5)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G5)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G5="同年受取",
+  "",
+  IF(
+    I5&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G5)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G5)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O5" s="30">
@@ -6429,19 +6462,19 @@
   _xlpm.前換算年,M5,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B5,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B5,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -6479,7 +6512,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I5="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -6586,7 +6619,19 @@
         <v>2</v>
       </c>
       <c r="AG5" s="32">
-        <f>IF(OR(J5="",K5="",G5="同年受取"),"",IF(J5&lt;K5,AF5,IF(G5="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J5="",K5="",G5="同年受取"),
+  "",
+  IF(
+    J5&lt;K5,
+    AF5,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G5)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH5" s="33" t="str">
@@ -6646,7 +6691,7 @@
         <v>25021948</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:43" ht="18.75" customHeight="1">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -6677,12 +6722,12 @@
   OR(G6="同年受取",G6=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G6)),
     入力!$B$15,
     IF(
-      G6="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G6)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -6719,22 +6764,21 @@
       </c>
       <c r="M6" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L6,
  _xlpm.前退,J6,
  _xlpm.前控,K6,
  _xlpm.会勤年,入力!$B$20,
  IF(G6="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G6)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G6)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B6,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G6)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G6)),
            _xlpm.会勤年,
            ""
          )
@@ -6746,7 +6790,18 @@
         <v>2</v>
       </c>
       <c r="N6" s="30">
-        <f>IF(G6="同年受取","",IF(I6&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G6)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G6)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G6="同年受取",
+  "",
+  IF(
+    I6&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G6)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G6)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O6" s="30">
@@ -6758,19 +6813,19 @@
   _xlpm.前換算年,M6,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B6,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B6,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -6808,7 +6863,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I6="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -6915,7 +6970,19 @@
         <v>2</v>
       </c>
       <c r="AG6" s="32">
-        <f>IF(OR(J6="",K6="",G6="同年受取"),"",IF(J6&lt;K6,AF6,IF(G6="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J6="",K6="",G6="同年受取"),
+  "",
+  IF(
+    J6&lt;K6,
+    AF6,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G6)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH6" s="33" t="str">
@@ -6975,7 +7042,7 @@
         <v>25128418</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:43" ht="18.75" customHeight="1">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -7006,12 +7073,12 @@
   OR(G7="同年受取",G7=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G7)),
     入力!$B$15,
     IF(
-      G7="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G7)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -7048,22 +7115,21 @@
       </c>
       <c r="M7" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L7,
  _xlpm.前退,J7,
  _xlpm.前控,K7,
  _xlpm.会勤年,入力!$B$20,
  IF(G7="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G7)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G7)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B7,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G7)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G7)),
            _xlpm.会勤年,
            ""
          )
@@ -7075,7 +7141,18 @@
         <v>2</v>
       </c>
       <c r="N7" s="30">
-        <f>IF(G7="同年受取","",IF(I7&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G7)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G7)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G7="同年受取",
+  "",
+  IF(
+    I7&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G7)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G7)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O7" s="30">
@@ -7087,19 +7164,19 @@
   _xlpm.前換算年,M7,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B7,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B7,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -7137,7 +7214,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I7="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -7244,7 +7321,19 @@
         <v>2</v>
       </c>
       <c r="AG7" s="32">
-        <f>IF(OR(J7="",K7="",G7="同年受取"),"",IF(J7&lt;K7,AF7,IF(G7="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J7="",K7="",G7="同年受取"),
+  "",
+  IF(
+    J7&lt;K7,
+    AF7,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G7)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH7" s="33" t="str">
@@ -7304,7 +7393,7 @@
         <v>25234888</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:43" ht="18.75" customHeight="1">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -7335,12 +7424,12 @@
   OR(G8="同年受取",G8=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G8)),
     入力!$B$15,
     IF(
-      G8="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G8)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -7377,22 +7466,21 @@
       </c>
       <c r="M8" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L8,
  _xlpm.前退,J8,
  _xlpm.前控,K8,
  _xlpm.会勤年,入力!$B$20,
  IF(G8="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G8)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G8)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B8,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G8)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G8)),
            _xlpm.会勤年,
            ""
          )
@@ -7404,7 +7492,18 @@
         <v>2</v>
       </c>
       <c r="N8" s="30">
-        <f>IF(G8="同年受取","",IF(I8&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G8)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G8)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G8="同年受取",
+  "",
+  IF(
+    I8&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G8)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G8)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O8" s="30">
@@ -7416,19 +7515,19 @@
   _xlpm.前換算年,M8,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B8,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B8,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -7466,7 +7565,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I8="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -7573,7 +7672,19 @@
         <v>2</v>
       </c>
       <c r="AG8" s="32">
-        <f>IF(OR(J8="",K8="",G8="同年受取"),"",IF(J8&lt;K8,AF8,IF(G8="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J8="",K8="",G8="同年受取"),
+  "",
+  IF(
+    J8&lt;K8,
+    AF8,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G8)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH8" s="33" t="str">
@@ -7633,7 +7744,7 @@
         <v>25341358</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:43" ht="18.75" customHeight="1">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -7664,12 +7775,12 @@
   OR(G9="同年受取",G9=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G9)),
     入力!$B$15,
     IF(
-      G9="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G9)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -7706,22 +7817,21 @@
       </c>
       <c r="M9" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L9,
  _xlpm.前退,J9,
  _xlpm.前控,K9,
  _xlpm.会勤年,入力!$B$20,
  IF(G9="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G9)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G9)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B9,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G9)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G9)),
            _xlpm.会勤年,
            ""
          )
@@ -7733,7 +7843,18 @@
         <v>2</v>
       </c>
       <c r="N9" s="30">
-        <f>IF(G9="同年受取","",IF(I9&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G9)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G9)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G9="同年受取",
+  "",
+  IF(
+    I9&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G9)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G9)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O9" s="30">
@@ -7745,19 +7866,19 @@
   _xlpm.前換算年,M9,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B9,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B9,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -7795,7 +7916,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I9="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -7902,7 +8023,19 @@
         <v>2</v>
       </c>
       <c r="AG9" s="32">
-        <f>IF(OR(J9="",K9="",G9="同年受取"),"",IF(J9&lt;K9,AF9,IF(G9="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J9="",K9="",G9="同年受取"),
+  "",
+  IF(
+    J9&lt;K9,
+    AF9,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G9)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH9" s="33" t="str">
@@ -7962,7 +8095,7 @@
         <v>25442723</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:43" ht="18.75" customHeight="1">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -7993,12 +8126,12 @@
   OR(G10="同年受取",G10=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G10)),
     入力!$B$15,
     IF(
-      G10="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G10)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -8035,22 +8168,21 @@
       </c>
       <c r="M10" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L10,
  _xlpm.前退,J10,
  _xlpm.前控,K10,
  _xlpm.会勤年,入力!$B$20,
  IF(G10="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G10)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G10)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B10,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G10)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G10)),
            _xlpm.会勤年,
            ""
          )
@@ -8062,7 +8194,18 @@
         <v>2</v>
       </c>
       <c r="N10" s="30">
-        <f>IF(G10="同年受取","",IF(I10&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G10)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G10)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G10="同年受取",
+  "",
+  IF(
+    I10&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G10)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G10)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O10" s="30">
@@ -8074,19 +8217,19 @@
   _xlpm.前換算年,M10,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B10,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B10,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -8124,7 +8267,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I10="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -8231,7 +8374,19 @@
         <v>2</v>
       </c>
       <c r="AG10" s="32">
-        <f>IF(OR(J10="",K10="",G10="同年受取"),"",IF(J10&lt;K10,AF10,IF(G10="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J10="",K10="",G10="同年受取"),
+  "",
+  IF(
+    J10&lt;K10,
+    AF10,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G10)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH10" s="33" t="str">
@@ -8291,7 +8446,7 @@
         <v>25513458</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:43" ht="18.75" customHeight="1">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -8322,12 +8477,12 @@
   OR(G11="同年受取",G11=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G11)),
     入力!$B$15,
     IF(
-      G11="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G11)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -8364,22 +8519,21 @@
       </c>
       <c r="M11" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L11,
  _xlpm.前退,J11,
  _xlpm.前控,K11,
  _xlpm.会勤年,入力!$B$20,
  IF(G11="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G11)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G11)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B11,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G11)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G11)),
            _xlpm.会勤年,
            ""
          )
@@ -8391,7 +8545,18 @@
         <v>2</v>
       </c>
       <c r="N11" s="30">
-        <f>IF(G11="同年受取","",IF(I11&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G11)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G11)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G11="同年受取",
+  "",
+  IF(
+    I11&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G11)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G11)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O11" s="30">
@@ -8403,19 +8568,19 @@
   _xlpm.前換算年,M11,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B11,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B11,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -8453,7 +8618,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I11="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -8560,7 +8725,19 @@
         <v>2</v>
       </c>
       <c r="AG11" s="32">
-        <f>IF(OR(J11="",K11="",G11="同年受取"),"",IF(J11&lt;K11,AF11,IF(G11="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J11="",K11="",G11="同年受取"),
+  "",
+  IF(
+    J11&lt;K11,
+    AF11,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G11)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH11" s="33" t="str">
@@ -8620,7 +8797,7 @@
         <v>25584193</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:43" ht="18.75" customHeight="1">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -8651,12 +8828,12 @@
   OR(G12="同年受取",G12=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G12)),
     入力!$B$15,
     IF(
-      G12="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G12)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -8693,22 +8870,21 @@
       </c>
       <c r="M12" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L12,
  _xlpm.前退,J12,
  _xlpm.前控,K12,
  _xlpm.会勤年,入力!$B$20,
  IF(G12="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G12)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G12)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B12,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G12)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G12)),
            _xlpm.会勤年,
            ""
          )
@@ -8720,7 +8896,18 @@
         <v>2</v>
       </c>
       <c r="N12" s="30">
-        <f>IF(G12="同年受取","",IF(I12&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G12)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G12)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G12="同年受取",
+  "",
+  IF(
+    I12&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G12)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G12)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O12" s="30">
@@ -8732,19 +8919,19 @@
   _xlpm.前換算年,M12,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B12,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B12,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -8782,7 +8969,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I12="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -8889,7 +9076,19 @@
         <v>2</v>
       </c>
       <c r="AG12" s="32">
-        <f>IF(OR(J12="",K12="",G12="同年受取"),"",IF(J12&lt;K12,AF12,IF(G12="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J12="",K12="",G12="同年受取"),
+  "",
+  IF(
+    J12&lt;K12,
+    AF12,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G12)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH12" s="33" t="str">
@@ -8949,7 +9148,7 @@
         <v>25654928</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:43" ht="18.75" customHeight="1">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -8980,12 +9179,12 @@
   OR(G13="同年受取",G13=""),
   "",
   IF(
-    入力!$B$6="DB",
+    ISNUMBER(SEARCH("→ 会社退職金",G13)),
     入力!$B$15,
     IF(
-      G13="DC → 会社退職金",
-      入力!$B$15,
-      入力!$B$16
+      ISNUMBER(SEARCH("会社退職金 →",G13)),
+      入力!$B$16,
+      ""
     )
   )
 )</f>
@@ -9022,22 +9221,21 @@
       </c>
       <c r="M13" s="29">
         <f>_xlfn.LET(
- _xlpm.前判定,L13,
  _xlpm.前退,J13,
  _xlpm.前控,K13,
  _xlpm.会勤年,入力!$B$20,
  IF(G13="同年受取","",
    IF(OR(_xlpm.前退="",_xlpm.前控=""),"",
-     IF(_xlpm.前判定="該当",
+     IF(_xlpm.前退&lt;_xlpm.前控,
        ROUNDDOWN(IF(_xlpm.前退&lt;=8000000,_xlpm.前退/400000,(_xlpm.前退-8000000)/700000+20),0),
-       IF(ISNUMBER(SEARCH(" → 会社退職金",G13)),
+       IF(ISNUMBER(SEARCH("→ 会社退職金",G13)),
          _xlfn.LET(
            _xlpm.DC開始,入力!$B$11,
            _xlpm.DC終了,B13,
            DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"Y")
            +IF(DATEDIF(_xlpm.DC開始,_xlpm.DC終了+1,"YD")&gt;0,1,0)
          ),
-         IF(ISNUMBER(SEARCH("会社退職金 → ",G13)),
+         IF(ISNUMBER(SEARCH("会社退職金 →",G13)),
            _xlpm.会勤年,
            ""
          )
@@ -9049,7 +9247,18 @@
         <v>2</v>
       </c>
       <c r="N13" s="30">
-        <f>IF(G13="同年受取","",IF(I13&lt;&gt;"対象","",MAX(IF(ISNUMBER(SEARCH(" → 会社退職金",G13)),入力!$B$11,入力!$B$7),IF(ISNUMBER(SEARCH(" → 会社退職金",G13)),入力!$B$7,入力!$B$11))))</f>
+        <f>IF(
+  G13="同年受取",
+  "",
+  IF(
+    I13&lt;&gt;"対象",
+    "",
+    MAX(
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G13)),入力!$B$11,入力!$B$7),
+      IF(ISNUMBER(SEARCH("→ 会社退職金",G13)),入力!$B$7,入力!$B$11)
+    )
+  )
+)</f>
         <v>36982</v>
       </c>
       <c r="O13" s="30">
@@ -9061,19 +9270,19 @@
   _xlpm.前換算年,M13,
   _xlpm.会社開始,入力!$B$7,
   _xlpm.会社終了,入力!$B$8,
-  _xlpm.DC開始,入力!$B$11,
-  _xlpm.DC終了,B13,
+  _xlpm.対象制度開始,入力!$B$11,
+  _xlpm.対象制度終了,B13,
   _xlpm.重複終了上限,IF(
-    ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-    _xlpm.DC終了,
+    ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+    _xlpm.対象制度終了,
     _xlpm.会社終了
   ),
   _xlpm.換算期間終了,IF(
     _xlpm.前退&lt;_xlpm.前控,
     EDATE(
       IF(
-        ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
-        _xlpm.DC開始,
+        ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
+        _xlpm.対象制度開始,
         _xlpm.会社開始
       ),
       _xlpm.前換算年*12
@@ -9111,7 +9320,7 @@
 8000000+700000*(_xlpm.実重複年-20)
 ),
 IF(
-ISNUMBER(SEARCH(" → 会社退職金",_xlpm.受取順)),
+ISNUMBER(SEARCH("→ 会社退職金",_xlpm.受取順)),
 IF(
 I13="対象",
 MAX(0,_xlpm.会社本来控除-_xlpm.重複控除),
@@ -9218,7 +9427,19 @@
         <v>2</v>
       </c>
       <c r="AG13" s="32">
-        <f>IF(OR(J13="",K13="",G13="同年受取"),"",IF(J13&lt;K13,AF13,IF(G13="DC → 会社退職金",入力!$B$22,入力!$B$20)))</f>
+        <f>IF(
+  OR(J13="",K13="",G13="同年受取"),
+  "",
+  IF(
+    J13&lt;K13,
+    AF13,
+    IF(
+      ISNUMBER(SEARCH("→ 会社退職金",G13)),
+      入力!$B$22,
+      入力!$B$20
+    )
+  )
+)</f>
         <v>2</v>
       </c>
       <c r="AH13" s="33" t="str">
@@ -9278,16 +9499,16 @@
         <v>25720558</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:43">
       <c r="AJ14" s="11"/>
     </row>
-    <row r="15" spans="1:43" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:43" ht="19.5">
       <c r="A15" s="36" t="s">
         <v>115</v>
       </c>
       <c r="O15" s="37"/>
     </row>
-    <row r="16" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:43" ht="18.75" customHeight="1">
       <c r="A16" s="38" t="s">
         <v>116</v>
       </c>
@@ -9303,7 +9524,7 @@
       <c r="I16" s="40"/>
       <c r="J16" s="40"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10">
       <c r="B17" s="40"/>
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
@@ -9314,7 +9535,7 @@
       <c r="I17" s="40"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10">
       <c r="B18" s="40"/>
       <c r="C18" s="40"/>
       <c r="D18" s="40"/>
@@ -9325,7 +9546,7 @@
       <c r="I18" s="40"/>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10">
       <c r="A19" s="41" t="s">
         <v>118</v>
       </c>
@@ -9333,7 +9554,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10">
       <c r="A20" s="41" t="s">
         <v>194</v>
       </c>
@@ -9341,19 +9562,19 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10">
       <c r="A21" s="41"/>
       <c r="C21" s="39" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10">
       <c r="A22" s="41"/>
       <c r="C22" s="39" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10">
       <c r="A23" s="41" t="s">
         <v>120</v>
       </c>
@@ -9361,7 +9582,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10">
       <c r="A24" s="41" t="s">
         <v>122</v>
       </c>
@@ -9369,7 +9590,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" ht="19.5">
       <c r="A25" s="41" t="s">
         <v>124</v>
       </c>
@@ -9378,12 +9599,12 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="zyqE/1b6GfRmEB1h+XpUqOyNjFVGqw7dbe2Fu2wnPV6dzq89sznv0Rk4DLpmtOebi1nQA++Kw1ipoFJitHHnxg==" saltValue="CMXh4bEllpPSsubu6DKZTg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="KXrpTWvyWdh5+hrcE5AyRiaoK9Wtey40U6km79OjKFmdLN6F04KVZoIsRClob8fKYAjEUfDqxbrKcz0pfZ2vow==" saltValue="Xh5CyF+qt3k+tbnCarxJ2w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:C13" xr:uid="{5475A85F-6272-4C07-AB27-853C2D0B5070}">
       <formula1>1</formula1>
       <formula2>2958465</formula2>
@@ -9400,7 +9621,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="18" style="10" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="10" bestFit="1" customWidth="1"/>
@@ -9420,17 +9641,17 @@
     <col min="23" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25">
       <c r="A1" s="10" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:25">
       <c r="A3" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:25">
       <c r="A4" s="43" t="s">
         <v>127</v>
       </c>
@@ -9438,7 +9659,7 @@
         <v>25689</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:25">
       <c r="A5" s="43" t="s">
         <v>128</v>
       </c>
@@ -9446,7 +9667,7 @@
         <v>33329</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25">
       <c r="A6" s="43" t="s">
         <v>129</v>
       </c>
@@ -9461,7 +9682,7 @@
         <v>60歳0ヶ月</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25">
       <c r="A7" s="43" t="s">
         <v>131</v>
       </c>
@@ -9470,7 +9691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:25">
       <c r="A8" s="43" t="s">
         <v>120</v>
       </c>
@@ -9482,7 +9703,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:25">
       <c r="A9" s="43" t="s">
         <v>133</v>
       </c>
@@ -9490,7 +9711,7 @@
         <v>22010000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:25">
       <c r="A10" s="43" t="s">
         <v>122</v>
       </c>
@@ -9502,7 +9723,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:25">
       <c r="A11" s="43" t="s">
         <v>135</v>
       </c>
@@ -9517,7 +9738,7 @@
       <c r="S11" s="47"/>
       <c r="T11" s="47"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:25">
       <c r="A12" s="43" t="s">
         <v>137</v>
       </c>
@@ -9546,7 +9767,7 @@
       <c r="X12" s="47"/>
       <c r="Y12" s="47"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:25">
       <c r="A13" s="43" t="s">
         <v>141</v>
       </c>
@@ -9581,7 +9802,7 @@
       <c r="X13" s="47"/>
       <c r="Y13" s="47"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:25">
       <c r="A14" s="43" t="s">
         <v>148</v>
       </c>
@@ -9616,7 +9837,7 @@
       <c r="X14" s="47"/>
       <c r="Y14" s="47"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:25">
       <c r="A15" s="43" t="s">
         <v>106</v>
       </c>
@@ -9647,7 +9868,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:25">
       <c r="A16" s="43" t="s">
         <v>153</v>
       </c>
@@ -9679,7 +9900,7 @@
       <c r="X16" s="47"/>
       <c r="Y16" s="47"/>
     </row>
-    <row r="17" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:25">
       <c r="B17" s="34"/>
       <c r="N17" s="53"/>
       <c r="O17" s="54" t="s">
@@ -9703,7 +9924,7 @@
       <c r="X17" s="47"/>
       <c r="Y17" s="47"/>
     </row>
-    <row r="18" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:25">
       <c r="N18" s="48" t="s">
         <v>163</v>
       </c>
@@ -9728,7 +9949,7 @@
       <c r="X18" s="47"/>
       <c r="Y18" s="47"/>
     </row>
-    <row r="19" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:25">
       <c r="N19" s="47"/>
       <c r="O19" s="47"/>
       <c r="P19" s="47"/>
@@ -9749,7 +9970,7 @@
       <c r="X19" s="47"/>
       <c r="Y19" s="47"/>
     </row>
-    <row r="20" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:25">
       <c r="N20" s="47"/>
       <c r="O20" s="47"/>
       <c r="P20" s="47"/>
@@ -9770,7 +9991,7 @@
       <c r="X20" s="47"/>
       <c r="Y20" s="47"/>
     </row>
-    <row r="21" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:25">
       <c r="N21" s="47"/>
       <c r="O21" s="47"/>
       <c r="P21" s="47"/>
@@ -9779,57 +10000,57 @@
       <c r="X21" s="47"/>
       <c r="Y21" s="47"/>
     </row>
-    <row r="22" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:25">
       <c r="W22" s="47"/>
       <c r="X22" s="47"/>
       <c r="Y22" s="47"/>
     </row>
-    <row r="23" spans="2:25" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:25">
       <c r="W23" s="47"/>
       <c r="X23" s="47"/>
       <c r="Y23" s="47"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:1">
       <c r="A33" s="11" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:1">
       <c r="A34" s="11" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:1">
       <c r="A35" s="55" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:1">
       <c r="A36" s="11" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:1">
       <c r="A37" s="55" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:1">
       <c r="A38" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:1">
       <c r="A39" s="55" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:1">
       <c r="A40" s="11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:1">
       <c r="A41" s="55" t="s">
         <v>175</v>
       </c>
@@ -9859,14 +10080,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="38" style="2" customWidth="1"/>
     <col min="2" max="2" width="42" style="2" customWidth="1"/>
     <col min="3" max="6" width="20" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="24">
       <c r="A1" s="100" t="s">
         <v>176</v>
       </c>
@@ -9874,7 +10095,7 @@
       <c r="C1" s="101"/>
       <c r="D1" s="101"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>177</v>
       </c>
@@ -9886,21 +10107,21 @@
       <c r="E3" s="101"/>
       <c r="F3" s="101"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6">
       <c r="B4" s="101"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="101"/>
       <c r="F4" s="101"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6">
       <c r="B5" s="101"/>
       <c r="C5" s="101"/>
       <c r="D5" s="101"/>
       <c r="E5" s="101"/>
       <c r="F5" s="101"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
         <v>179</v>
       </c>
@@ -9910,17 +10131,17 @@
       <c r="C6" s="101"/>
       <c r="D6" s="101"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6">
       <c r="B7" s="101"/>
       <c r="C7" s="101"/>
       <c r="D7" s="101"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:6">
       <c r="B8" s="101"/>
       <c r="C8" s="101"/>
       <c r="D8" s="101"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
         <v>181</v>
       </c>
@@ -9932,21 +10153,21 @@
       <c r="E9" s="101"/>
       <c r="F9" s="101"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:6">
       <c r="B10" s="101"/>
       <c r="C10" s="101"/>
       <c r="D10" s="101"/>
       <c r="E10" s="101"/>
       <c r="F10" s="101"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6">
       <c r="B11" s="101"/>
       <c r="C11" s="101"/>
       <c r="D11" s="101"/>
       <c r="E11" s="101"/>
       <c r="F11" s="101"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
         <v>183</v>
       </c>
@@ -9956,21 +10177,21 @@
       <c r="E12" s="101"/>
       <c r="F12" s="101"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:6">
       <c r="B13" s="101"/>
       <c r="C13" s="101"/>
       <c r="D13" s="101"/>
       <c r="E13" s="101"/>
       <c r="F13" s="101"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6">
       <c r="B14" s="101"/>
       <c r="C14" s="101"/>
       <c r="D14" s="101"/>
       <c r="E14" s="101"/>
       <c r="F14" s="101"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
         <v>184</v>
       </c>
@@ -9978,7 +10199,7 @@
       <c r="C16" s="101"/>
       <c r="D16" s="101"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>185</v>
       </c>
@@ -9988,7 +10209,7 @@
       <c r="C17" s="103"/>
       <c r="D17" s="103"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>186</v>
       </c>
@@ -9998,22 +10219,22 @@
       <c r="C18" s="103"/>
       <c r="D18" s="103"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4">
       <c r="A20"/>
       <c r="B20" s="9" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4">
       <c r="A21"/>
       <c r="B21"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4">
       <c r="A22"/>
       <c r="B22"/>
     </row>
@@ -10044,13 +10265,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
     <col min="2" max="3" width="12" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" s="56" t="s">
         <v>188</v>
       </c>
@@ -10061,7 +10282,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3">
       <c r="A2" s="58">
         <v>0</v>
       </c>
@@ -10072,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3">
       <c r="A3" s="58">
         <v>1950000</v>
       </c>
@@ -10083,7 +10304,7 @@
         <v>97500</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3">
       <c r="A4" s="58">
         <v>3300000</v>
       </c>
@@ -10094,7 +10315,7 @@
         <v>427500</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3">
       <c r="A5" s="58">
         <v>6950000</v>
       </c>
@@ -10105,7 +10326,7 @@
         <v>636000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3">
       <c r="A6" s="58">
         <v>9000000</v>
       </c>
@@ -10116,7 +10337,7 @@
         <v>1536000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3">
       <c r="A7" s="58">
         <v>18000000</v>
       </c>
@@ -10127,7 +10348,7 @@
         <v>2796000</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3">
       <c r="A8" s="58">
         <v>40000000</v>
       </c>

--- a/退職金_DC・DB_重複調整シミュレーション.xlsx
+++ b/退職金_DC・DB_重複調整シミュレーション.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\personal\克彦\40_個人年金\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F43D8E-F7D3-478B-B218-CA857ADF0C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972220A6-E492-45B0-9B8F-908E36561603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="xDy3cd6TjsApx1SYHegDGF3A84e1AD38me84/BeuVDCiF8QUyic1TygQQScbJfuh4omJj/k1OOWDR6319YaKYw==" workbookSaltValue="nU/5cJljJzN7UnsxmBLLvg==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -1270,7 +1270,7 @@
     <numFmt numFmtId="180" formatCode="0&quot;年&quot;"/>
     <numFmt numFmtId="181" formatCode="0_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1899,10 +1899,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
@@ -1919,18 +1915,18 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1945,6 +1941,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2004,7 +2004,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4471"/>
+                  <a14:cameraTool cellRange="$R$12:$T$20" spid="_x0000_s4474"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2069,7 +2069,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4472"/>
+                  <a14:cameraTool cellRange="$N$12:$O$18" spid="_x0000_s4475"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2134,7 +2134,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4473"/>
+                  <a14:cameraTool cellRange="$V$12:$V$15" spid="_x0000_s4476"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -2492,7 +2492,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F38"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" style="10" customWidth="1"/>
     <col min="2" max="2" width="22.25" style="10" customWidth="1"/>
@@ -2503,24 +2503,24 @@
     <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="85" t="s">
         <v>213</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="10" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3" s="10" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5" s="12" t="s">
         <v>0</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="10" t="s">
         <v>210</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>3</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>25689</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>5</v>
       </c>
@@ -2577,7 +2577,7 @@
         <v>60歳0ヶ月</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>6</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>8</v>
       </c>
@@ -2599,7 +2599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="str">
         <f>$B$6&amp;"の控除計算用加入開始日"</f>
         <v>DCの控除計算用加入開始日</v>
@@ -2611,7 +2611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1">
+    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="str">
         <f>$B$6&amp;"の控除計算用加入終了日"</f>
         <v>DCの控除計算用加入終了日</v>
@@ -2630,7 +2630,7 @@
         <v>65歳0ヶ月</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="str">
         <f>$B$6&amp;"一時金の受取日"</f>
         <v>DC一時金の受取日</v>
@@ -2642,7 +2642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="str">
         <f>$B$6&amp;"一時金額"</f>
         <v>DC一時金額</v>
@@ -2654,7 +2654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15" s="10" t="str">
         <f>B6&amp;"→会社退職金の調整対象期間"</f>
         <v>DC→会社退職金の調整対象期間</v>
@@ -2668,7 +2668,7 @@
         <v>DC一時金を先に受け取る場合、2026年1月1日以後に支払を受けたDC一時金について、国税庁の定める条件に該当する前年以前9年内の退職手当等が調整対象となります。</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="13" t="str">
         <f>"会社退職金→"&amp;B6&amp;"の調整対象期間"</f>
         <v>会社退職金→DCの調整対象期間</v>
@@ -2682,12 +2682,12 @@
         <v>会社退職金を先に受け取り、DC一時金を後で受け取る場合は19年の取扱い。</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="18.75" customHeight="1">
+    <row r="17" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="18.75" customHeight="1">
+    <row r="18" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="10" t="s">
         <v>14</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="18.75" customHeight="1">
+    <row r="19" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="12" t="s">
         <v>16</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="18.75" customHeight="1">
+    <row r="20" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13" t="s">
         <v>19</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="18.75" customHeight="1">
+    <row r="21" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="13" t="s">
         <v>21</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="18.75" customHeight="1">
+    <row r="22" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="13" t="str">
         <f>$B$6&amp;"の加入年数"</f>
         <v>DCの加入年数</v>
@@ -2747,7 +2747,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="18.75" customHeight="1">
+    <row r="23" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13" t="str">
         <f>$B$6&amp;"の退職所得控除額"</f>
         <v>DCの退職所得控除額</v>
@@ -2760,7 +2760,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>25</v>
       </c>
@@ -2768,111 +2768,111 @@
         <v>216</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="48" customHeight="1">
+    <row r="25" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="85" t="s">
+      <c r="B25" s="84" t="s">
         <v>217</v>
       </c>
-      <c r="C25" s="85"/>
-    </row>
-    <row r="27" spans="1:4" ht="18.75" customHeight="1">
+      <c r="C25" s="84"/>
+    </row>
+    <row r="27" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="85" t="s">
+      <c r="B27" s="84" t="s">
         <v>218</v>
       </c>
-      <c r="C27" s="85"/>
+      <c r="C27" s="84"/>
       <c r="D27" s="13"/>
     </row>
-    <row r="28" spans="1:4">
-      <c r="B28" s="85"/>
-      <c r="C28" s="85"/>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B28" s="84"/>
+      <c r="C28" s="84"/>
       <c r="D28" s="13"/>
     </row>
-    <row r="29" spans="1:4">
-      <c r="B29" s="87"/>
-      <c r="C29" s="87"/>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="B29" s="86"/>
+      <c r="C29" s="86"/>
       <c r="D29" s="13"/>
     </row>
-    <row r="30" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A30" s="88" t="s">
+    <row r="30" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="88"/>
-      <c r="C30" s="88"/>
-    </row>
-    <row r="31" spans="1:4" ht="54.95" customHeight="1">
+      <c r="B30" s="87"/>
+      <c r="C30" s="87"/>
+    </row>
+    <row r="31" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="85" t="s">
+      <c r="B31" s="84" t="s">
         <v>219</v>
       </c>
-      <c r="C31" s="85"/>
-    </row>
-    <row r="32" spans="1:4" ht="54.95" customHeight="1">
+      <c r="C31" s="84"/>
+    </row>
+    <row r="32" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="85" t="s">
+      <c r="B32" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="85"/>
+      <c r="C32" s="84"/>
       <c r="D32" s="17"/>
     </row>
-    <row r="33" spans="1:4" ht="54.95" customHeight="1">
+    <row r="33" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="85" t="s">
+      <c r="B33" s="84" t="s">
         <v>220</v>
       </c>
-      <c r="C33" s="85"/>
+      <c r="C33" s="84"/>
       <c r="D33" s="17"/>
     </row>
-    <row r="34" spans="1:4" ht="54.95" customHeight="1">
+    <row r="34" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="84" t="s">
         <v>221</v>
       </c>
-      <c r="C34" s="85"/>
+      <c r="C34" s="84"/>
       <c r="D34" s="17"/>
     </row>
-    <row r="35" spans="1:4" ht="54.95" customHeight="1">
+    <row r="35" spans="1:4" ht="54.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="85" t="s">
+      <c r="B35" s="84" t="s">
         <v>222</v>
       </c>
-      <c r="C35" s="85"/>
+      <c r="C35" s="84"/>
       <c r="D35" s="17"/>
     </row>
-    <row r="36" spans="1:4" ht="18.75" customHeight="1">
+    <row r="36" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="85" t="s">
+      <c r="B36" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="85"/>
-    </row>
-    <row r="37" spans="1:4" ht="50.1" customHeight="1">
+      <c r="C36" s="84"/>
+    </row>
+    <row r="37" spans="1:4" ht="50.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="85" t="s">
+      <c r="B37" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="85"/>
+      <c r="C37" s="84"/>
       <c r="D37" s="17"/>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
         <v>208</v>
       </c>
@@ -2881,7 +2881,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ERnHc8J7kjsQBz3ST3lE867VwG+ZIRG+FxfEXa2xg04FcgmEeyfoQkNsBSGlxWCRjK75D/IFPs65s7LTGrGa4Q==" saltValue="9gMkRekPo/0TdSbMM/Zy5Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Zg9X4T9sllKvlGD6lQM/Bu/yPhk2y9pQ1CYI9sNDk7qPCKGRZLfIogTt7CcwLU8K3ZiWr1yG1130snY1xXp94A==" saltValue="FEUjD4HnK3a09R7oW0y50g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
@@ -2920,7 +2920,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:BD70"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="61"/>
     <col min="2" max="2" width="16.625" style="61" customWidth="1"/>
@@ -2928,27 +2928,27 @@
     <col min="57" max="16384" width="9" style="61"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:56">
+    <row r="2" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B2" s="61" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="3" spans="2:56">
+    <row r="3" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B3" s="61" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="4" spans="2:56">
+    <row r="4" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B4" s="61" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="2:56">
+    <row r="5" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B5" s="61" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="6" spans="2:56">
+    <row r="6" spans="2:56" x14ac:dyDescent="0.4">
       <c r="C6" s="62" t="s">
         <v>229</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="AF6" s="63"/>
       <c r="AG6" s="64"/>
     </row>
-    <row r="7" spans="2:56">
+    <row r="7" spans="2:56" x14ac:dyDescent="0.4">
       <c r="C7" s="65" t="s">
         <v>231</v>
       </c>
@@ -3022,7 +3022,7 @@
       <c r="AF7" s="66"/>
       <c r="AG7" s="67"/>
     </row>
-    <row r="8" spans="2:56">
+    <row r="8" spans="2:56" x14ac:dyDescent="0.4">
       <c r="C8" s="62" t="s">
         <v>233</v>
       </c>
@@ -3059,7 +3059,7 @@
       <c r="AF8" s="63"/>
       <c r="AG8" s="64"/>
     </row>
-    <row r="9" spans="2:56">
+    <row r="9" spans="2:56" x14ac:dyDescent="0.4">
       <c r="C9" s="65"/>
       <c r="D9" s="66"/>
       <c r="E9" s="66"/>
@@ -3094,120 +3094,120 @@
       <c r="AF9" s="66"/>
       <c r="AG9" s="67"/>
     </row>
-    <row r="10" spans="2:56">
+    <row r="10" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B10" s="61" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="12" spans="2:56" ht="23.25">
-      <c r="B12" s="91" t="s">
+    <row r="12" spans="2:56" ht="23.25" x14ac:dyDescent="0.4">
+      <c r="B12" s="92" t="s">
         <v>237</v>
       </c>
-      <c r="C12" s="92"/>
-      <c r="D12" s="92"/>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="92"/>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
-      <c r="L12" s="92"/>
-      <c r="M12" s="92"/>
-      <c r="N12" s="92"/>
-      <c r="O12" s="92"/>
-      <c r="P12" s="92"/>
-      <c r="Q12" s="92"/>
-      <c r="R12" s="92"/>
-      <c r="S12" s="92"/>
-      <c r="T12" s="92"/>
-      <c r="U12" s="92"/>
-      <c r="V12" s="92"/>
-      <c r="W12" s="92"/>
-      <c r="X12" s="92"/>
-      <c r="Y12" s="92"/>
-      <c r="Z12" s="92"/>
-      <c r="AA12" s="92"/>
-      <c r="AB12" s="92"/>
-      <c r="AC12" s="92"/>
-      <c r="AD12" s="92"/>
-      <c r="AE12" s="92"/>
-      <c r="AF12" s="92"/>
-      <c r="AG12" s="92"/>
-      <c r="AH12" s="92"/>
-      <c r="AI12" s="92"/>
-      <c r="AJ12" s="92"/>
-      <c r="AK12" s="92"/>
-      <c r="AL12" s="92"/>
-      <c r="AM12" s="92"/>
-      <c r="AN12" s="92"/>
-      <c r="AO12" s="92"/>
-      <c r="AP12" s="92"/>
-      <c r="AQ12" s="92"/>
-      <c r="AR12" s="92"/>
-      <c r="AS12" s="92"/>
-      <c r="AT12" s="92"/>
-      <c r="AU12" s="92"/>
-      <c r="AV12" s="92"/>
-      <c r="AW12" s="92"/>
-      <c r="AX12" s="92"/>
-      <c r="AY12" s="92"/>
-    </row>
-    <row r="13" spans="2:56">
-      <c r="B13" s="93" t="s">
+      <c r="C12" s="93"/>
+      <c r="D12" s="93"/>
+      <c r="E12" s="93"/>
+      <c r="F12" s="93"/>
+      <c r="G12" s="93"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="93"/>
+      <c r="J12" s="93"/>
+      <c r="K12" s="93"/>
+      <c r="L12" s="93"/>
+      <c r="M12" s="93"/>
+      <c r="N12" s="93"/>
+      <c r="O12" s="93"/>
+      <c r="P12" s="93"/>
+      <c r="Q12" s="93"/>
+      <c r="R12" s="93"/>
+      <c r="S12" s="93"/>
+      <c r="T12" s="93"/>
+      <c r="U12" s="93"/>
+      <c r="V12" s="93"/>
+      <c r="W12" s="93"/>
+      <c r="X12" s="93"/>
+      <c r="Y12" s="93"/>
+      <c r="Z12" s="93"/>
+      <c r="AA12" s="93"/>
+      <c r="AB12" s="93"/>
+      <c r="AC12" s="93"/>
+      <c r="AD12" s="93"/>
+      <c r="AE12" s="93"/>
+      <c r="AF12" s="93"/>
+      <c r="AG12" s="93"/>
+      <c r="AH12" s="93"/>
+      <c r="AI12" s="93"/>
+      <c r="AJ12" s="93"/>
+      <c r="AK12" s="93"/>
+      <c r="AL12" s="93"/>
+      <c r="AM12" s="93"/>
+      <c r="AN12" s="93"/>
+      <c r="AO12" s="93"/>
+      <c r="AP12" s="93"/>
+      <c r="AQ12" s="93"/>
+      <c r="AR12" s="93"/>
+      <c r="AS12" s="93"/>
+      <c r="AT12" s="93"/>
+      <c r="AU12" s="93"/>
+      <c r="AV12" s="93"/>
+      <c r="AW12" s="93"/>
+      <c r="AX12" s="93"/>
+      <c r="AY12" s="93"/>
+    </row>
+    <row r="13" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="B13" s="94" t="s">
         <v>238</v>
       </c>
-      <c r="C13" s="92"/>
-      <c r="D13" s="92"/>
-      <c r="E13" s="92"/>
-      <c r="F13" s="92"/>
-      <c r="G13" s="92"/>
-      <c r="H13" s="92"/>
-      <c r="I13" s="92"/>
-      <c r="J13" s="92"/>
-      <c r="K13" s="92"/>
-      <c r="L13" s="92"/>
-      <c r="M13" s="92"/>
-      <c r="N13" s="92"/>
-      <c r="O13" s="92"/>
-      <c r="P13" s="92"/>
-      <c r="Q13" s="92"/>
-      <c r="R13" s="92"/>
-      <c r="S13" s="92"/>
-      <c r="T13" s="92"/>
-      <c r="U13" s="92"/>
-      <c r="V13" s="92"/>
-      <c r="W13" s="92"/>
-      <c r="X13" s="92"/>
-      <c r="Y13" s="92"/>
-      <c r="Z13" s="92"/>
-      <c r="AA13" s="92"/>
-      <c r="AB13" s="92"/>
-      <c r="AC13" s="92"/>
-      <c r="AD13" s="92"/>
-      <c r="AE13" s="92"/>
-      <c r="AF13" s="92"/>
-      <c r="AG13" s="92"/>
-      <c r="AH13" s="92"/>
-      <c r="AI13" s="92"/>
-      <c r="AJ13" s="92"/>
-      <c r="AK13" s="92"/>
-      <c r="AL13" s="92"/>
-      <c r="AM13" s="92"/>
-      <c r="AN13" s="92"/>
-      <c r="AO13" s="92"/>
-      <c r="AP13" s="92"/>
-      <c r="AQ13" s="92"/>
-      <c r="AR13" s="92"/>
-      <c r="AS13" s="92"/>
-      <c r="AT13" s="92"/>
-      <c r="AU13" s="92"/>
-      <c r="AV13" s="92"/>
-      <c r="AW13" s="92"/>
-      <c r="AX13" s="92"/>
-      <c r="AY13" s="92"/>
-    </row>
-    <row r="14" spans="2:56">
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="93"/>
+      <c r="K13" s="93"/>
+      <c r="L13" s="93"/>
+      <c r="M13" s="93"/>
+      <c r="N13" s="93"/>
+      <c r="O13" s="93"/>
+      <c r="P13" s="93"/>
+      <c r="Q13" s="93"/>
+      <c r="R13" s="93"/>
+      <c r="S13" s="93"/>
+      <c r="T13" s="93"/>
+      <c r="U13" s="93"/>
+      <c r="V13" s="93"/>
+      <c r="W13" s="93"/>
+      <c r="X13" s="93"/>
+      <c r="Y13" s="93"/>
+      <c r="Z13" s="93"/>
+      <c r="AA13" s="93"/>
+      <c r="AB13" s="93"/>
+      <c r="AC13" s="93"/>
+      <c r="AD13" s="93"/>
+      <c r="AE13" s="93"/>
+      <c r="AF13" s="93"/>
+      <c r="AG13" s="93"/>
+      <c r="AH13" s="93"/>
+      <c r="AI13" s="93"/>
+      <c r="AJ13" s="93"/>
+      <c r="AK13" s="93"/>
+      <c r="AL13" s="93"/>
+      <c r="AM13" s="93"/>
+      <c r="AN13" s="93"/>
+      <c r="AO13" s="93"/>
+      <c r="AP13" s="93"/>
+      <c r="AQ13" s="93"/>
+      <c r="AR13" s="93"/>
+      <c r="AS13" s="93"/>
+      <c r="AT13" s="93"/>
+      <c r="AU13" s="93"/>
+      <c r="AV13" s="93"/>
+      <c r="AW13" s="93"/>
+      <c r="AX13" s="93"/>
+      <c r="AY13" s="93"/>
+    </row>
+    <row r="14" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B14" s="68"/>
       <c r="C14" s="69" t="s">
         <v>239</v>
@@ -3265,7 +3265,7 @@
       <c r="AX14" s="68"/>
       <c r="AY14" s="68"/>
     </row>
-    <row r="15" spans="2:56">
+    <row r="15" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B15" s="72" t="s">
         <v>242</v>
       </c>
@@ -3424,7 +3424,7 @@
       <c r="BC15" s="74"/>
       <c r="BD15" s="74"/>
     </row>
-    <row r="17" spans="2:56">
+    <row r="17" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B17" s="75" t="s">
         <v>243</v>
       </c>
@@ -3485,7 +3485,7 @@
       <c r="BC17" s="76"/>
       <c r="BD17" s="76"/>
     </row>
-    <row r="18" spans="2:56">
+    <row r="18" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B18" s="77" t="s">
         <v>245</v>
       </c>
@@ -3536,7 +3536,7 @@
       <c r="AW18" s="78"/>
       <c r="AX18" s="78"/>
     </row>
-    <row r="19" spans="2:56">
+    <row r="19" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B19" s="77" t="s">
         <v>246</v>
       </c>
@@ -3572,7 +3572,7 @@
       <c r="AR19" s="79"/>
       <c r="AS19" s="79"/>
     </row>
-    <row r="20" spans="2:56">
+    <row r="20" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B20" s="77" t="s">
         <v>247</v>
       </c>
@@ -3608,7 +3608,7 @@
       <c r="AR20" s="80"/>
       <c r="AS20" s="80"/>
     </row>
-    <row r="21" spans="2:56">
+    <row r="21" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B21" s="77" t="s">
         <v>248</v>
       </c>
@@ -3667,7 +3667,7 @@
       <c r="BC21" s="81"/>
       <c r="BD21" s="81"/>
     </row>
-    <row r="22" spans="2:56">
+    <row r="22" spans="2:56" x14ac:dyDescent="0.4">
       <c r="E22" s="81"/>
       <c r="F22" s="81"/>
       <c r="G22" s="81"/>
@@ -3723,55 +3723,55 @@
       <c r="BC22" s="81"/>
       <c r="BD22" s="81"/>
     </row>
-    <row r="23" spans="2:56">
-      <c r="B23" s="89" t="s">
+    <row r="23" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="B23" s="90" t="s">
         <v>251</v>
       </c>
-      <c r="C23" s="90"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="90"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="90"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="90"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="90"/>
-      <c r="P23" s="90"/>
-    </row>
-    <row r="24" spans="2:56">
-      <c r="B24" s="94" t="s">
+      <c r="C23" s="89"/>
+      <c r="D23" s="89"/>
+      <c r="E23" s="89"/>
+      <c r="F23" s="89"/>
+      <c r="G23" s="89"/>
+      <c r="H23" s="89"/>
+      <c r="I23" s="89"/>
+      <c r="J23" s="89"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="89"/>
+      <c r="P23" s="89"/>
+    </row>
+    <row r="24" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="B24" s="88" t="s">
         <v>252</v>
       </c>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="90"/>
-      <c r="H24" s="90"/>
-      <c r="I24" s="90"/>
-      <c r="J24" s="90"/>
-      <c r="K24" s="90"/>
-      <c r="L24" s="90"/>
-      <c r="M24" s="90"/>
-      <c r="N24" s="90"/>
-      <c r="O24" s="90"/>
-      <c r="P24" s="90"/>
-      <c r="Q24" s="90"/>
-      <c r="R24" s="90"/>
-      <c r="S24" s="90"/>
-      <c r="T24" s="90"/>
-      <c r="U24" s="90"/>
-      <c r="V24" s="90"/>
-      <c r="W24" s="90"/>
-      <c r="X24" s="90"/>
-      <c r="Y24" s="90"/>
-      <c r="Z24" s="90"/>
-    </row>
-    <row r="27" spans="2:56">
+      <c r="C24" s="89"/>
+      <c r="D24" s="89"/>
+      <c r="E24" s="89"/>
+      <c r="F24" s="89"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="89"/>
+      <c r="I24" s="89"/>
+      <c r="J24" s="89"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="89"/>
+      <c r="N24" s="89"/>
+      <c r="O24" s="89"/>
+      <c r="P24" s="89"/>
+      <c r="Q24" s="89"/>
+      <c r="R24" s="89"/>
+      <c r="S24" s="89"/>
+      <c r="T24" s="89"/>
+      <c r="U24" s="89"/>
+      <c r="V24" s="89"/>
+      <c r="W24" s="89"/>
+      <c r="X24" s="89"/>
+      <c r="Y24" s="89"/>
+      <c r="Z24" s="89"/>
+    </row>
+    <row r="27" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B27" s="75" t="s">
         <v>253</v>
       </c>
@@ -3832,7 +3832,7 @@
       <c r="BC27" s="76"/>
       <c r="BD27" s="76"/>
     </row>
-    <row r="28" spans="2:56">
+    <row r="28" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B28" s="77" t="s">
         <v>245</v>
       </c>
@@ -3878,7 +3878,7 @@
       <c r="AR28" s="78"/>
       <c r="AS28" s="78"/>
     </row>
-    <row r="29" spans="2:56">
+    <row r="29" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B29" s="77" t="s">
         <v>246</v>
       </c>
@@ -3919,7 +3919,7 @@
       <c r="AW29" s="79"/>
       <c r="AX29" s="79"/>
     </row>
-    <row r="30" spans="2:56">
+    <row r="30" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B30" s="77" t="s">
         <v>247</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="AW30" s="80"/>
       <c r="AX30" s="80"/>
     </row>
-    <row r="31" spans="2:56">
+    <row r="31" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B31" s="77" t="s">
         <v>248</v>
       </c>
@@ -4019,7 +4019,7 @@
       <c r="BC31" s="81"/>
       <c r="BD31" s="81"/>
     </row>
-    <row r="32" spans="2:56">
+    <row r="32" spans="2:56" x14ac:dyDescent="0.4">
       <c r="E32" s="81"/>
       <c r="F32" s="81"/>
       <c r="G32" s="81"/>
@@ -4075,12 +4075,12 @@
       <c r="BC32" s="81"/>
       <c r="BD32" s="81"/>
     </row>
-    <row r="34" spans="2:56">
+    <row r="34" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B34" s="61" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="35" spans="2:56">
+    <row r="35" spans="2:56" x14ac:dyDescent="0.4">
       <c r="C35" s="62" t="s">
         <v>258</v>
       </c>
@@ -4118,7 +4118,7 @@
       <c r="AG35" s="63"/>
       <c r="AH35" s="64"/>
     </row>
-    <row r="36" spans="2:56">
+    <row r="36" spans="2:56" x14ac:dyDescent="0.4">
       <c r="C36" s="65" t="s">
         <v>231</v>
       </c>
@@ -4156,7 +4156,7 @@
       <c r="AG36" s="66"/>
       <c r="AH36" s="67"/>
     </row>
-    <row r="37" spans="2:56">
+    <row r="37" spans="2:56" x14ac:dyDescent="0.4">
       <c r="C37" s="62" t="s">
         <v>260</v>
       </c>
@@ -4194,7 +4194,7 @@
       <c r="AG37" s="63"/>
       <c r="AH37" s="64"/>
     </row>
-    <row r="38" spans="2:56">
+    <row r="38" spans="2:56" x14ac:dyDescent="0.4">
       <c r="C38" s="65"/>
       <c r="D38" s="66"/>
       <c r="E38" s="66"/>
@@ -4230,61 +4230,61 @@
       <c r="AG38" s="66"/>
       <c r="AH38" s="67"/>
     </row>
-    <row r="40" spans="2:56" ht="23.25">
-      <c r="B40" s="91" t="s">
+    <row r="40" spans="2:56" ht="23.25" x14ac:dyDescent="0.4">
+      <c r="B40" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="C40" s="92"/>
-      <c r="D40" s="92"/>
-      <c r="E40" s="92"/>
-      <c r="F40" s="92"/>
-      <c r="G40" s="92"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="92"/>
-      <c r="J40" s="92"/>
-      <c r="K40" s="92"/>
-      <c r="L40" s="92"/>
-      <c r="M40" s="92"/>
-      <c r="N40" s="92"/>
-      <c r="O40" s="92"/>
-      <c r="P40" s="92"/>
-      <c r="Q40" s="92"/>
-      <c r="R40" s="92"/>
-      <c r="S40" s="92"/>
-      <c r="T40" s="92"/>
-      <c r="U40" s="92"/>
-      <c r="V40" s="92"/>
-      <c r="W40" s="92"/>
-      <c r="X40" s="92"/>
-      <c r="Y40" s="92"/>
-      <c r="Z40" s="92"/>
-      <c r="AA40" s="92"/>
-      <c r="AB40" s="92"/>
-      <c r="AC40" s="92"/>
-      <c r="AD40" s="92"/>
-      <c r="AE40" s="92"/>
-      <c r="AF40" s="92"/>
-      <c r="AG40" s="92"/>
-      <c r="AH40" s="92"/>
-      <c r="AI40" s="92"/>
-      <c r="AJ40" s="92"/>
-      <c r="AK40" s="92"/>
-      <c r="AL40" s="92"/>
-      <c r="AM40" s="92"/>
-      <c r="AN40" s="92"/>
-      <c r="AO40" s="92"/>
-      <c r="AP40" s="92"/>
-      <c r="AQ40" s="92"/>
-      <c r="AR40" s="92"/>
-      <c r="AS40" s="92"/>
-      <c r="AT40" s="92"/>
-      <c r="AU40" s="92"/>
-      <c r="AV40" s="92"/>
-      <c r="AW40" s="92"/>
-      <c r="AX40" s="92"/>
-      <c r="AY40" s="92"/>
-    </row>
-    <row r="41" spans="2:56">
+      <c r="C40" s="93"/>
+      <c r="D40" s="93"/>
+      <c r="E40" s="93"/>
+      <c r="F40" s="93"/>
+      <c r="G40" s="93"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="93"/>
+      <c r="J40" s="93"/>
+      <c r="K40" s="93"/>
+      <c r="L40" s="93"/>
+      <c r="M40" s="93"/>
+      <c r="N40" s="93"/>
+      <c r="O40" s="93"/>
+      <c r="P40" s="93"/>
+      <c r="Q40" s="93"/>
+      <c r="R40" s="93"/>
+      <c r="S40" s="93"/>
+      <c r="T40" s="93"/>
+      <c r="U40" s="93"/>
+      <c r="V40" s="93"/>
+      <c r="W40" s="93"/>
+      <c r="X40" s="93"/>
+      <c r="Y40" s="93"/>
+      <c r="Z40" s="93"/>
+      <c r="AA40" s="93"/>
+      <c r="AB40" s="93"/>
+      <c r="AC40" s="93"/>
+      <c r="AD40" s="93"/>
+      <c r="AE40" s="93"/>
+      <c r="AF40" s="93"/>
+      <c r="AG40" s="93"/>
+      <c r="AH40" s="93"/>
+      <c r="AI40" s="93"/>
+      <c r="AJ40" s="93"/>
+      <c r="AK40" s="93"/>
+      <c r="AL40" s="93"/>
+      <c r="AM40" s="93"/>
+      <c r="AN40" s="93"/>
+      <c r="AO40" s="93"/>
+      <c r="AP40" s="93"/>
+      <c r="AQ40" s="93"/>
+      <c r="AR40" s="93"/>
+      <c r="AS40" s="93"/>
+      <c r="AT40" s="93"/>
+      <c r="AU40" s="93"/>
+      <c r="AV40" s="93"/>
+      <c r="AW40" s="93"/>
+      <c r="AX40" s="93"/>
+      <c r="AY40" s="93"/>
+    </row>
+    <row r="41" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B41" s="72" t="s">
         <v>242</v>
       </c>
@@ -4443,7 +4443,7 @@
       <c r="BC41" s="74"/>
       <c r="BD41" s="74"/>
     </row>
-    <row r="43" spans="2:56">
+    <row r="43" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B43" s="75" t="s">
         <v>264</v>
       </c>
@@ -4504,7 +4504,7 @@
       <c r="BC43" s="76"/>
       <c r="BD43" s="76"/>
     </row>
-    <row r="44" spans="2:56">
+    <row r="44" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B44" s="77" t="s">
         <v>245</v>
       </c>
@@ -4555,7 +4555,7 @@
       <c r="AW44" s="78"/>
       <c r="AX44" s="78"/>
     </row>
-    <row r="45" spans="2:56">
+    <row r="45" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B45" s="77" t="s">
         <v>265</v>
       </c>
@@ -4591,7 +4591,7 @@
       <c r="AR45" s="79"/>
       <c r="AS45" s="79"/>
     </row>
-    <row r="46" spans="2:56">
+    <row r="46" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B46" s="77" t="s">
         <v>247</v>
       </c>
@@ -4627,7 +4627,7 @@
       <c r="AR46" s="80"/>
       <c r="AS46" s="80"/>
     </row>
-    <row r="47" spans="2:56">
+    <row r="47" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B47" s="77" t="s">
         <v>248</v>
       </c>
@@ -4686,7 +4686,7 @@
       <c r="BC47" s="81"/>
       <c r="BD47" s="81"/>
     </row>
-    <row r="48" spans="2:56">
+    <row r="48" spans="2:56" x14ac:dyDescent="0.4">
       <c r="E48" s="81"/>
       <c r="F48" s="81"/>
       <c r="G48" s="81"/>
@@ -4737,60 +4737,60 @@
       <c r="BC48" s="81"/>
       <c r="BD48" s="81"/>
     </row>
-    <row r="49" spans="2:56">
-      <c r="B49" s="89" t="s">
+    <row r="49" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="B49" s="90" t="s">
         <v>251</v>
       </c>
-      <c r="C49" s="90"/>
-      <c r="D49" s="90"/>
-      <c r="E49" s="90"/>
-      <c r="F49" s="90"/>
-      <c r="G49" s="90"/>
-      <c r="H49" s="90"/>
-      <c r="I49" s="90"/>
-      <c r="J49" s="90"/>
-      <c r="K49" s="90"/>
-      <c r="L49" s="90"/>
-      <c r="M49" s="90"/>
-      <c r="N49" s="90"/>
-      <c r="O49" s="90"/>
-      <c r="P49" s="90"/>
-    </row>
-    <row r="50" spans="2:56">
-      <c r="B50" s="94" t="s">
+      <c r="C49" s="89"/>
+      <c r="D49" s="89"/>
+      <c r="E49" s="89"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
+      <c r="I49" s="89"/>
+      <c r="J49" s="89"/>
+      <c r="K49" s="89"/>
+      <c r="L49" s="89"/>
+      <c r="M49" s="89"/>
+      <c r="N49" s="89"/>
+      <c r="O49" s="89"/>
+      <c r="P49" s="89"/>
+    </row>
+    <row r="50" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="B50" s="88" t="s">
         <v>268</v>
       </c>
-      <c r="C50" s="90"/>
-      <c r="D50" s="90"/>
-      <c r="E50" s="90"/>
-      <c r="F50" s="90"/>
-      <c r="G50" s="90"/>
-      <c r="H50" s="90"/>
-      <c r="I50" s="90"/>
-      <c r="J50" s="90"/>
-      <c r="K50" s="90"/>
-      <c r="L50" s="90"/>
-      <c r="M50" s="90"/>
-      <c r="N50" s="90"/>
-      <c r="O50" s="90"/>
-      <c r="P50" s="90"/>
-      <c r="Q50" s="90"/>
-      <c r="R50" s="90"/>
-      <c r="S50" s="90"/>
-      <c r="T50" s="90"/>
-      <c r="U50" s="90"/>
-      <c r="V50" s="90"/>
-      <c r="W50" s="90"/>
-      <c r="X50" s="90"/>
-      <c r="Y50" s="90"/>
-      <c r="Z50" s="90"/>
-    </row>
-    <row r="51" spans="2:56">
+      <c r="C50" s="89"/>
+      <c r="D50" s="89"/>
+      <c r="E50" s="89"/>
+      <c r="F50" s="89"/>
+      <c r="G50" s="89"/>
+      <c r="H50" s="89"/>
+      <c r="I50" s="89"/>
+      <c r="J50" s="89"/>
+      <c r="K50" s="89"/>
+      <c r="L50" s="89"/>
+      <c r="M50" s="89"/>
+      <c r="N50" s="89"/>
+      <c r="O50" s="89"/>
+      <c r="P50" s="89"/>
+      <c r="Q50" s="89"/>
+      <c r="R50" s="89"/>
+      <c r="S50" s="89"/>
+      <c r="T50" s="89"/>
+      <c r="U50" s="89"/>
+      <c r="V50" s="89"/>
+      <c r="W50" s="89"/>
+      <c r="X50" s="89"/>
+      <c r="Y50" s="89"/>
+      <c r="Z50" s="89"/>
+    </row>
+    <row r="51" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B51" s="61" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="53" spans="2:56">
+    <row r="53" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B53" s="75" t="s">
         <v>270</v>
       </c>
@@ -4851,7 +4851,7 @@
       <c r="BC53" s="76"/>
       <c r="BD53" s="76"/>
     </row>
-    <row r="54" spans="2:56">
+    <row r="54" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B54" s="77" t="s">
         <v>245</v>
       </c>
@@ -4897,7 +4897,7 @@
       <c r="AR54" s="78"/>
       <c r="AS54" s="78"/>
     </row>
-    <row r="55" spans="2:56">
+    <row r="55" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B55" s="77" t="s">
         <v>265</v>
       </c>
@@ -4938,7 +4938,7 @@
       <c r="AW55" s="79"/>
       <c r="AX55" s="79"/>
     </row>
-    <row r="56" spans="2:56">
+    <row r="56" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B56" s="77" t="s">
         <v>247</v>
       </c>
@@ -4979,7 +4979,7 @@
       <c r="AW56" s="80"/>
       <c r="AX56" s="80"/>
     </row>
-    <row r="57" spans="2:56">
+    <row r="57" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B57" s="77" t="s">
         <v>248</v>
       </c>
@@ -5038,7 +5038,7 @@
       <c r="BC57" s="81"/>
       <c r="BD57" s="81"/>
     </row>
-    <row r="58" spans="2:56">
+    <row r="58" spans="2:56" x14ac:dyDescent="0.4">
       <c r="E58" s="81"/>
       <c r="F58" s="81"/>
       <c r="G58" s="81"/>
@@ -5077,347 +5077,347 @@
       <c r="BC58" s="81"/>
       <c r="BD58" s="81"/>
     </row>
-    <row r="59" spans="2:56">
-      <c r="B59" s="89" t="s">
+    <row r="59" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="B59" s="90" t="s">
         <v>272</v>
       </c>
-      <c r="C59" s="90"/>
-      <c r="D59" s="90"/>
-      <c r="E59" s="90"/>
-      <c r="F59" s="90"/>
-      <c r="G59" s="90"/>
-      <c r="H59" s="90"/>
-      <c r="I59" s="90"/>
-      <c r="J59" s="90"/>
-      <c r="K59" s="90"/>
-      <c r="L59" s="90"/>
-      <c r="M59" s="90"/>
-      <c r="N59" s="90"/>
-      <c r="O59" s="90"/>
-      <c r="P59" s="90"/>
-    </row>
-    <row r="60" spans="2:56">
-      <c r="B60" s="94" t="s">
+      <c r="C59" s="89"/>
+      <c r="D59" s="89"/>
+      <c r="E59" s="89"/>
+      <c r="F59" s="89"/>
+      <c r="G59" s="89"/>
+      <c r="H59" s="89"/>
+      <c r="I59" s="89"/>
+      <c r="J59" s="89"/>
+      <c r="K59" s="89"/>
+      <c r="L59" s="89"/>
+      <c r="M59" s="89"/>
+      <c r="N59" s="89"/>
+      <c r="O59" s="89"/>
+      <c r="P59" s="89"/>
+    </row>
+    <row r="60" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="B60" s="88" t="s">
         <v>268</v>
       </c>
-      <c r="C60" s="90"/>
-      <c r="D60" s="90"/>
-      <c r="E60" s="90"/>
-      <c r="F60" s="90"/>
-      <c r="G60" s="90"/>
-      <c r="H60" s="90"/>
-      <c r="I60" s="90"/>
-      <c r="J60" s="90"/>
-      <c r="K60" s="90"/>
-      <c r="L60" s="90"/>
-      <c r="M60" s="90"/>
-      <c r="N60" s="90"/>
-      <c r="O60" s="90"/>
-      <c r="P60" s="90"/>
-      <c r="Q60" s="90"/>
-      <c r="R60" s="90"/>
-      <c r="S60" s="90"/>
-      <c r="T60" s="90"/>
-      <c r="U60" s="90"/>
-      <c r="V60" s="90"/>
-      <c r="W60" s="90"/>
-      <c r="X60" s="90"/>
-      <c r="Y60" s="90"/>
-      <c r="Z60" s="90"/>
-    </row>
-    <row r="61" spans="2:56">
+      <c r="C60" s="89"/>
+      <c r="D60" s="89"/>
+      <c r="E60" s="89"/>
+      <c r="F60" s="89"/>
+      <c r="G60" s="89"/>
+      <c r="H60" s="89"/>
+      <c r="I60" s="89"/>
+      <c r="J60" s="89"/>
+      <c r="K60" s="89"/>
+      <c r="L60" s="89"/>
+      <c r="M60" s="89"/>
+      <c r="N60" s="89"/>
+      <c r="O60" s="89"/>
+      <c r="P60" s="89"/>
+      <c r="Q60" s="89"/>
+      <c r="R60" s="89"/>
+      <c r="S60" s="89"/>
+      <c r="T60" s="89"/>
+      <c r="U60" s="89"/>
+      <c r="V60" s="89"/>
+      <c r="W60" s="89"/>
+      <c r="X60" s="89"/>
+      <c r="Y60" s="89"/>
+      <c r="Z60" s="89"/>
+    </row>
+    <row r="61" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B61" s="61" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="63" spans="2:56">
+    <row r="63" spans="2:56" x14ac:dyDescent="0.4">
       <c r="B63" s="75" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:56">
-      <c r="B64" s="95" t="s">
+    <row r="64" spans="2:56" x14ac:dyDescent="0.4">
+      <c r="B64" s="91" t="s">
         <v>274</v>
       </c>
-      <c r="C64" s="90"/>
-      <c r="D64" s="90"/>
-      <c r="E64" s="90"/>
-      <c r="F64" s="90"/>
-      <c r="G64" s="90"/>
-      <c r="H64" s="90"/>
-      <c r="I64" s="90"/>
-      <c r="J64" s="90"/>
-      <c r="K64" s="90"/>
-      <c r="L64" s="90"/>
-      <c r="M64" s="90"/>
-      <c r="N64" s="90"/>
-      <c r="O64" s="90"/>
-      <c r="P64" s="90"/>
-      <c r="Q64" s="90"/>
-      <c r="R64" s="90"/>
-      <c r="S64" s="90"/>
-      <c r="T64" s="90"/>
-      <c r="U64" s="90"/>
-      <c r="V64" s="90"/>
-      <c r="W64" s="90"/>
-      <c r="X64" s="90"/>
-      <c r="Y64" s="90"/>
-      <c r="Z64" s="90"/>
-      <c r="AA64" s="90"/>
-      <c r="AB64" s="90"/>
-      <c r="AC64" s="90"/>
-      <c r="AD64" s="90"/>
-      <c r="AE64" s="90"/>
-      <c r="AF64" s="90"/>
-      <c r="AG64" s="90"/>
-      <c r="AH64" s="90"/>
-      <c r="AI64" s="90"/>
-      <c r="AJ64" s="90"/>
-      <c r="AK64" s="90"/>
-      <c r="AL64" s="90"/>
-      <c r="AM64" s="90"/>
-      <c r="AN64" s="90"/>
-      <c r="AO64" s="90"/>
-      <c r="AP64" s="90"/>
-      <c r="AQ64" s="90"/>
-      <c r="AR64" s="90"/>
-      <c r="AS64" s="90"/>
-      <c r="AT64" s="90"/>
-      <c r="AU64" s="90"/>
-      <c r="AV64" s="90"/>
-      <c r="AW64" s="90"/>
-      <c r="AX64" s="90"/>
-      <c r="AY64" s="90"/>
-    </row>
-    <row r="65" spans="2:51">
-      <c r="B65" s="90"/>
-      <c r="C65" s="90"/>
-      <c r="D65" s="90"/>
-      <c r="E65" s="90"/>
-      <c r="F65" s="90"/>
-      <c r="G65" s="90"/>
-      <c r="H65" s="90"/>
-      <c r="I65" s="90"/>
-      <c r="J65" s="90"/>
-      <c r="K65" s="90"/>
-      <c r="L65" s="90"/>
-      <c r="M65" s="90"/>
-      <c r="N65" s="90"/>
-      <c r="O65" s="90"/>
-      <c r="P65" s="90"/>
-      <c r="Q65" s="90"/>
-      <c r="R65" s="90"/>
-      <c r="S65" s="90"/>
-      <c r="T65" s="90"/>
-      <c r="U65" s="90"/>
-      <c r="V65" s="90"/>
-      <c r="W65" s="90"/>
-      <c r="X65" s="90"/>
-      <c r="Y65" s="90"/>
-      <c r="Z65" s="90"/>
-      <c r="AA65" s="90"/>
-      <c r="AB65" s="90"/>
-      <c r="AC65" s="90"/>
-      <c r="AD65" s="90"/>
-      <c r="AE65" s="90"/>
-      <c r="AF65" s="90"/>
-      <c r="AG65" s="90"/>
-      <c r="AH65" s="90"/>
-      <c r="AI65" s="90"/>
-      <c r="AJ65" s="90"/>
-      <c r="AK65" s="90"/>
-      <c r="AL65" s="90"/>
-      <c r="AM65" s="90"/>
-      <c r="AN65" s="90"/>
-      <c r="AO65" s="90"/>
-      <c r="AP65" s="90"/>
-      <c r="AQ65" s="90"/>
-      <c r="AR65" s="90"/>
-      <c r="AS65" s="90"/>
-      <c r="AT65" s="90"/>
-      <c r="AU65" s="90"/>
-      <c r="AV65" s="90"/>
-      <c r="AW65" s="90"/>
-      <c r="AX65" s="90"/>
-      <c r="AY65" s="90"/>
-    </row>
-    <row r="66" spans="2:51">
-      <c r="B66" s="90"/>
-      <c r="C66" s="90"/>
-      <c r="D66" s="90"/>
-      <c r="E66" s="90"/>
-      <c r="F66" s="90"/>
-      <c r="G66" s="90"/>
-      <c r="H66" s="90"/>
-      <c r="I66" s="90"/>
-      <c r="J66" s="90"/>
-      <c r="K66" s="90"/>
-      <c r="L66" s="90"/>
-      <c r="M66" s="90"/>
-      <c r="N66" s="90"/>
-      <c r="O66" s="90"/>
-      <c r="P66" s="90"/>
-      <c r="Q66" s="90"/>
-      <c r="R66" s="90"/>
-      <c r="S66" s="90"/>
-      <c r="T66" s="90"/>
-      <c r="U66" s="90"/>
-      <c r="V66" s="90"/>
-      <c r="W66" s="90"/>
-      <c r="X66" s="90"/>
-      <c r="Y66" s="90"/>
-      <c r="Z66" s="90"/>
-      <c r="AA66" s="90"/>
-      <c r="AB66" s="90"/>
-      <c r="AC66" s="90"/>
-      <c r="AD66" s="90"/>
-      <c r="AE66" s="90"/>
-      <c r="AF66" s="90"/>
-      <c r="AG66" s="90"/>
-      <c r="AH66" s="90"/>
-      <c r="AI66" s="90"/>
-      <c r="AJ66" s="90"/>
-      <c r="AK66" s="90"/>
-      <c r="AL66" s="90"/>
-      <c r="AM66" s="90"/>
-      <c r="AN66" s="90"/>
-      <c r="AO66" s="90"/>
-      <c r="AP66" s="90"/>
-      <c r="AQ66" s="90"/>
-      <c r="AR66" s="90"/>
-      <c r="AS66" s="90"/>
-      <c r="AT66" s="90"/>
-      <c r="AU66" s="90"/>
-      <c r="AV66" s="90"/>
-      <c r="AW66" s="90"/>
-      <c r="AX66" s="90"/>
-      <c r="AY66" s="90"/>
-    </row>
-    <row r="68" spans="2:51">
+      <c r="C64" s="89"/>
+      <c r="D64" s="89"/>
+      <c r="E64" s="89"/>
+      <c r="F64" s="89"/>
+      <c r="G64" s="89"/>
+      <c r="H64" s="89"/>
+      <c r="I64" s="89"/>
+      <c r="J64" s="89"/>
+      <c r="K64" s="89"/>
+      <c r="L64" s="89"/>
+      <c r="M64" s="89"/>
+      <c r="N64" s="89"/>
+      <c r="O64" s="89"/>
+      <c r="P64" s="89"/>
+      <c r="Q64" s="89"/>
+      <c r="R64" s="89"/>
+      <c r="S64" s="89"/>
+      <c r="T64" s="89"/>
+      <c r="U64" s="89"/>
+      <c r="V64" s="89"/>
+      <c r="W64" s="89"/>
+      <c r="X64" s="89"/>
+      <c r="Y64" s="89"/>
+      <c r="Z64" s="89"/>
+      <c r="AA64" s="89"/>
+      <c r="AB64" s="89"/>
+      <c r="AC64" s="89"/>
+      <c r="AD64" s="89"/>
+      <c r="AE64" s="89"/>
+      <c r="AF64" s="89"/>
+      <c r="AG64" s="89"/>
+      <c r="AH64" s="89"/>
+      <c r="AI64" s="89"/>
+      <c r="AJ64" s="89"/>
+      <c r="AK64" s="89"/>
+      <c r="AL64" s="89"/>
+      <c r="AM64" s="89"/>
+      <c r="AN64" s="89"/>
+      <c r="AO64" s="89"/>
+      <c r="AP64" s="89"/>
+      <c r="AQ64" s="89"/>
+      <c r="AR64" s="89"/>
+      <c r="AS64" s="89"/>
+      <c r="AT64" s="89"/>
+      <c r="AU64" s="89"/>
+      <c r="AV64" s="89"/>
+      <c r="AW64" s="89"/>
+      <c r="AX64" s="89"/>
+      <c r="AY64" s="89"/>
+    </row>
+    <row r="65" spans="2:51" x14ac:dyDescent="0.4">
+      <c r="B65" s="89"/>
+      <c r="C65" s="89"/>
+      <c r="D65" s="89"/>
+      <c r="E65" s="89"/>
+      <c r="F65" s="89"/>
+      <c r="G65" s="89"/>
+      <c r="H65" s="89"/>
+      <c r="I65" s="89"/>
+      <c r="J65" s="89"/>
+      <c r="K65" s="89"/>
+      <c r="L65" s="89"/>
+      <c r="M65" s="89"/>
+      <c r="N65" s="89"/>
+      <c r="O65" s="89"/>
+      <c r="P65" s="89"/>
+      <c r="Q65" s="89"/>
+      <c r="R65" s="89"/>
+      <c r="S65" s="89"/>
+      <c r="T65" s="89"/>
+      <c r="U65" s="89"/>
+      <c r="V65" s="89"/>
+      <c r="W65" s="89"/>
+      <c r="X65" s="89"/>
+      <c r="Y65" s="89"/>
+      <c r="Z65" s="89"/>
+      <c r="AA65" s="89"/>
+      <c r="AB65" s="89"/>
+      <c r="AC65" s="89"/>
+      <c r="AD65" s="89"/>
+      <c r="AE65" s="89"/>
+      <c r="AF65" s="89"/>
+      <c r="AG65" s="89"/>
+      <c r="AH65" s="89"/>
+      <c r="AI65" s="89"/>
+      <c r="AJ65" s="89"/>
+      <c r="AK65" s="89"/>
+      <c r="AL65" s="89"/>
+      <c r="AM65" s="89"/>
+      <c r="AN65" s="89"/>
+      <c r="AO65" s="89"/>
+      <c r="AP65" s="89"/>
+      <c r="AQ65" s="89"/>
+      <c r="AR65" s="89"/>
+      <c r="AS65" s="89"/>
+      <c r="AT65" s="89"/>
+      <c r="AU65" s="89"/>
+      <c r="AV65" s="89"/>
+      <c r="AW65" s="89"/>
+      <c r="AX65" s="89"/>
+      <c r="AY65" s="89"/>
+    </row>
+    <row r="66" spans="2:51" x14ac:dyDescent="0.4">
+      <c r="B66" s="89"/>
+      <c r="C66" s="89"/>
+      <c r="D66" s="89"/>
+      <c r="E66" s="89"/>
+      <c r="F66" s="89"/>
+      <c r="G66" s="89"/>
+      <c r="H66" s="89"/>
+      <c r="I66" s="89"/>
+      <c r="J66" s="89"/>
+      <c r="K66" s="89"/>
+      <c r="L66" s="89"/>
+      <c r="M66" s="89"/>
+      <c r="N66" s="89"/>
+      <c r="O66" s="89"/>
+      <c r="P66" s="89"/>
+      <c r="Q66" s="89"/>
+      <c r="R66" s="89"/>
+      <c r="S66" s="89"/>
+      <c r="T66" s="89"/>
+      <c r="U66" s="89"/>
+      <c r="V66" s="89"/>
+      <c r="W66" s="89"/>
+      <c r="X66" s="89"/>
+      <c r="Y66" s="89"/>
+      <c r="Z66" s="89"/>
+      <c r="AA66" s="89"/>
+      <c r="AB66" s="89"/>
+      <c r="AC66" s="89"/>
+      <c r="AD66" s="89"/>
+      <c r="AE66" s="89"/>
+      <c r="AF66" s="89"/>
+      <c r="AG66" s="89"/>
+      <c r="AH66" s="89"/>
+      <c r="AI66" s="89"/>
+      <c r="AJ66" s="89"/>
+      <c r="AK66" s="89"/>
+      <c r="AL66" s="89"/>
+      <c r="AM66" s="89"/>
+      <c r="AN66" s="89"/>
+      <c r="AO66" s="89"/>
+      <c r="AP66" s="89"/>
+      <c r="AQ66" s="89"/>
+      <c r="AR66" s="89"/>
+      <c r="AS66" s="89"/>
+      <c r="AT66" s="89"/>
+      <c r="AU66" s="89"/>
+      <c r="AV66" s="89"/>
+      <c r="AW66" s="89"/>
+      <c r="AX66" s="89"/>
+      <c r="AY66" s="89"/>
+    </row>
+    <row r="68" spans="2:51" x14ac:dyDescent="0.4">
       <c r="B68" s="75" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="69" spans="2:51">
-      <c r="B69" s="95" t="s">
+    <row r="69" spans="2:51" x14ac:dyDescent="0.4">
+      <c r="B69" s="91" t="s">
         <v>276</v>
       </c>
-      <c r="C69" s="90"/>
-      <c r="D69" s="90"/>
-      <c r="E69" s="90"/>
-      <c r="F69" s="90"/>
-      <c r="G69" s="90"/>
-      <c r="H69" s="90"/>
-      <c r="I69" s="90"/>
-      <c r="J69" s="90"/>
-      <c r="K69" s="90"/>
-      <c r="L69" s="90"/>
-      <c r="M69" s="90"/>
-      <c r="N69" s="90"/>
-      <c r="O69" s="90"/>
-      <c r="P69" s="90"/>
-      <c r="Q69" s="90"/>
-      <c r="R69" s="90"/>
-      <c r="S69" s="90"/>
-      <c r="T69" s="90"/>
-      <c r="U69" s="90"/>
-      <c r="V69" s="90"/>
-      <c r="W69" s="90"/>
-      <c r="X69" s="90"/>
-      <c r="Y69" s="90"/>
-      <c r="Z69" s="90"/>
-      <c r="AA69" s="90"/>
-      <c r="AB69" s="90"/>
-      <c r="AC69" s="90"/>
-      <c r="AD69" s="90"/>
-      <c r="AE69" s="90"/>
-      <c r="AF69" s="90"/>
-      <c r="AG69" s="90"/>
-      <c r="AH69" s="90"/>
-      <c r="AI69" s="90"/>
-      <c r="AJ69" s="90"/>
-      <c r="AK69" s="90"/>
-      <c r="AL69" s="90"/>
-      <c r="AM69" s="90"/>
-      <c r="AN69" s="90"/>
-      <c r="AO69" s="90"/>
-      <c r="AP69" s="90"/>
-      <c r="AQ69" s="90"/>
-      <c r="AR69" s="90"/>
-      <c r="AS69" s="90"/>
-      <c r="AT69" s="90"/>
-      <c r="AU69" s="90"/>
-      <c r="AV69" s="90"/>
-      <c r="AW69" s="90"/>
-      <c r="AX69" s="90"/>
-      <c r="AY69" s="90"/>
-    </row>
-    <row r="70" spans="2:51">
-      <c r="B70" s="90"/>
-      <c r="C70" s="90"/>
-      <c r="D70" s="90"/>
-      <c r="E70" s="90"/>
-      <c r="F70" s="90"/>
-      <c r="G70" s="90"/>
-      <c r="H70" s="90"/>
-      <c r="I70" s="90"/>
-      <c r="J70" s="90"/>
-      <c r="K70" s="90"/>
-      <c r="L70" s="90"/>
-      <c r="M70" s="90"/>
-      <c r="N70" s="90"/>
-      <c r="O70" s="90"/>
-      <c r="P70" s="90"/>
-      <c r="Q70" s="90"/>
-      <c r="R70" s="90"/>
-      <c r="S70" s="90"/>
-      <c r="T70" s="90"/>
-      <c r="U70" s="90"/>
-      <c r="V70" s="90"/>
-      <c r="W70" s="90"/>
-      <c r="X70" s="90"/>
-      <c r="Y70" s="90"/>
-      <c r="Z70" s="90"/>
-      <c r="AA70" s="90"/>
-      <c r="AB70" s="90"/>
-      <c r="AC70" s="90"/>
-      <c r="AD70" s="90"/>
-      <c r="AE70" s="90"/>
-      <c r="AF70" s="90"/>
-      <c r="AG70" s="90"/>
-      <c r="AH70" s="90"/>
-      <c r="AI70" s="90"/>
-      <c r="AJ70" s="90"/>
-      <c r="AK70" s="90"/>
-      <c r="AL70" s="90"/>
-      <c r="AM70" s="90"/>
-      <c r="AN70" s="90"/>
-      <c r="AO70" s="90"/>
-      <c r="AP70" s="90"/>
-      <c r="AQ70" s="90"/>
-      <c r="AR70" s="90"/>
-      <c r="AS70" s="90"/>
-      <c r="AT70" s="90"/>
-      <c r="AU70" s="90"/>
-      <c r="AV70" s="90"/>
-      <c r="AW70" s="90"/>
-      <c r="AX70" s="90"/>
-      <c r="AY70" s="90"/>
+      <c r="C69" s="89"/>
+      <c r="D69" s="89"/>
+      <c r="E69" s="89"/>
+      <c r="F69" s="89"/>
+      <c r="G69" s="89"/>
+      <c r="H69" s="89"/>
+      <c r="I69" s="89"/>
+      <c r="J69" s="89"/>
+      <c r="K69" s="89"/>
+      <c r="L69" s="89"/>
+      <c r="M69" s="89"/>
+      <c r="N69" s="89"/>
+      <c r="O69" s="89"/>
+      <c r="P69" s="89"/>
+      <c r="Q69" s="89"/>
+      <c r="R69" s="89"/>
+      <c r="S69" s="89"/>
+      <c r="T69" s="89"/>
+      <c r="U69" s="89"/>
+      <c r="V69" s="89"/>
+      <c r="W69" s="89"/>
+      <c r="X69" s="89"/>
+      <c r="Y69" s="89"/>
+      <c r="Z69" s="89"/>
+      <c r="AA69" s="89"/>
+      <c r="AB69" s="89"/>
+      <c r="AC69" s="89"/>
+      <c r="AD69" s="89"/>
+      <c r="AE69" s="89"/>
+      <c r="AF69" s="89"/>
+      <c r="AG69" s="89"/>
+      <c r="AH69" s="89"/>
+      <c r="AI69" s="89"/>
+      <c r="AJ69" s="89"/>
+      <c r="AK69" s="89"/>
+      <c r="AL69" s="89"/>
+      <c r="AM69" s="89"/>
+      <c r="AN69" s="89"/>
+      <c r="AO69" s="89"/>
+      <c r="AP69" s="89"/>
+      <c r="AQ69" s="89"/>
+      <c r="AR69" s="89"/>
+      <c r="AS69" s="89"/>
+      <c r="AT69" s="89"/>
+      <c r="AU69" s="89"/>
+      <c r="AV69" s="89"/>
+      <c r="AW69" s="89"/>
+      <c r="AX69" s="89"/>
+      <c r="AY69" s="89"/>
+    </row>
+    <row r="70" spans="2:51" x14ac:dyDescent="0.4">
+      <c r="B70" s="89"/>
+      <c r="C70" s="89"/>
+      <c r="D70" s="89"/>
+      <c r="E70" s="89"/>
+      <c r="F70" s="89"/>
+      <c r="G70" s="89"/>
+      <c r="H70" s="89"/>
+      <c r="I70" s="89"/>
+      <c r="J70" s="89"/>
+      <c r="K70" s="89"/>
+      <c r="L70" s="89"/>
+      <c r="M70" s="89"/>
+      <c r="N70" s="89"/>
+      <c r="O70" s="89"/>
+      <c r="P70" s="89"/>
+      <c r="Q70" s="89"/>
+      <c r="R70" s="89"/>
+      <c r="S70" s="89"/>
+      <c r="T70" s="89"/>
+      <c r="U70" s="89"/>
+      <c r="V70" s="89"/>
+      <c r="W70" s="89"/>
+      <c r="X70" s="89"/>
+      <c r="Y70" s="89"/>
+      <c r="Z70" s="89"/>
+      <c r="AA70" s="89"/>
+      <c r="AB70" s="89"/>
+      <c r="AC70" s="89"/>
+      <c r="AD70" s="89"/>
+      <c r="AE70" s="89"/>
+      <c r="AF70" s="89"/>
+      <c r="AG70" s="89"/>
+      <c r="AH70" s="89"/>
+      <c r="AI70" s="89"/>
+      <c r="AJ70" s="89"/>
+      <c r="AK70" s="89"/>
+      <c r="AL70" s="89"/>
+      <c r="AM70" s="89"/>
+      <c r="AN70" s="89"/>
+      <c r="AO70" s="89"/>
+      <c r="AP70" s="89"/>
+      <c r="AQ70" s="89"/>
+      <c r="AR70" s="89"/>
+      <c r="AS70" s="89"/>
+      <c r="AT70" s="89"/>
+      <c r="AU70" s="89"/>
+      <c r="AV70" s="89"/>
+      <c r="AW70" s="89"/>
+      <c r="AX70" s="89"/>
+      <c r="AY70" s="89"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="oRew7oK5RrebL3ikYbb5mrrqCwtYk96SN7lm2yyxRaPIrPICb7DS7sYEbupYaTok13XO6PM3C0vgC2TZ6/xVQA==" saltValue="3tduD31ZVtNoKEQtwr17xQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="11">
-    <mergeCell ref="B50:Z50"/>
-    <mergeCell ref="B59:P59"/>
-    <mergeCell ref="B60:Z60"/>
-    <mergeCell ref="B64:AY66"/>
-    <mergeCell ref="B69:AY70"/>
     <mergeCell ref="B49:P49"/>
     <mergeCell ref="B12:AY12"/>
     <mergeCell ref="B13:AY13"/>
     <mergeCell ref="B23:P23"/>
     <mergeCell ref="B24:Z24"/>
     <mergeCell ref="B40:AY40"/>
+    <mergeCell ref="B50:Z50"/>
+    <mergeCell ref="B59:P59"/>
+    <mergeCell ref="B60:Z60"/>
+    <mergeCell ref="B64:AY66"/>
+    <mergeCell ref="B69:AY70"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5428,7 +5428,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="30" style="10" customWidth="1"/>
     <col min="2" max="2" width="22.625" style="10" customWidth="1"/>
@@ -5439,17 +5439,17 @@
     <col min="7" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="98" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A1" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1">
+      <c r="B1" s="96"/>
+      <c r="C1" s="96"/>
+      <c r="D1" s="96"/>
+      <c r="E1" s="96"/>
+      <c r="F1" s="96"/>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="12" t="s">
         <v>40</v>
       </c>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="F3" s="12"/>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1">
+    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="13" t="s">
         <v>44</v>
       </c>
@@ -5484,7 +5484,7 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1">
+    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="13" t="s">
         <v>47</v>
       </c>
@@ -5501,7 +5501,7 @@
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
     </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1">
+    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="13" t="s">
         <v>50</v>
       </c>
@@ -5518,7 +5518,7 @@
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1">
+    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
         <v>52</v>
       </c>
@@ -5535,7 +5535,7 @@
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1">
+    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
         <v>54</v>
       </c>
@@ -5552,7 +5552,7 @@
       <c r="E8" s="13"/>
       <c r="F8" s="13"/>
     </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1">
+    <row r="9" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="13" t="s">
         <v>56</v>
       </c>
@@ -5569,7 +5569,7 @@
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1">
+    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="13" t="s">
         <v>58</v>
       </c>
@@ -5586,7 +5586,7 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1">
+    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13" t="s">
         <v>61</v>
       </c>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="F11" s="13"/>
     </row>
-    <row r="12" spans="1:6" ht="37.5" customHeight="1">
+    <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="13" t="s">
         <v>24</v>
       </c>
@@ -5622,7 +5622,7 @@
       <c r="E12" s="13"/>
       <c r="F12" s="13"/>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1">
+    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="13" t="s">
         <v>65</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1">
+    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13" t="s">
         <v>68</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1">
+    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="13" t="s">
         <v>71</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1">
+    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="10" t="s">
         <v>74</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1">
+    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="10" t="s">
         <v>25</v>
       </c>
@@ -5702,73 +5702,73 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1"/>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1">
+    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="98" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1">
-      <c r="B20" s="97"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-    </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1">
-      <c r="B21" s="97"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="97"/>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1"/>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A23" s="96" t="s">
+      <c r="C19" s="96"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="96"/>
+      <c r="F19" s="96"/>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B20" s="96"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="96"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="96"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="96"/>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="95" t="s">
         <v>80</v>
       </c>
-      <c r="B23" s="97"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="97"/>
-    </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1">
+      <c r="B23" s="96"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="96"/>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="99" t="s">
+      <c r="B24" s="98" t="s">
         <v>224</v>
       </c>
-      <c r="C24" s="97"/>
-      <c r="D24" s="97"/>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1">
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="99" t="s">
+      <c r="B25" s="98" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1">
+      <c r="C25" s="96"/>
+      <c r="D25" s="96"/>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="99" t="s">
+      <c r="B26" s="98" t="s">
         <v>84</v>
       </c>
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-    </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1"/>
+      <c r="C26" s="96"/>
+      <c r="D26" s="96"/>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="RL8xUoJgQXr1o0YCUzHa1TR5jGiwEormafv3pgBz5bAwpR0uYdjHMctOBkQSE8cnspnulXwIKRl4qUNlj3YcNg==" saltValue="Qor62r+Udy9XQqoKoo04LQ==" spinCount="100000" sheet="1" selectLockedCells="1"/>
   <mergeCells count="6">
@@ -5788,7 +5788,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AQ25"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="10" customWidth="1"/>
     <col min="2" max="2" width="13" style="10" customWidth="1"/>
@@ -5822,21 +5822,21 @@
     <col min="44" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="24">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:43" ht="24" x14ac:dyDescent="0.5">
+      <c r="A1" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
-      <c r="H1" s="84"/>
-      <c r="I1" s="84"/>
-      <c r="J1" s="84"/>
-    </row>
-    <row r="2" spans="1:43">
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="99"/>
+      <c r="E1" s="99"/>
+      <c r="F1" s="99"/>
+      <c r="G1" s="99"/>
+      <c r="H1" s="99"/>
+      <c r="I1" s="99"/>
+      <c r="J1" s="99"/>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.4">
       <c r="A2" s="11" t="s">
         <v>86</v>
       </c>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="AN2" s="10"/>
     </row>
-    <row r="3" spans="1:43" ht="60" customHeight="1">
+    <row r="3" spans="1:43" ht="60" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="22" t="s">
         <v>87</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="1:43" ht="18.75" customHeight="1">
+    <row r="4" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="24">
         <v>1</v>
       </c>
@@ -6199,7 +6199,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I4="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -6340,7 +6340,7 @@
         <v>25695348</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="18.75" customHeight="1">
+    <row r="5" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="24">
         <v>2</v>
       </c>
@@ -6550,7 +6550,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I5="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -6691,7 +6691,7 @@
         <v>25021948</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="18.75" customHeight="1">
+    <row r="6" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="24">
         <v>3</v>
       </c>
@@ -6901,7 +6901,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I6="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -7042,7 +7042,7 @@
         <v>25128418</v>
       </c>
     </row>
-    <row r="7" spans="1:43" ht="18.75" customHeight="1">
+    <row r="7" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="24">
         <v>4</v>
       </c>
@@ -7252,7 +7252,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I7="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -7393,7 +7393,7 @@
         <v>25234888</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="18.75" customHeight="1">
+    <row r="8" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="24">
         <v>5</v>
       </c>
@@ -7603,7 +7603,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I8="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -7744,7 +7744,7 @@
         <v>25341358</v>
       </c>
     </row>
-    <row r="9" spans="1:43" ht="18.75" customHeight="1">
+    <row r="9" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="24">
         <v>6</v>
       </c>
@@ -7954,7 +7954,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I9="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -8095,7 +8095,7 @@
         <v>25442723</v>
       </c>
     </row>
-    <row r="10" spans="1:43" ht="18.75" customHeight="1">
+    <row r="10" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="24">
         <v>7</v>
       </c>
@@ -8305,7 +8305,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I10="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -8446,7 +8446,7 @@
         <v>25513458</v>
       </c>
     </row>
-    <row r="11" spans="1:43" ht="18.75" customHeight="1">
+    <row r="11" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="24">
         <v>8</v>
       </c>
@@ -8656,7 +8656,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I11="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -8797,7 +8797,7 @@
         <v>25584193</v>
       </c>
     </row>
-    <row r="12" spans="1:43" ht="18.75" customHeight="1">
+    <row r="12" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="24">
         <v>9</v>
       </c>
@@ -9007,7 +9007,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I12="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -9148,7 +9148,7 @@
         <v>25654928</v>
       </c>
     </row>
-    <row r="13" spans="1:43" ht="18.75" customHeight="1">
+    <row r="13" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24">
         <v>10</v>
       </c>
@@ -9358,7 +9358,7 @@
    )
   ),
   IF(
-   _xlpm.受取順="会社退職金 → DC",
+   ISNUMBER(SEARCH("会社退職金 → ",_xlpm.受取順)),
    IF(
     I13="対象",
     MAX(0,_xlpm.DC本来控除-_xlpm.重複控除),
@@ -9499,16 +9499,16 @@
         <v>25720558</v>
       </c>
     </row>
-    <row r="14" spans="1:43">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.4">
       <c r="AJ14" s="11"/>
     </row>
-    <row r="15" spans="1:43" ht="19.5">
+    <row r="15" spans="1:43" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A15" s="36" t="s">
         <v>115</v>
       </c>
       <c r="O15" s="37"/>
     </row>
-    <row r="16" spans="1:43" ht="18.75" customHeight="1">
+    <row r="16" spans="1:43" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="38" t="s">
         <v>116</v>
       </c>
@@ -9524,7 +9524,7 @@
       <c r="I16" s="40"/>
       <c r="J16" s="40"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B17" s="40"/>
       <c r="C17" s="40"/>
       <c r="D17" s="40"/>
@@ -9535,7 +9535,7 @@
       <c r="I17" s="40"/>
       <c r="J17" s="40"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B18" s="40"/>
       <c r="C18" s="40"/>
       <c r="D18" s="40"/>
@@ -9546,7 +9546,7 @@
       <c r="I18" s="40"/>
       <c r="J18" s="40"/>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="41" t="s">
         <v>118</v>
       </c>
@@ -9554,7 +9554,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="41" t="s">
         <v>194</v>
       </c>
@@ -9562,19 +9562,19 @@
         <v>192</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="41"/>
       <c r="C21" s="39" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="41"/>
       <c r="C22" s="39" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="41" t="s">
         <v>120</v>
       </c>
@@ -9582,7 +9582,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="41" t="s">
         <v>122</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="19.5">
+    <row r="25" spans="1:10" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A25" s="41" t="s">
         <v>124</v>
       </c>
@@ -9599,7 +9599,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="KXrpTWvyWdh5+hrcE5AyRiaoK9Wtey40U6km79OjKFmdLN6F04KVZoIsRClob8fKYAjEUfDqxbrKcz0pfZ2vow==" saltValue="Xh5CyF+qt3k+tbnCarxJ2w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="a2CZFk43gavQysnAa+UOtDdSOBicyEwnog33wRveBzrjvIcsyLDJmWXyusQKREdU9m3R/TTPQnjIFHUCXSdTzA==" saltValue="8VJQkE+FBnxgHk8l6lFpMA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
@@ -9621,7 +9621,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18" style="10" customWidth="1"/>
     <col min="2" max="2" width="12.875" style="10" bestFit="1" customWidth="1"/>
@@ -9641,17 +9641,17 @@
     <col min="23" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A3" s="11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A4" s="43" t="s">
         <v>127</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>25689</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A5" s="43" t="s">
         <v>128</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>33329</v>
       </c>
     </row>
-    <row r="6" spans="1:25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A6" s="43" t="s">
         <v>129</v>
       </c>
@@ -9682,7 +9682,7 @@
         <v>60歳0ヶ月</v>
       </c>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A7" s="43" t="s">
         <v>131</v>
       </c>
@@ -9691,7 +9691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A8" s="43" t="s">
         <v>120</v>
       </c>
@@ -9703,7 +9703,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A9" s="43" t="s">
         <v>133</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>22010000</v>
       </c>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A10" s="43" t="s">
         <v>122</v>
       </c>
@@ -9723,7 +9723,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A11" s="43" t="s">
         <v>135</v>
       </c>
@@ -9738,7 +9738,7 @@
       <c r="S11" s="47"/>
       <c r="T11" s="47"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A12" s="43" t="s">
         <v>137</v>
       </c>
@@ -9767,7 +9767,7 @@
       <c r="X12" s="47"/>
       <c r="Y12" s="47"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A13" s="43" t="s">
         <v>141</v>
       </c>
@@ -9802,7 +9802,7 @@
       <c r="X13" s="47"/>
       <c r="Y13" s="47"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A14" s="43" t="s">
         <v>148</v>
       </c>
@@ -9837,7 +9837,7 @@
       <c r="X14" s="47"/>
       <c r="Y14" s="47"/>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A15" s="43" t="s">
         <v>106</v>
       </c>
@@ -9868,7 +9868,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
       <c r="A16" s="43" t="s">
         <v>153</v>
       </c>
@@ -9900,7 +9900,7 @@
       <c r="X16" s="47"/>
       <c r="Y16" s="47"/>
     </row>
-    <row r="17" spans="2:25">
+    <row r="17" spans="2:25" x14ac:dyDescent="0.4">
       <c r="B17" s="34"/>
       <c r="N17" s="53"/>
       <c r="O17" s="54" t="s">
@@ -9924,7 +9924,7 @@
       <c r="X17" s="47"/>
       <c r="Y17" s="47"/>
     </row>
-    <row r="18" spans="2:25">
+    <row r="18" spans="2:25" x14ac:dyDescent="0.4">
       <c r="N18" s="48" t="s">
         <v>163</v>
       </c>
@@ -9949,7 +9949,7 @@
       <c r="X18" s="47"/>
       <c r="Y18" s="47"/>
     </row>
-    <row r="19" spans="2:25">
+    <row r="19" spans="2:25" x14ac:dyDescent="0.4">
       <c r="N19" s="47"/>
       <c r="O19" s="47"/>
       <c r="P19" s="47"/>
@@ -9970,7 +9970,7 @@
       <c r="X19" s="47"/>
       <c r="Y19" s="47"/>
     </row>
-    <row r="20" spans="2:25">
+    <row r="20" spans="2:25" x14ac:dyDescent="0.4">
       <c r="N20" s="47"/>
       <c r="O20" s="47"/>
       <c r="P20" s="47"/>
@@ -9991,7 +9991,7 @@
       <c r="X20" s="47"/>
       <c r="Y20" s="47"/>
     </row>
-    <row r="21" spans="2:25">
+    <row r="21" spans="2:25" x14ac:dyDescent="0.4">
       <c r="N21" s="47"/>
       <c r="O21" s="47"/>
       <c r="P21" s="47"/>
@@ -10000,57 +10000,57 @@
       <c r="X21" s="47"/>
       <c r="Y21" s="47"/>
     </row>
-    <row r="22" spans="2:25">
+    <row r="22" spans="2:25" x14ac:dyDescent="0.4">
       <c r="W22" s="47"/>
       <c r="X22" s="47"/>
       <c r="Y22" s="47"/>
     </row>
-    <row r="23" spans="2:25">
+    <row r="23" spans="2:25" x14ac:dyDescent="0.4">
       <c r="W23" s="47"/>
       <c r="X23" s="47"/>
       <c r="Y23" s="47"/>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A33" s="11" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A34" s="11" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A35" s="55" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A36" s="11" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A37" s="55" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A38" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A39" s="55" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A40" s="11" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A41" s="55" t="s">
         <v>175</v>
       </c>
@@ -10080,14 +10080,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="38" style="2" customWidth="1"/>
     <col min="2" max="2" width="42" style="2" customWidth="1"/>
     <col min="3" max="6" width="20" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24">
+    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.5">
       <c r="A1" s="100" t="s">
         <v>176</v>
       </c>
@@ -10095,7 +10095,7 @@
       <c r="C1" s="101"/>
       <c r="D1" s="101"/>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>177</v>
       </c>
@@ -10107,21 +10107,21 @@
       <c r="E3" s="101"/>
       <c r="F3" s="101"/>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B4" s="101"/>
       <c r="C4" s="101"/>
       <c r="D4" s="101"/>
       <c r="E4" s="101"/>
       <c r="F4" s="101"/>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B5" s="101"/>
       <c r="C5" s="101"/>
       <c r="D5" s="101"/>
       <c r="E5" s="101"/>
       <c r="F5" s="101"/>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
         <v>179</v>
       </c>
@@ -10131,17 +10131,17 @@
       <c r="C6" s="101"/>
       <c r="D6" s="101"/>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B7" s="101"/>
       <c r="C7" s="101"/>
       <c r="D7" s="101"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B8" s="101"/>
       <c r="C8" s="101"/>
       <c r="D8" s="101"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>181</v>
       </c>
@@ -10153,21 +10153,21 @@
       <c r="E9" s="101"/>
       <c r="F9" s="101"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B10" s="101"/>
       <c r="C10" s="101"/>
       <c r="D10" s="101"/>
       <c r="E10" s="101"/>
       <c r="F10" s="101"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B11" s="101"/>
       <c r="C11" s="101"/>
       <c r="D11" s="101"/>
       <c r="E11" s="101"/>
       <c r="F11" s="101"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>183</v>
       </c>
@@ -10177,21 +10177,21 @@
       <c r="E12" s="101"/>
       <c r="F12" s="101"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B13" s="101"/>
       <c r="C13" s="101"/>
       <c r="D13" s="101"/>
       <c r="E13" s="101"/>
       <c r="F13" s="101"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B14" s="101"/>
       <c r="C14" s="101"/>
       <c r="D14" s="101"/>
       <c r="E14" s="101"/>
       <c r="F14" s="101"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
         <v>184</v>
       </c>
@@ -10199,7 +10199,7 @@
       <c r="C16" s="101"/>
       <c r="D16" s="101"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>185</v>
       </c>
@@ -10209,7 +10209,7 @@
       <c r="C17" s="103"/>
       <c r="D17" s="103"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>186</v>
       </c>
@@ -10219,22 +10219,22 @@
       <c r="C18" s="103"/>
       <c r="D18" s="103"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20"/>
       <c r="B20" s="9" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21"/>
       <c r="B21"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22"/>
       <c r="B22"/>
     </row>
@@ -10265,13 +10265,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
     <col min="2" max="3" width="12" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="56" t="s">
         <v>188</v>
       </c>
@@ -10282,7 +10282,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="58">
         <v>0</v>
       </c>
@@ -10293,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="58">
         <v>1950000</v>
       </c>
@@ -10304,7 +10304,7 @@
         <v>97500</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="58">
         <v>3300000</v>
       </c>
@@ -10315,7 +10315,7 @@
         <v>427500</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="58">
         <v>6950000</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>636000</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="58">
         <v>9000000</v>
       </c>
@@ -10337,7 +10337,7 @@
         <v>1536000</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="58">
         <v>18000000</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>2796000</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="58">
         <v>40000000</v>
       </c>
